--- a/income_forecaster.xlsx
+++ b/income_forecaster.xlsx
@@ -12,6 +12,10 @@
     <sheet name="Forecast" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Taxes" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Personal Expenses" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Framework OPS P&amp;L" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Cash Roll-Forward" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Debt Strategy" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="310">
   <si>
     <t xml:space="preserve">Income Forecaster — Chance Peare</t>
   </si>
@@ -124,6 +128,204 @@
     <t xml:space="preserve">Key assumption — sanity-check</t>
   </si>
   <si>
+    <t xml:space="preserve">PERSONAL / HOUSEHOLD INPUTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale close month # (1=Jun26, 2=Jul, 3=Aug)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default Jul-26 — edit per actual close.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current PITI (until sale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage + tax + insurance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net sale proceeds (post-costs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$615K sale − $471K mortgage − ~$48K (8% costs, pessimistic).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridge rent (post-sale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-year rental during transition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moving costs (one-time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movers, storage, misc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent deposit (1st + last)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 months rent at $3,200.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health insurance (paycheck)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midpoint of $200–600 range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto loan payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7% APR, 5-yr, ~$10K balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal loan #1 payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$13K balance, 4 yrs left, ~10.5% APR (calc).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal loan #2 payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$24.5K balance, 6 yrs, 12.72% APR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC balance (paid at sale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliminated month of sale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC monthly min (until paid off)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~2.5% of balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal #1 payoff month (0=keep)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default: pay off at sale from proceeds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal #2 payoff month (0=keep)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default: pay off at sale (highest APR after CC).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities (electric/water/gas/trash/phone, est)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarpon Springs 4BR estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet (total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allocated 30% to business below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groceries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User said $1K — bumped pessimistic for 6-person household.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User said $200 — bumped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto fuel/maint/insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User said $300 — bumped (2 cars + FL insurance).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal subscriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discretionary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining, household, misc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">401(k) contribution (4% of W2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$96K × 4% / 12 to capture full match.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roth IRA contribution (monthly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$13K/yr ÷ 12. At/near MFJ limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting cash on hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal accounts today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting 401(k) balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright 401(k) balance today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRAMEWORK OPS EXPENSE INPUTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude (monthly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per user.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Railway (monthly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business phones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet allocation to business (30%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30% of $90.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPA / bookkeeping accrual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT YET INCURRED. Annual return + advisory ~$1.5K/yr. Reserve now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E&amp;O / GL insurance (est)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT YET IN PLACE. $50–100/mo for new fractional COO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional software reserve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClickUp, Buffer, etc. as you add tools.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLC + agent (annual, one-time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid for 2026 — accrual for next year.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-Month Income Forecast</t>
   </si>
   <si>
@@ -292,6 +494,33 @@
     <t xml:space="preserve">Effective Rate</t>
   </si>
   <si>
+    <t xml:space="preserve">Consolidated household cash flow (Base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After-tax income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal expenses (avg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Framework OPS OpEx (avg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net household cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-of-year cash position</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tax Model — Take-Home Calculator</t>
   </si>
   <si>
@@ -434,23 +663,318 @@
   </si>
   <si>
     <t xml:space="preserve">• Estimated quarterly payments required for 1099 income. Roughly: SE tax + (1099 × ~22%) ÷ 4 = your quarterly federal payment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Expenses — Monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family of 6 | Housing transition built in | Debt payoff at sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PITI (current home)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent (bridge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moving + rent deposit (one-time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities (less biz internet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal loan #1 ($13K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal loan #2 ($24.5K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC minimum (until sale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">401(k) contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roth IRA contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL PERSONAL OUTFLOWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Framework OPS LLC — Pro Forma P&amp;L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue = client/variable income. Owner pay flows to personal 1040 (no W2 from LLC).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVENUE (Base scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos retainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client 3 retainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel + Upwork variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATING EXPENSES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Railway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet (biz allocation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPA / bookkeeping (accrual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E&amp;O / GL insurance (recommended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLC + agent (accrual for next renewal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total OpEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NET INCOME (pre-owner pay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net margin %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P&amp;L notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Revenue mirrors the Forecast tab base scenario. Edit assumptions there to flow through.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• No COGS — pure services business. Net margin equals operating margin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Owner pay (Chance) is NOT an expense to the LLC — single-member disregarded entity flows net income to your 1040 as 1099 income, already taxed on Taxes tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• When/if S-corp election is made, your W-2 salary from the LLC becomes an expense here, lowering LLC net income — but offset by SE tax savings on personal side. Re-model at that point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• CPA, E&amp;O insurance, software reserve are NOT YET INCURRED — modeled as reserves to plan for. Pull from Mercury when you set them up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Roll-Forward (Base scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts at $11K personal cash. Sale event adds $95K. Debt payoff applied at sale month per assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beginning cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(+) After-tax income (Base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(−) Personal expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(−) Framework OPS OpEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(+) Net sale proceeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(−) Debt payoff (CC, loans)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net cash change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ending cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roll-forward notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• After-tax income line is the Base scenario monthly average from Taxes tab (B43). To stress to Downside, change formula in row 6 to Taxes!$C$43.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Framework OPS OpEx is subtracted because Carlos/Client3 receipts hit your gross 1099 income, but you actually pay these expenses from those receipts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sale proceeds and debt payoffs are one-time, triggered by the month set on Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Roth IRA + 401(k) contributions are treated as outflows (they leave checking) but ARE building net worth elsewhere. Do not double-count.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt Payoff Strategy — Recommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current debt stack (CC first, by APR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Pmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APR (est)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22–29% (typ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 — pay off at sale (no question)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal loan #2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.72%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 — pay off at sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal loan #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~10.5% (calc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 — pay off at sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 — KEEP (rate &lt; safe yield)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 — Skyright paying in full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommended deployment of $95K sale proceeds + $11K cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use of funds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting: existing cash + sale proceeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: Pay off credit cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: Moving costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: Rent deposit (1st + last)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: Pay off Personal Loan #2 ($24.5K @ 12.72%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: Pay off Personal Loan #1 ($13K @ ~10.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining for emergency fund / buffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why this order (data-backed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• CCs at 22–29% APR are the most expensive debt by a wide margin. Eliminating $16K saves $3,500–$4,600/yr in interest. No-brainer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Personal Loan #2 (12.72%) is the next-highest rate. Eliminating $24.5K saves ~$3,116/yr in interest AND frees $499/mo in cash flow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Personal Loan #1 (~10.5% calc) is third. Eliminating $13K saves ~$1,365/yr interest, frees $334/mo cash flow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Keep the auto loan at 7%. After-tax yield on a HYSA is currently ~4.0–4.3%; the spread isn't worth liquidating to kill a 7% debt with a low fixed payment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Combined cash flow freed: $833/mo from killing the two personal loans. That fills the emergency fund and adds to retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Total interest saved over remaining loan terms (rough): $8,000–$12,000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risks / counterpoints (pessimistic check)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sale price $615K is a target, not closed. If it sells for $590K, net proceeds drop to ~$72K. At that level, pay off CC + Loan #2 only; keep $11K cash + $7K residual ($18K). Loan #1 stays.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Family of 6 in housing transition + new consulting practice = volatile period. Standard advice is 6 months of essential expenses as emergency fund. Your essential burn after debt payoff is ~$7,000/mo → 6-month fund = $42K. The recommended plan leaves ~$41K — right at the floor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• CC payoff is only durable if spending behavior holds. If CCs build up again in 90 days, you've traded equity for short-term lifestyle inflation. Set up automatic full-balance pay from Mercury.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Carlos and Client 3 retainers are revocable. If both churn in Q4, you lose $6K/mo of 1099 income. The buffer covers ~6 months of that hole at current burn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• You are NOT carrying business insurance. One client lawsuit (even meritless) can wipe out the emergency fund in legal fees. E&amp;O quote should happen this month, not next quarter.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="\$#,##0"/>
-    <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="0.00%"/>
-    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.00%"/>
+    <numFmt numFmtId="172" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,6 +1048,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -546,6 +1078,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF003366"/>
       </patternFill>
@@ -554,12 +1092,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -603,7 +1135,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -656,7 +1188,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -664,11 +1220,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -700,15 +1256,47 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -720,55 +1308,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1024,7 +1584,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
@@ -1218,13 +1778,394 @@
         <v>32</v>
       </c>
     </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>95000</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>198</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>334</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>499</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>1083</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B58" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A51:D51"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1250,7 +2191,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1268,55 +2209,55 @@
       <c r="O1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>48</v>
+      <c r="A3" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="N3" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1335,312 +2276,312 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="L5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="M5" s="14" t="n">
+      <c r="M5" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="N5" s="14" t="n">
+      <c r="N5" s="20" t="n">
         <f aca="false">SUM(B5:M5)</f>
         <v>96000</v>
       </c>
-      <c r="O5" s="14" t="n">
+      <c r="O5" s="20" t="n">
         <f aca="false">AVERAGE(B5:M5)</f>
         <v>8000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="B6" s="20" t="n">
         <f aca="false">Assumptions!$B$6</f>
         <v>1500</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="K6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="L6" s="14" t="n">
+      <c r="L6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="M6" s="14" t="n">
+      <c r="M6" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="N6" s="14" t="n">
+      <c r="N6" s="20" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>34500</v>
       </c>
-      <c r="O6" s="14" t="n">
+      <c r="O6" s="20" t="n">
         <f aca="false">AVERAGE(B6:M6)</f>
         <v>2875</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="B7" s="20" t="n">
         <f aca="false">IF(1&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="20" t="n">
         <f aca="false">IF(2&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">IF(3&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">IF(4&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="20" t="n">
         <f aca="false">IF(5&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="20" t="n">
         <f aca="false">IF(6&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="20" t="n">
         <f aca="false">IF(7&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="20" t="n">
         <f aca="false">IF(8&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="20" t="n">
         <f aca="false">IF(9&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="20" t="n">
         <f aca="false">IF(10&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="L7" s="14" t="n">
+      <c r="L7" s="20" t="n">
         <f aca="false">IF(11&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="M7" s="20" t="n">
         <f aca="false">IF(12&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="N7" s="14" t="n">
+      <c r="N7" s="20" t="n">
         <f aca="false">SUM(B7:M7)</f>
         <v>27000</v>
       </c>
-      <c r="O7" s="14" t="n">
+      <c r="O7" s="20" t="n">
         <f aca="false">AVERAGE(B7:M7)</f>
         <v>2250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="B8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="20" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>2000</v>
       </c>
-      <c r="N8" s="14" t="n">
+      <c r="N8" s="20" t="n">
         <f aca="false">SUM(B8:M8)</f>
         <v>24000</v>
       </c>
-      <c r="O8" s="14" t="n">
+      <c r="O8" s="20" t="n">
         <f aca="false">AVERAGE(B8:M8)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="B9" s="21" t="n">
         <f aca="false">SUM(B5:B8)</f>
         <v>11500</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="21" t="n">
         <f aca="false">SUM(C5:C8)</f>
         <v>13000</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="21" t="n">
         <f aca="false">SUM(D5:D8)</f>
         <v>13000</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">SUM(E5:E8)</f>
         <v>16000</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="21" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>16000</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="21" t="n">
         <f aca="false">SUM(G5:G8)</f>
         <v>16000</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="21" t="n">
         <f aca="false">SUM(H5:H8)</f>
         <v>16000</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="21" t="n">
         <f aca="false">SUM(I5:I8)</f>
         <v>16000</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="21" t="n">
         <f aca="false">SUM(J5:J8)</f>
         <v>16000</v>
       </c>
-      <c r="K9" s="15" t="n">
+      <c r="K9" s="21" t="n">
         <f aca="false">SUM(K5:K8)</f>
         <v>16000</v>
       </c>
-      <c r="L9" s="15" t="n">
+      <c r="L9" s="21" t="n">
         <f aca="false">SUM(L5:L8)</f>
         <v>16000</v>
       </c>
-      <c r="M9" s="15" t="n">
+      <c r="M9" s="21" t="n">
         <f aca="false">SUM(M5:M8)</f>
         <v>16000</v>
       </c>
-      <c r="N9" s="15" t="n">
+      <c r="N9" s="21" t="n">
         <f aca="false">SUM(B9:M9)</f>
         <v>181500</v>
       </c>
-      <c r="O9" s="15" t="n">
+      <c r="O9" s="21" t="n">
         <f aca="false">AVERAGE(B9:M9)</f>
         <v>15125</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1659,312 +2600,312 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="14" t="n">
+        <v>122</v>
+      </c>
+      <c r="B12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="L12" s="14" t="n">
+      <c r="L12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="20" t="n">
         <f aca="false">Assumptions!$B$5*Assumptions!$B$15</f>
         <v>8000</v>
       </c>
-      <c r="N12" s="14" t="n">
+      <c r="N12" s="20" t="n">
         <f aca="false">SUM(B12:M12)</f>
         <v>96000</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O12" s="20" t="n">
         <f aca="false">AVERAGE(B12:M12)</f>
         <v>8000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="B13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,1&lt;Assumptions!$B$12),Assumptions!$B$6,0)</f>
         <v>1500</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,2&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,3&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,4&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,5&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,6&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,7&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,8&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,9&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>3000</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,10&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="14" t="n">
+      <c r="L13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,11&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="20" t="n">
         <f aca="false">IF(OR(Assumptions!$B$12=0,12&lt;Assumptions!$B$12),Assumptions!$B$7,0)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="14" t="n">
+      <c r="N13" s="20" t="n">
         <f aca="false">SUM(B13:M13)</f>
         <v>25500</v>
       </c>
-      <c r="O13" s="14" t="n">
+      <c r="O13" s="20" t="n">
         <f aca="false">AVERAGE(B13:M13)</f>
         <v>2125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="B14" s="20" t="n">
         <f aca="false">IF(AND(1&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,1&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="20" t="n">
         <f aca="false">IF(AND(2&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,2&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="20" t="n">
         <f aca="false">IF(AND(3&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,3&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="20" t="n">
         <f aca="false">IF(AND(4&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,4&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="20" t="n">
         <f aca="false">IF(AND(5&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,5&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="20" t="n">
         <f aca="false">IF(AND(6&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,6&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="20" t="n">
         <f aca="false">IF(AND(7&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,7&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="20" t="n">
         <f aca="false">IF(AND(8&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,8&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="20" t="n">
         <f aca="false">IF(AND(9&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,9&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="20" t="n">
         <f aca="false">IF(AND(10&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,10&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L14" s="20" t="n">
         <f aca="false">IF(AND(11&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,11&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="20" t="n">
         <f aca="false">IF(AND(12&gt;=Assumptions!$B$9,OR(Assumptions!$B$13=0,12&lt;Assumptions!$B$13)),Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="14" t="n">
+      <c r="N14" s="20" t="n">
         <f aca="false">SUM(B14:M14)</f>
         <v>15000</v>
       </c>
-      <c r="O14" s="14" t="n">
+      <c r="O14" s="20" t="n">
         <f aca="false">AVERAGE(B14:M14)</f>
         <v>1250</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="B15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="L15" s="14" t="n">
+      <c r="L15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="M15" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1-Assumptions!$B$14)</f>
         <v>1000</v>
       </c>
-      <c r="N15" s="14" t="n">
+      <c r="N15" s="20" t="n">
         <f aca="false">SUM(B15:M15)</f>
         <v>12000</v>
       </c>
-      <c r="O15" s="14" t="n">
+      <c r="O15" s="20" t="n">
         <f aca="false">AVERAGE(B15:M15)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="16" t="n">
+        <v>126</v>
+      </c>
+      <c r="B16" s="22" t="n">
         <f aca="false">SUM(B12:B15)</f>
         <v>10500</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="22" t="n">
         <f aca="false">SUM(C12:C15)</f>
         <v>12000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="22" t="n">
         <f aca="false">SUM(D12:D15)</f>
         <v>12000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="22" t="n">
         <f aca="false">SUM(E12:E15)</f>
         <v>15000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="22" t="n">
         <f aca="false">SUM(F12:F15)</f>
         <v>15000</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="22" t="n">
         <f aca="false">SUM(G12:G15)</f>
         <v>15000</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="22" t="n">
         <f aca="false">SUM(H12:H15)</f>
         <v>15000</v>
       </c>
-      <c r="I16" s="16" t="n">
+      <c r="I16" s="22" t="n">
         <f aca="false">SUM(I12:I15)</f>
         <v>15000</v>
       </c>
-      <c r="J16" s="16" t="n">
+      <c r="J16" s="22" t="n">
         <f aca="false">SUM(J12:J15)</f>
         <v>12000</v>
       </c>
-      <c r="K16" s="16" t="n">
+      <c r="K16" s="22" t="n">
         <f aca="false">SUM(K12:K15)</f>
         <v>9000</v>
       </c>
-      <c r="L16" s="16" t="n">
+      <c r="L16" s="22" t="n">
         <f aca="false">SUM(L12:L15)</f>
         <v>9000</v>
       </c>
-      <c r="M16" s="16" t="n">
+      <c r="M16" s="22" t="n">
         <f aca="false">SUM(M12:M15)</f>
         <v>9000</v>
       </c>
-      <c r="N16" s="16" t="n">
+      <c r="N16" s="22" t="n">
         <f aca="false">SUM(B16:M16)</f>
         <v>148500</v>
       </c>
-      <c r="O16" s="16" t="n">
+      <c r="O16" s="22" t="n">
         <f aca="false">AVERAGE(B16:M16)</f>
         <v>12375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1983,305 +2924,305 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="L19" s="14" t="n">
+      <c r="L19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="M19" s="14" t="n">
+      <c r="M19" s="20" t="n">
         <f aca="false">Assumptions!$B$5</f>
         <v>8000</v>
       </c>
-      <c r="N19" s="14" t="n">
+      <c r="N19" s="20" t="n">
         <f aca="false">SUM(B19:M19)</f>
         <v>96000</v>
       </c>
-      <c r="O19" s="14" t="n">
+      <c r="O19" s="20" t="n">
         <f aca="false">AVERAGE(B19:M19)</f>
         <v>8000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="B20" s="20" t="n">
         <f aca="false">Assumptions!$B$6</f>
         <v>1500</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="J20" s="14" t="n">
+      <c r="J20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="K20" s="14" t="n">
+      <c r="K20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="L20" s="14" t="n">
+      <c r="L20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="M20" s="14" t="n">
+      <c r="M20" s="20" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>3000</v>
       </c>
-      <c r="N20" s="14" t="n">
+      <c r="N20" s="20" t="n">
         <f aca="false">SUM(B20:M20)</f>
         <v>34500</v>
       </c>
-      <c r="O20" s="14" t="n">
+      <c r="O20" s="20" t="n">
         <f aca="false">AVERAGE(B20:M20)</f>
         <v>2875</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="B21" s="20" t="n">
         <f aca="false">IF(1&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="20" t="n">
         <f aca="false">IF(2&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="20" t="n">
         <f aca="false">IF(3&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="20" t="n">
         <f aca="false">IF(4&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="20" t="n">
         <f aca="false">IF(5&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="20" t="n">
         <f aca="false">IF(6&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="20" t="n">
         <f aca="false">IF(7&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="I21" s="20" t="n">
         <f aca="false">IF(8&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="J21" s="14" t="n">
+      <c r="J21" s="20" t="n">
         <f aca="false">IF(9&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="K21" s="14" t="n">
+      <c r="K21" s="20" t="n">
         <f aca="false">IF(10&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="L21" s="14" t="n">
+      <c r="L21" s="20" t="n">
         <f aca="false">IF(11&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="M21" s="14" t="n">
+      <c r="M21" s="20" t="n">
         <f aca="false">IF(12&gt;=Assumptions!$B$9,Assumptions!$B$8,0)</f>
         <v>3000</v>
       </c>
-      <c r="N21" s="14" t="n">
+      <c r="N21" s="20" t="n">
         <f aca="false">SUM(B21:M21)</f>
         <v>27000</v>
       </c>
-      <c r="O21" s="14" t="n">
+      <c r="O21" s="20" t="n">
         <f aca="false">AVERAGE(B21:M21)</f>
         <v>2250</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="B22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="G22" s="14" t="n">
+      <c r="G22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="I22" s="14" t="n">
+      <c r="I22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="J22" s="14" t="n">
+      <c r="J22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="K22" s="14" t="n">
+      <c r="K22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="L22" s="14" t="n">
+      <c r="L22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M22" s="20" t="n">
         <f aca="false">Assumptions!$B$10*(1+Assumptions!$B$16)</f>
         <v>2500</v>
       </c>
-      <c r="N22" s="14" t="n">
+      <c r="N22" s="20" t="n">
         <f aca="false">SUM(B22:M22)</f>
         <v>30000</v>
       </c>
-      <c r="O22" s="14" t="n">
+      <c r="O22" s="20" t="n">
         <f aca="false">AVERAGE(B22:M22)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="B23" s="23" t="n">
         <f aca="false">SUM(B19:B22)</f>
         <v>12000</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="23" t="n">
         <f aca="false">SUM(C19:C22)</f>
         <v>13500</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="23" t="n">
         <f aca="false">SUM(D19:D22)</f>
         <v>13500</v>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="23" t="n">
         <f aca="false">SUM(E19:E22)</f>
         <v>16500</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="23" t="n">
         <f aca="false">SUM(F19:F22)</f>
         <v>16500</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G23" s="23" t="n">
         <f aca="false">SUM(G19:G22)</f>
         <v>16500</v>
       </c>
-      <c r="H23" s="17" t="n">
+      <c r="H23" s="23" t="n">
         <f aca="false">SUM(H19:H22)</f>
         <v>16500</v>
       </c>
-      <c r="I23" s="17" t="n">
+      <c r="I23" s="23" t="n">
         <f aca="false">SUM(I19:I22)</f>
         <v>16500</v>
       </c>
-      <c r="J23" s="17" t="n">
+      <c r="J23" s="23" t="n">
         <f aca="false">SUM(J19:J22)</f>
         <v>16500</v>
       </c>
-      <c r="K23" s="17" t="n">
+      <c r="K23" s="23" t="n">
         <f aca="false">SUM(K19:K22)</f>
         <v>16500</v>
       </c>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="23" t="n">
         <f aca="false">SUM(L19:L22)</f>
         <v>16500</v>
       </c>
-      <c r="M23" s="17" t="n">
+      <c r="M23" s="23" t="n">
         <f aca="false">SUM(M19:M22)</f>
         <v>16500</v>
       </c>
-      <c r="N23" s="17" t="n">
+      <c r="N23" s="23" t="n">
         <f aca="false">SUM(B23:M23)</f>
         <v>187500</v>
       </c>
-      <c r="O23" s="17" t="n">
+      <c r="O23" s="23" t="n">
         <f aca="false">AVERAGE(B23:M23)</f>
         <v>15625</v>
       </c>
@@ -2308,7 +3249,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
@@ -2317,298 +3258,377 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>68</v>
+      <c r="A3" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="18" t="n">
+        <v>135</v>
+      </c>
+      <c r="B4" s="24" t="n">
         <f aca="false">Forecast!N9</f>
         <v>181500</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="24" t="n">
         <f aca="false">Forecast!O9</f>
         <v>15125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="18" t="n">
+        <v>136</v>
+      </c>
+      <c r="B5" s="24" t="n">
         <f aca="false">Forecast!N16</f>
         <v>148500</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="24" t="n">
         <f aca="false">Forecast!O16</f>
         <v>12375</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="18" t="n">
+        <v>137</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <f aca="false">Forecast!N23</f>
         <v>187500</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="24" t="n">
         <f aca="false">Forecast!O23</f>
         <v>15625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <f aca="false">Forecast!N5</f>
         <v>96000</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="25" t="n">
         <f aca="false">B9/$B$4</f>
         <v>0.528925619834711</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="B10" s="20" t="n">
         <f aca="false">Forecast!N6</f>
         <v>34500</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="25" t="n">
         <f aca="false">B10/$B$4</f>
         <v>0.190082644628099</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="B11" s="20" t="n">
         <f aca="false">Forecast!N7</f>
         <v>27000</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="25" t="n">
         <f aca="false">B11/$B$4</f>
         <v>0.148760330578512</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="B12" s="20" t="n">
         <f aca="false">Forecast!N8</f>
         <v>24000</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="25" t="n">
         <f aca="false">B12/$B$4</f>
         <v>0.132231404958678</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="21" t="n">
+      <c r="A13" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="27" t="n">
         <f aca="false">SUM(B9:B12)</f>
         <v>181500</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="28" t="n">
         <f aca="false">SUM(C9:C12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
+      <c r="A16" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
+      <c r="A20" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="25" t="n">
+        <v>135</v>
+      </c>
+      <c r="B24" s="24" t="n">
         <f aca="false">Taxes!B42</f>
         <v>159086.342092</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="24" t="n">
         <f aca="false">Taxes!B43</f>
         <v>13257.1951743333</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="25" t="n">
+        <v>151</v>
+      </c>
+      <c r="B25" s="24" t="n">
         <f aca="false">Taxes!C42</f>
         <v>136146.77146</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="24" t="n">
         <f aca="false">Taxes!C43</f>
         <v>11345.5642883333</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="25" t="n">
+        <v>137</v>
+      </c>
+      <c r="B26" s="24" t="n">
         <f aca="false">Taxes!D42</f>
         <v>163257.173116</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="24" t="n">
         <f aca="false">Taxes!D43</f>
         <v>13604.7644263333</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="25" t="n">
+        <v>135</v>
+      </c>
+      <c r="B30" s="24" t="n">
         <f aca="false">Taxes!B41</f>
         <v>22413.657908</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="30" t="n">
         <f aca="false">Taxes!B44</f>
         <v>0.123491228143251</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="25" t="n">
+        <v>151</v>
+      </c>
+      <c r="B31" s="24" t="n">
         <f aca="false">Taxes!C41</f>
         <v>12353.22854</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="30" t="n">
         <f aca="false">Taxes!C44</f>
         <v>0.0831867241750842</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="25" t="n">
+        <v>137</v>
+      </c>
+      <c r="B32" s="24" t="n">
         <f aca="false">Taxes!D41</f>
         <v>24242.826884</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="30" t="n">
         <f aca="false">Taxes!D44</f>
         <v>0.129295076714667</v>
       </c>
     </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="31" t="n">
+        <f aca="false">Taxes!B43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <f aca="false">B36*12</f>
+        <v>159086.342092</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="31" t="n">
+        <f aca="false">'Personal Expenses'!O21</f>
+        <v>9189.5</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <f aca="false">B37*12</f>
+        <v>110274</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">'Framework OPS P&amp;L'!O20</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <f aca="false">B38*12</f>
+        <v>6314</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="33" t="n">
+        <f aca="false">B36-B37-B38</f>
+        <v>3541.52850766667</v>
+      </c>
+      <c r="C39" s="33" t="n">
+        <f aca="false">B39*12</f>
+        <v>42498.342092</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" s="34" t="n">
+        <f aca="false">'Cash Roll-Forward'!M12</f>
+        <v>94998.342092</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A15:C15"/>
@@ -2620,6 +3640,7 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2639,596 +3660,596 @@
   <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="29" t="n">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="35" t="n">
         <v>30000</v>
       </c>
-      <c r="C5" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="31" t="n">
+      <c r="C5" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="34" t="n">
+      <c r="C6" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="39" t="n">
         <v>0.9235</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="35" t="n">
+      <c r="C9" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="9" t="n">
         <v>0.153</v>
       </c>
-      <c r="C10" s="30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="35" t="n">
+      <c r="C10" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="C11" s="30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="n">
+      <c r="C11" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="n">
         <v>23850</v>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="40" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="35" t="n">
         <v>96950</v>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="40" t="n">
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="35" t="n">
         <v>206700</v>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="40" t="n">
         <v>0.22</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="35" t="n">
         <v>394600</v>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="40" t="n">
         <v>0.24</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="35" t="n">
         <v>501050</v>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="40" t="n">
         <v>0.32</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="35" t="n">
         <v>751600</v>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="40" t="n">
         <v>0.35</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="35" t="n">
         <v>10000000</v>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="40" t="n">
         <v>0.37</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="25" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B26" s="24" t="n">
         <f aca="false">Forecast!N5</f>
         <v>96000</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="24" t="n">
         <f aca="false">Forecast!N12</f>
         <v>96000</v>
       </c>
-      <c r="D26" s="25" t="n">
+      <c r="D26" s="24" t="n">
         <f aca="false">Forecast!N19</f>
         <v>96000</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="B27" s="25" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B27" s="24" t="n">
         <f aca="false">(Forecast!N6+Forecast!N7+Forecast!N8)</f>
         <v>85500</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="24" t="n">
         <f aca="false">(Forecast!N13+Forecast!N14+Forecast!N15)</f>
         <v>52500</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="24" t="n">
         <f aca="false">(Forecast!N20+Forecast!N21+Forecast!N22)</f>
         <v>91500</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="38" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="20" t="n">
         <f aca="false">B26+B27</f>
         <v>181500</v>
       </c>
-      <c r="C28" s="38" t="n">
+      <c r="C28" s="20" t="n">
         <f aca="false">C26+C27</f>
         <v>148500</v>
       </c>
-      <c r="D28" s="38" t="n">
+      <c r="D28" s="20" t="n">
         <f aca="false">D26+D27</f>
         <v>187500</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" s="38" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="20" t="n">
         <f aca="false">B27*$B$9</f>
         <v>78959.25</v>
       </c>
-      <c r="C29" s="38" t="n">
+      <c r="C29" s="20" t="n">
         <f aca="false">C27*$B$9</f>
         <v>48483.75</v>
       </c>
-      <c r="D29" s="38" t="n">
+      <c r="D29" s="20" t="n">
         <f aca="false">D27*$B$9</f>
         <v>84500.25</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="38" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="20" t="n">
         <f aca="false">B29*$B$10</f>
         <v>12080.76525</v>
       </c>
-      <c r="C30" s="38" t="n">
+      <c r="C30" s="20" t="n">
         <f aca="false">C29*$B$10</f>
         <v>7418.01375</v>
       </c>
-      <c r="D30" s="38" t="n">
+      <c r="D30" s="20" t="n">
         <f aca="false">D29*$B$10</f>
         <v>12928.53825</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" s="38" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" s="20" t="n">
         <f aca="false">B30/2</f>
         <v>6040.382625</v>
       </c>
-      <c r="C31" s="38" t="n">
+      <c r="C31" s="20" t="n">
         <f aca="false">C30/2</f>
         <v>3709.006875</v>
       </c>
-      <c r="D31" s="38" t="n">
+      <c r="D31" s="20" t="n">
         <f aca="false">D30/2</f>
         <v>6464.269125</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" s="38" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="20" t="n">
         <f aca="false">B26+B27-B31</f>
         <v>175459.617375</v>
       </c>
-      <c r="C32" s="38" t="n">
+      <c r="C32" s="20" t="n">
         <f aca="false">C26+C27-C31</f>
         <v>144790.993125</v>
       </c>
-      <c r="D32" s="38" t="n">
+      <c r="D32" s="20" t="n">
         <f aca="false">D26+D27-D31</f>
         <v>181035.730875</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="B33" s="38" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="20" t="n">
         <f aca="false">B27-B31</f>
         <v>79459.617375</v>
       </c>
-      <c r="C33" s="38" t="n">
+      <c r="C33" s="20" t="n">
         <f aca="false">C27-C31</f>
         <v>48790.993125</v>
       </c>
-      <c r="D33" s="38" t="n">
+      <c r="D33" s="20" t="n">
         <f aca="false">D27-D31</f>
         <v>85035.730875</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" s="38" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="20" t="n">
         <f aca="false">MIN(B33*$B$11,MAX(0,(B32-$B$5))*$B$11)</f>
         <v>15891.923475</v>
       </c>
-      <c r="C34" s="38" t="n">
+      <c r="C34" s="20" t="n">
         <f aca="false">MIN(C33*$B$11,MAX(0,(C32-$B$5))*$B$11)</f>
         <v>9758.198625</v>
       </c>
-      <c r="D34" s="38" t="n">
+      <c r="D34" s="20" t="n">
         <f aca="false">MIN(D33*$B$11,MAX(0,(D32-$B$5))*$B$11)</f>
         <v>17007.146175</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="B35" s="38" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" s="20" t="n">
         <f aca="false">$B$5</f>
         <v>30000</v>
       </c>
-      <c r="C35" s="38" t="n">
+      <c r="C35" s="20" t="n">
         <f aca="false">$B$5</f>
         <v>30000</v>
       </c>
-      <c r="D35" s="38" t="n">
+      <c r="D35" s="20" t="n">
         <f aca="false">$B$5</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="B36" s="38" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="20" t="n">
         <f aca="false">MAX(0,B32-B34-B35)</f>
         <v>129567.6939</v>
       </c>
-      <c r="C36" s="38" t="n">
+      <c r="C36" s="20" t="n">
         <f aca="false">MAX(0,C32-C34-C35)</f>
         <v>105032.7945</v>
       </c>
-      <c r="D36" s="38" t="n">
+      <c r="D36" s="20" t="n">
         <f aca="false">MAX(0,D32-D34-D35)</f>
         <v>134028.5847</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="38" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="20" t="n">
         <f aca="false">MIN(B36,$A$15)*$B$15+MAX(0,MIN(B36,$A$16)-$A$15)*$B$16+MAX(0,MIN(B36,$A$17)-$A$16)*$B$17+MAX(0,MIN(B36,$A$18)-$A$17)*$B$18+MAX(0,MIN(B36,$A$19)-$A$18)*$B$19+MAX(0,MIN(B36,$A$20)-$A$19)*$B$20+MAX(0,MIN(B36,$A$21)-$A$20)*$B$21</f>
         <v>18332.892658</v>
       </c>
-      <c r="C37" s="38" t="n">
+      <c r="C37" s="20" t="n">
         <f aca="false">MIN(C36,$A$15)*$B$15+MAX(0,MIN(C36,$A$16)-$A$15)*$B$16+MAX(0,MIN(C36,$A$17)-$A$16)*$B$17+MAX(0,MIN(C36,$A$18)-$A$17)*$B$18+MAX(0,MIN(C36,$A$19)-$A$18)*$B$19+MAX(0,MIN(C36,$A$20)-$A$19)*$B$20+MAX(0,MIN(C36,$A$21)-$A$20)*$B$21</f>
         <v>12935.21479</v>
       </c>
-      <c r="D37" s="38" t="n">
+      <c r="D37" s="20" t="n">
         <f aca="false">MIN(D36,$A$15)*$B$15+MAX(0,MIN(D36,$A$16)-$A$15)*$B$16+MAX(0,MIN(D36,$A$17)-$A$16)*$B$17+MAX(0,MIN(D36,$A$18)-$A$17)*$B$18+MAX(0,MIN(D36,$A$19)-$A$18)*$B$19+MAX(0,MIN(D36,$A$20)-$A$19)*$B$20+MAX(0,MIN(D36,$A$21)-$A$20)*$B$21</f>
         <v>19314.288634</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="B38" s="38" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" s="20" t="n">
         <f aca="false">$B$6*2000+$B$7*500</f>
         <v>8000</v>
       </c>
-      <c r="C38" s="38" t="n">
+      <c r="C38" s="20" t="n">
         <f aca="false">$B$6*2000+$B$7*500</f>
         <v>8000</v>
       </c>
-      <c r="D38" s="38" t="n">
+      <c r="D38" s="20" t="n">
         <f aca="false">$B$6*2000+$B$7*500</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="B39" s="38" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B39" s="20" t="n">
         <f aca="false">MAX(0,B37-B38)</f>
         <v>10332.892658</v>
       </c>
-      <c r="C39" s="38" t="n">
+      <c r="C39" s="20" t="n">
         <f aca="false">MAX(0,C37-C38)</f>
         <v>4935.21479</v>
       </c>
-      <c r="D39" s="38" t="n">
+      <c r="D39" s="20" t="n">
         <f aca="false">MAX(0,D37-D38)</f>
         <v>11314.288634</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="B40" s="38" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" s="20" t="n">
         <f aca="false">B36*$B$8</f>
         <v>0</v>
       </c>
-      <c r="C40" s="38" t="n">
+      <c r="C40" s="20" t="n">
         <f aca="false">C36*$B$8</f>
         <v>0</v>
       </c>
-      <c r="D40" s="38" t="n">
+      <c r="D40" s="20" t="n">
         <f aca="false">D36*$B$8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="B41" s="39" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" s="27" t="n">
         <f aca="false">B30+B39+B40</f>
         <v>22413.657908</v>
       </c>
-      <c r="C41" s="39" t="n">
+      <c r="C41" s="27" t="n">
         <f aca="false">C30+C39+C40</f>
         <v>12353.22854</v>
       </c>
-      <c r="D41" s="39" t="n">
+      <c r="D41" s="27" t="n">
         <f aca="false">D30+D39+D40</f>
         <v>24242.826884</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="40" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" s="21" t="n">
         <f aca="false">B28-B41</f>
         <v>159086.342092</v>
       </c>
-      <c r="C42" s="40" t="n">
+      <c r="C42" s="21" t="n">
         <f aca="false">C28-C41</f>
         <v>136146.77146</v>
       </c>
-      <c r="D42" s="40" t="n">
+      <c r="D42" s="21" t="n">
         <f aca="false">D28-D41</f>
         <v>163257.173116</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="B43" s="40" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" s="21" t="n">
         <f aca="false">B42/12</f>
         <v>13257.1951743333</v>
       </c>
-      <c r="C43" s="40" t="n">
+      <c r="C43" s="21" t="n">
         <f aca="false">C42/12</f>
         <v>11345.5642883333</v>
       </c>
-      <c r="D43" s="40" t="n">
+      <c r="D43" s="21" t="n">
         <f aca="false">D42/12</f>
         <v>13604.7644263333</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="B44" s="41" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B44" s="25" t="n">
         <f aca="false">B41/B28</f>
         <v>0.123491228143251</v>
       </c>
-      <c r="C44" s="41" t="n">
+      <c r="C44" s="25" t="n">
         <f aca="false">C41/C28</f>
         <v>0.0831867241750842</v>
       </c>
-      <c r="D44" s="41" t="n">
+      <c r="D44" s="25" t="n">
         <f aca="false">D41/D28</f>
         <v>0.129295076714667</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-    </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+    </row>
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+    </row>
+    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
+      <c r="A50" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+    </row>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3254,4 +4275,3354 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="2" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="N4" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" s="19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="31" t="n">
+        <f aca="false">IF(1&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>3600</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <f aca="false">IF(2&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <f aca="false">IF(3&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <f aca="false">IF(4&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <f aca="false">IF(5&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <f aca="false">IF(6&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="31" t="n">
+        <f aca="false">IF(7&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="31" t="n">
+        <f aca="false">IF(8&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="31" t="n">
+        <f aca="false">IF(9&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="31" t="n">
+        <f aca="false">IF(10&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <f aca="false">IF(11&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <f aca="false">IF(12&lt;Assumptions!$B$25,Assumptions!$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="31" t="n">
+        <f aca="false">SUM(B5:M5)</f>
+        <v>3600</v>
+      </c>
+      <c r="O5" s="31" t="n">
+        <f aca="false">AVERAGE(B5:M5)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="31" t="n">
+        <f aca="false">IF(1&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <f aca="false">IF(2&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <f aca="false">IF(3&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <f aca="false">IF(4&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <f aca="false">IF(5&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <f aca="false">IF(6&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <f aca="false">IF(7&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <f aca="false">IF(8&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <f aca="false">IF(9&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <f aca="false">IF(10&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="L6" s="31" t="n">
+        <f aca="false">IF(11&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="M6" s="31" t="n">
+        <f aca="false">IF(12&gt;=Assumptions!$B$25,Assumptions!$B$28,0)</f>
+        <v>3200</v>
+      </c>
+      <c r="N6" s="31" t="n">
+        <f aca="false">SUM(B6:M6)</f>
+        <v>35200</v>
+      </c>
+      <c r="O6" s="31" t="n">
+        <f aca="false">AVERAGE(B6:M6)</f>
+        <v>2933.33333333333</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="31" t="n">
+        <f aca="false">IF(1=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <f aca="false">IF(2=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>11400</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <f aca="false">IF(3=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <f aca="false">IF(4=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <f aca="false">IF(5=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <f aca="false">IF(6=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <f aca="false">IF(7=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="31" t="n">
+        <f aca="false">IF(8=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="31" t="n">
+        <f aca="false">IF(9=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="31" t="n">
+        <f aca="false">IF(10=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="31" t="n">
+        <f aca="false">IF(11=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="31" t="n">
+        <f aca="false">IF(12=Assumptions!$B$25,Assumptions!$B$29+Assumptions!$B$30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="31" t="n">
+        <f aca="false">SUM(B7:M7)</f>
+        <v>11400</v>
+      </c>
+      <c r="O7" s="31" t="n">
+        <f aca="false">AVERAGE(B7:M7)</f>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="I8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="J8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="K8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="L8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="M8" s="31" t="n">
+        <f aca="false">Assumptions!$B$39+Assumptions!$B$40*0.7</f>
+        <v>633</v>
+      </c>
+      <c r="N8" s="31" t="n">
+        <f aca="false">SUM(B8:M8)</f>
+        <v>7596</v>
+      </c>
+      <c r="O8" s="31" t="n">
+        <f aca="false">AVERAGE(B8:M8)</f>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="I9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="J9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="K9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="L9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="M9" s="31" t="n">
+        <f aca="false">Assumptions!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="N9" s="31" t="n">
+        <f aca="false">SUM(B9:M9)</f>
+        <v>4800</v>
+      </c>
+      <c r="O9" s="31" t="n">
+        <f aca="false">AVERAGE(B9:M9)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="I10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="J10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="K10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="L10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="M10" s="31" t="n">
+        <f aca="false">Assumptions!$B$32</f>
+        <v>198</v>
+      </c>
+      <c r="N10" s="31" t="n">
+        <f aca="false">SUM(B10:M10)</f>
+        <v>2376</v>
+      </c>
+      <c r="O10" s="31" t="n">
+        <f aca="false">AVERAGE(B10:M10)</f>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,1&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>334</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,2&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>334</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,3&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,4&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,5&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,6&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,7&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,8&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,9&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,10&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,11&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$37=0,12&lt;=Assumptions!$B$37),Assumptions!$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="31" t="n">
+        <f aca="false">SUM(B11:M11)</f>
+        <v>668</v>
+      </c>
+      <c r="O11" s="31" t="n">
+        <f aca="false">AVERAGE(B11:M11)</f>
+        <v>55.6666666666667</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,1&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>499</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,2&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>499</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,3&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,4&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,5&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,6&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,7&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,8&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,9&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,10&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,11&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$38=0,12&lt;=Assumptions!$B$38),Assumptions!$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="31" t="n">
+        <f aca="false">SUM(B12:M12)</f>
+        <v>998</v>
+      </c>
+      <c r="O12" s="31" t="n">
+        <f aca="false">AVERAGE(B12:M12)</f>
+        <v>83.1666666666667</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="31" t="n">
+        <f aca="false">IF(1&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>400</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <f aca="false">IF(2&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <f aca="false">IF(3&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <f aca="false">IF(4&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <f aca="false">IF(5&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <f aca="false">IF(6&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <f aca="false">IF(7&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <f aca="false">IF(8&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="31" t="n">
+        <f aca="false">IF(9&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="31" t="n">
+        <f aca="false">IF(10&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="31" t="n">
+        <f aca="false">IF(11&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="31" t="n">
+        <f aca="false">IF(12&lt;Assumptions!$B$25,Assumptions!$B$36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="31" t="n">
+        <f aca="false">SUM(B13:M13)</f>
+        <v>400</v>
+      </c>
+      <c r="O13" s="31" t="n">
+        <f aca="false">AVERAGE(B13:M13)</f>
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="G14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="H14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="I14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="J14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="K14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="L14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="M14" s="31" t="n">
+        <f aca="false">Assumptions!$B$41</f>
+        <v>1200</v>
+      </c>
+      <c r="N14" s="31" t="n">
+        <f aca="false">SUM(B14:M14)</f>
+        <v>14400</v>
+      </c>
+      <c r="O14" s="31" t="n">
+        <f aca="false">AVERAGE(B14:M14)</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="H15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="J15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="K15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="L15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="M15" s="31" t="n">
+        <f aca="false">Assumptions!$B$42</f>
+        <v>250</v>
+      </c>
+      <c r="N15" s="31" t="n">
+        <f aca="false">SUM(B15:M15)</f>
+        <v>3000</v>
+      </c>
+      <c r="O15" s="31" t="n">
+        <f aca="false">AVERAGE(B15:M15)</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="J16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="K16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="L16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>350</v>
+      </c>
+      <c r="N16" s="31" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>4200</v>
+      </c>
+      <c r="O16" s="31" t="n">
+        <f aca="false">AVERAGE(B16:M16)</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="H17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="I17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="J17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="K17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>100</v>
+      </c>
+      <c r="N17" s="31" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>1200</v>
+      </c>
+      <c r="O17" s="31" t="n">
+        <f aca="false">AVERAGE(B17:M17)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="H18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="I18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="J18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="K18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="L18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>300</v>
+      </c>
+      <c r="N18" s="31" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>3600</v>
+      </c>
+      <c r="O18" s="31" t="n">
+        <f aca="false">AVERAGE(B18:M18)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="I19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="J19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="K19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="L19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="M19" s="31" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>320</v>
+      </c>
+      <c r="N19" s="31" t="n">
+        <f aca="false">SUM(B19:M19)</f>
+        <v>3840</v>
+      </c>
+      <c r="O19" s="31" t="n">
+        <f aca="false">AVERAGE(B19:M19)</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="C20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="F20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="G20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="H20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="I20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="J20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="K20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="L20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="M20" s="31" t="n">
+        <f aca="false">Assumptions!$B$47</f>
+        <v>1083</v>
+      </c>
+      <c r="N20" s="31" t="n">
+        <f aca="false">SUM(B20:M20)</f>
+        <v>12996</v>
+      </c>
+      <c r="O20" s="31" t="n">
+        <f aca="false">AVERAGE(B20:M20)</f>
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="B21" s="43" t="n">
+        <f aca="false">SUM(B5:B20)</f>
+        <v>9667</v>
+      </c>
+      <c r="C21" s="43" t="n">
+        <f aca="false">SUM(C5:C20)</f>
+        <v>20267</v>
+      </c>
+      <c r="D21" s="43" t="n">
+        <f aca="false">SUM(D5:D20)</f>
+        <v>8034</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <f aca="false">SUM(E5:E20)</f>
+        <v>8034</v>
+      </c>
+      <c r="F21" s="43" t="n">
+        <f aca="false">SUM(F5:F20)</f>
+        <v>8034</v>
+      </c>
+      <c r="G21" s="43" t="n">
+        <f aca="false">SUM(G5:G20)</f>
+        <v>8034</v>
+      </c>
+      <c r="H21" s="43" t="n">
+        <f aca="false">SUM(H5:H20)</f>
+        <v>8034</v>
+      </c>
+      <c r="I21" s="43" t="n">
+        <f aca="false">SUM(I5:I20)</f>
+        <v>8034</v>
+      </c>
+      <c r="J21" s="43" t="n">
+        <f aca="false">SUM(J5:J20)</f>
+        <v>8034</v>
+      </c>
+      <c r="K21" s="43" t="n">
+        <f aca="false">SUM(K5:K20)</f>
+        <v>8034</v>
+      </c>
+      <c r="L21" s="43" t="n">
+        <f aca="false">SUM(L5:L20)</f>
+        <v>8034</v>
+      </c>
+      <c r="M21" s="43" t="n">
+        <f aca="false">SUM(M5:M20)</f>
+        <v>8034</v>
+      </c>
+      <c r="N21" s="43" t="n">
+        <f aca="false">SUM(B21:M21)</f>
+        <v>110274</v>
+      </c>
+      <c r="O21" s="43" t="n">
+        <f aca="false">AVERAGE(B21:M21)</f>
+        <v>9189.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="2" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="N4" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" s="19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="31" t="n">
+        <f aca="false">Forecast!B6</f>
+        <v>1500</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <f aca="false">Forecast!C6</f>
+        <v>3000</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <f aca="false">Forecast!D6</f>
+        <v>3000</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <f aca="false">Forecast!E6</f>
+        <v>3000</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <f aca="false">Forecast!F6</f>
+        <v>3000</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <f aca="false">Forecast!G6</f>
+        <v>3000</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <f aca="false">Forecast!H6</f>
+        <v>3000</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <f aca="false">Forecast!I6</f>
+        <v>3000</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <f aca="false">Forecast!J6</f>
+        <v>3000</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <f aca="false">Forecast!K6</f>
+        <v>3000</v>
+      </c>
+      <c r="L6" s="31" t="n">
+        <f aca="false">Forecast!L6</f>
+        <v>3000</v>
+      </c>
+      <c r="M6" s="31" t="n">
+        <f aca="false">Forecast!M6</f>
+        <v>3000</v>
+      </c>
+      <c r="N6" s="31" t="n">
+        <f aca="false">SUM(B6:M6)</f>
+        <v>34500</v>
+      </c>
+      <c r="O6" s="31" t="n">
+        <f aca="false">AVERAGE(B6:M6)</f>
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="31" t="n">
+        <f aca="false">Forecast!B7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <f aca="false">Forecast!C7</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <f aca="false">Forecast!D7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <f aca="false">Forecast!E7</f>
+        <v>3000</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <f aca="false">Forecast!F7</f>
+        <v>3000</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <f aca="false">Forecast!G7</f>
+        <v>3000</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <f aca="false">Forecast!H7</f>
+        <v>3000</v>
+      </c>
+      <c r="I7" s="31" t="n">
+        <f aca="false">Forecast!I7</f>
+        <v>3000</v>
+      </c>
+      <c r="J7" s="31" t="n">
+        <f aca="false">Forecast!J7</f>
+        <v>3000</v>
+      </c>
+      <c r="K7" s="31" t="n">
+        <f aca="false">Forecast!K7</f>
+        <v>3000</v>
+      </c>
+      <c r="L7" s="31" t="n">
+        <f aca="false">Forecast!L7</f>
+        <v>3000</v>
+      </c>
+      <c r="M7" s="31" t="n">
+        <f aca="false">Forecast!M7</f>
+        <v>3000</v>
+      </c>
+      <c r="N7" s="31" t="n">
+        <f aca="false">SUM(B7:M7)</f>
+        <v>27000</v>
+      </c>
+      <c r="O7" s="31" t="n">
+        <f aca="false">AVERAGE(B7:M7)</f>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="31" t="n">
+        <f aca="false">Forecast!B8</f>
+        <v>2000</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <f aca="false">Forecast!C8</f>
+        <v>2000</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <f aca="false">Forecast!D8</f>
+        <v>2000</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <f aca="false">Forecast!E8</f>
+        <v>2000</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <f aca="false">Forecast!F8</f>
+        <v>2000</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <f aca="false">Forecast!G8</f>
+        <v>2000</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <f aca="false">Forecast!H8</f>
+        <v>2000</v>
+      </c>
+      <c r="I8" s="31" t="n">
+        <f aca="false">Forecast!I8</f>
+        <v>2000</v>
+      </c>
+      <c r="J8" s="31" t="n">
+        <f aca="false">Forecast!J8</f>
+        <v>2000</v>
+      </c>
+      <c r="K8" s="31" t="n">
+        <f aca="false">Forecast!K8</f>
+        <v>2000</v>
+      </c>
+      <c r="L8" s="31" t="n">
+        <f aca="false">Forecast!L8</f>
+        <v>2000</v>
+      </c>
+      <c r="M8" s="31" t="n">
+        <f aca="false">Forecast!M8</f>
+        <v>2000</v>
+      </c>
+      <c r="N8" s="31" t="n">
+        <f aca="false">SUM(B8:M8)</f>
+        <v>24000</v>
+      </c>
+      <c r="O8" s="31" t="n">
+        <f aca="false">AVERAGE(B8:M8)</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="33" t="n">
+        <f aca="false">SUM(B6:B8)</f>
+        <v>3500</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <f aca="false">SUM(C6:C8)</f>
+        <v>5000</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <f aca="false">SUM(D6:D8)</f>
+        <v>5000</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <f aca="false">SUM(E6:E8)</f>
+        <v>8000</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <f aca="false">SUM(F6:F8)</f>
+        <v>8000</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <f aca="false">SUM(G6:G8)</f>
+        <v>8000</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <f aca="false">SUM(H6:H8)</f>
+        <v>8000</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <f aca="false">SUM(I6:I8)</f>
+        <v>8000</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <f aca="false">SUM(J6:J8)</f>
+        <v>8000</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <f aca="false">SUM(K6:K8)</f>
+        <v>8000</v>
+      </c>
+      <c r="L9" s="33" t="n">
+        <f aca="false">SUM(L6:L8)</f>
+        <v>8000</v>
+      </c>
+      <c r="M9" s="33" t="n">
+        <f aca="false">SUM(M6:M8)</f>
+        <v>8000</v>
+      </c>
+      <c r="N9" s="33" t="n">
+        <f aca="false">SUM(B9:M9)</f>
+        <v>85500</v>
+      </c>
+      <c r="O9" s="33" t="n">
+        <f aca="false">AVERAGE(B9:M9)</f>
+        <v>7125</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="B12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="J12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="K12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="L12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <f aca="false">Assumptions!$B$52</f>
+        <v>100</v>
+      </c>
+      <c r="N12" s="31" t="n">
+        <f aca="false">SUM(B12:M12)</f>
+        <v>1200</v>
+      </c>
+      <c r="O12" s="31" t="n">
+        <f aca="false">AVERAGE(B12:M12)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="J13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="K13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="L13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="M13" s="31" t="n">
+        <f aca="false">Assumptions!$B$53</f>
+        <v>20</v>
+      </c>
+      <c r="N13" s="31" t="n">
+        <f aca="false">SUM(B13:M13)</f>
+        <v>240</v>
+      </c>
+      <c r="O13" s="31" t="n">
+        <f aca="false">AVERAGE(B13:M13)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="G14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="H14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="I14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="J14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="K14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="L14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="M14" s="31" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>100</v>
+      </c>
+      <c r="N14" s="31" t="n">
+        <f aca="false">SUM(B14:M14)</f>
+        <v>1200</v>
+      </c>
+      <c r="O14" s="31" t="n">
+        <f aca="false">AVERAGE(B14:M14)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="H15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="J15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="K15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="L15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="M15" s="31" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>27</v>
+      </c>
+      <c r="N15" s="31" t="n">
+        <f aca="false">SUM(B15:M15)</f>
+        <v>324</v>
+      </c>
+      <c r="O15" s="31" t="n">
+        <f aca="false">AVERAGE(B15:M15)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="J16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="K16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="L16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>125</v>
+      </c>
+      <c r="N16" s="31" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>1500</v>
+      </c>
+      <c r="O16" s="31" t="n">
+        <f aca="false">AVERAGE(B16:M16)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="H17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="I17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="J17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="K17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>75</v>
+      </c>
+      <c r="N17" s="31" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>900</v>
+      </c>
+      <c r="O17" s="31" t="n">
+        <f aca="false">AVERAGE(B17:M17)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="H18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="I18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="J18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="K18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="L18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>50</v>
+      </c>
+      <c r="N18" s="31" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>600</v>
+      </c>
+      <c r="O18" s="31" t="n">
+        <f aca="false">AVERAGE(B18:M18)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="B19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="I19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="J19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="K19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="L19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="M19" s="31" t="n">
+        <f aca="false">Assumptions!$B$59/12</f>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="N19" s="31" t="n">
+        <f aca="false">SUM(B19:M19)</f>
+        <v>350</v>
+      </c>
+      <c r="O19" s="31" t="n">
+        <f aca="false">AVERAGE(B19:M19)</f>
+        <v>29.1666666666667</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="43" t="n">
+        <f aca="false">SUM(B12:B19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="C20" s="43" t="n">
+        <f aca="false">SUM(C12:C19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="D20" s="43" t="n">
+        <f aca="false">SUM(D12:D19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="E20" s="43" t="n">
+        <f aca="false">SUM(E12:E19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="F20" s="43" t="n">
+        <f aca="false">SUM(F12:F19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="G20" s="43" t="n">
+        <f aca="false">SUM(G12:G19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="H20" s="43" t="n">
+        <f aca="false">SUM(H12:H19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="I20" s="43" t="n">
+        <f aca="false">SUM(I12:I19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="J20" s="43" t="n">
+        <f aca="false">SUM(J12:J19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="K20" s="43" t="n">
+        <f aca="false">SUM(K12:K19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="L20" s="43" t="n">
+        <f aca="false">SUM(L12:L19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="M20" s="43" t="n">
+        <f aca="false">SUM(M12:M19)</f>
+        <v>526.166666666667</v>
+      </c>
+      <c r="N20" s="43" t="n">
+        <f aca="false">SUM(B20:M20)</f>
+        <v>6314</v>
+      </c>
+      <c r="O20" s="43" t="n">
+        <f aca="false">AVERAGE(B20:M20)</f>
+        <v>526.166666666667</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" s="33" t="n">
+        <f aca="false">B9-B20</f>
+        <v>2973.83333333333</v>
+      </c>
+      <c r="C22" s="33" t="n">
+        <f aca="false">C9-C20</f>
+        <v>4473.83333333333</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <f aca="false">D9-D20</f>
+        <v>4473.83333333333</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <f aca="false">E9-E20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="F22" s="33" t="n">
+        <f aca="false">F9-F20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="G22" s="33" t="n">
+        <f aca="false">G9-G20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="H22" s="33" t="n">
+        <f aca="false">H9-H20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="I22" s="33" t="n">
+        <f aca="false">I9-I20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="J22" s="33" t="n">
+        <f aca="false">J9-J20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="K22" s="33" t="n">
+        <f aca="false">K9-K20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="L22" s="33" t="n">
+        <f aca="false">L9-L20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="M22" s="33" t="n">
+        <f aca="false">M9-M20</f>
+        <v>7473.83333333333</v>
+      </c>
+      <c r="N22" s="33" t="n">
+        <f aca="false">SUM(B22:M22)</f>
+        <v>79186</v>
+      </c>
+      <c r="O22" s="33" t="n">
+        <f aca="false">AVERAGE(B22:M22)</f>
+        <v>6598.83333333333</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="B24" s="44" t="n">
+        <f aca="false">IFERROR(B22/B9,0)</f>
+        <v>0.849666666666667</v>
+      </c>
+      <c r="C24" s="44" t="n">
+        <f aca="false">IFERROR(C22/C9,0)</f>
+        <v>0.894766666666667</v>
+      </c>
+      <c r="D24" s="44" t="n">
+        <f aca="false">IFERROR(D22/D9,0)</f>
+        <v>0.894766666666667</v>
+      </c>
+      <c r="E24" s="44" t="n">
+        <f aca="false">IFERROR(E22/E9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="F24" s="44" t="n">
+        <f aca="false">IFERROR(F22/F9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="G24" s="44" t="n">
+        <f aca="false">IFERROR(G22/G9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="H24" s="44" t="n">
+        <f aca="false">IFERROR(H22/H9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="I24" s="44" t="n">
+        <f aca="false">IFERROR(I22/I9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="J24" s="44" t="n">
+        <f aca="false">IFERROR(J22/J9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="K24" s="44" t="n">
+        <f aca="false">IFERROR(K22/K9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="L24" s="44" t="n">
+        <f aca="false">IFERROR(L22/L9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="M24" s="44" t="n">
+        <f aca="false">IFERROR(M22/M9,0)</f>
+        <v>0.934229166666667</v>
+      </c>
+      <c r="N24" s="44" t="n">
+        <f aca="false">IFERROR(N22/N9,0)</f>
+        <v>0.926152046783626</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A31:O31"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="31" t="n">
+        <f aca="false">Assumptions!$B$48</f>
+        <v>11000</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <f aca="false">B12</f>
+        <v>14064.0285076667</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <f aca="false">C12</f>
+        <v>48028.0570153333</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <f aca="false">D12</f>
+        <v>52725.085523</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <f aca="false">E12</f>
+        <v>57422.1140306667</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <f aca="false">F12</f>
+        <v>62119.1425383334</v>
+      </c>
+      <c r="H5" s="31" t="n">
+        <f aca="false">G12</f>
+        <v>66816.171046</v>
+      </c>
+      <c r="I5" s="31" t="n">
+        <f aca="false">H12</f>
+        <v>71513.1995536667</v>
+      </c>
+      <c r="J5" s="31" t="n">
+        <f aca="false">I12</f>
+        <v>76210.2280613333</v>
+      </c>
+      <c r="K5" s="31" t="n">
+        <f aca="false">J12</f>
+        <v>80907.256569</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <f aca="false">K12</f>
+        <v>85604.2850766667</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <f aca="false">L12</f>
+        <v>90301.3135843333</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="L6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+      <c r="M6" s="31" t="n">
+        <f aca="false">Taxes!$B$43</f>
+        <v>13257.1951743333</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!B21</f>
+        <v>-9667</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!C21</f>
+        <v>-20267</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!D21</f>
+        <v>-8034</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!E21</f>
+        <v>-8034</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!F21</f>
+        <v>-8034</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!G21</f>
+        <v>-8034</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!H21</f>
+        <v>-8034</v>
+      </c>
+      <c r="I7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!I21</f>
+        <v>-8034</v>
+      </c>
+      <c r="J7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!J21</f>
+        <v>-8034</v>
+      </c>
+      <c r="K7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!K21</f>
+        <v>-8034</v>
+      </c>
+      <c r="L7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!L21</f>
+        <v>-8034</v>
+      </c>
+      <c r="M7" s="31" t="n">
+        <f aca="false">-'Personal Expenses'!M21</f>
+        <v>-8034</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!B20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!C20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!D20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!E20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!F20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!G20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!H20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="I8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!I20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="J8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!J20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="K8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!K20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="L8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!L20</f>
+        <v>-526.166666666667</v>
+      </c>
+      <c r="M8" s="31" t="n">
+        <f aca="false">-'Framework OPS P&amp;L'!M20</f>
+        <v>-526.166666666667</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="31" t="n">
+        <f aca="false">IF(1=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <f aca="false">IF(2=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>95000</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <f aca="false">IF(3=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <f aca="false">IF(4=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <f aca="false">IF(5=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <f aca="false">IF(6=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <f aca="false">IF(7=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="31" t="n">
+        <f aca="false">IF(8=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="31" t="n">
+        <f aca="false">IF(9=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="31" t="n">
+        <f aca="false">IF(10=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="31" t="n">
+        <f aca="false">IF(11=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="31" t="n">
+        <f aca="false">IF(12=Assumptions!$B$25,Assumptions!$B$27,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="31" t="n">
+        <f aca="false">-(IF(1=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,1=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,1=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <f aca="false">-(IF(2=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,2=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,2=Assumptions!$B$38),24500,0))</f>
+        <v>-53500</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <f aca="false">-(IF(3=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,3=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,3=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <f aca="false">-(IF(4=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,4=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,4=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <f aca="false">-(IF(5=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,5=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,5=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <f aca="false">-(IF(6=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,6=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,6=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <f aca="false">-(IF(7=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,7=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,7=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="I10" s="31" t="n">
+        <f aca="false">-(IF(8=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,8=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,8=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="J10" s="31" t="n">
+        <f aca="false">-(IF(9=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,9=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,9=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="K10" s="31" t="n">
+        <f aca="false">-(IF(10=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,10=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,10=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="L10" s="31" t="n">
+        <f aca="false">-(IF(11=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,11=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,11=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+      <c r="M10" s="31" t="n">
+        <f aca="false">-(IF(12=Assumptions!$B$25,Assumptions!$B$35,0)+IF(AND(Assumptions!$B$37&gt;0,12=Assumptions!$B$37),13000,0)+IF(AND(Assumptions!$B$38&gt;0,12=Assumptions!$B$38),24500,0))</f>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="46" t="n">
+        <f aca="false">SUM(B6:B10)</f>
+        <v>3064.02850766667</v>
+      </c>
+      <c r="C11" s="46" t="n">
+        <f aca="false">SUM(C6:C10)</f>
+        <v>33964.0285076667</v>
+      </c>
+      <c r="D11" s="46" t="n">
+        <f aca="false">SUM(D6:D10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="E11" s="46" t="n">
+        <f aca="false">SUM(E6:E10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="F11" s="46" t="n">
+        <f aca="false">SUM(F6:F10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <f aca="false">SUM(G6:G10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="H11" s="46" t="n">
+        <f aca="false">SUM(H6:H10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <f aca="false">SUM(I6:I10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <f aca="false">SUM(J6:J10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="K11" s="46" t="n">
+        <f aca="false">SUM(K6:K10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="L11" s="46" t="n">
+        <f aca="false">SUM(L6:L10)</f>
+        <v>4697.02850766667</v>
+      </c>
+      <c r="M11" s="46" t="n">
+        <f aca="false">SUM(M6:M10)</f>
+        <v>4697.02850766667</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="33" t="n">
+        <f aca="false">B5+B11</f>
+        <v>14064.0285076667</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <f aca="false">C5+C11</f>
+        <v>48028.0570153333</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <f aca="false">D5+D11</f>
+        <v>52725.085523</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <f aca="false">E5+E11</f>
+        <v>57422.1140306667</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <f aca="false">F5+F11</f>
+        <v>62119.1425383334</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <f aca="false">G5+G11</f>
+        <v>66816.171046</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <f aca="false">H5+H11</f>
+        <v>71513.1995536667</v>
+      </c>
+      <c r="I12" s="33" t="n">
+        <f aca="false">I5+I11</f>
+        <v>76210.2280613333</v>
+      </c>
+      <c r="J12" s="33" t="n">
+        <f aca="false">J5+J11</f>
+        <v>80907.256569</v>
+      </c>
+      <c r="K12" s="33" t="n">
+        <f aca="false">K5+K11</f>
+        <v>85604.2850766667</v>
+      </c>
+      <c r="L12" s="33" t="n">
+        <f aca="false">L5+L11</f>
+        <v>90301.3135843333</v>
+      </c>
+      <c r="M12" s="33" t="n">
+        <f aca="false">M5+M11</f>
+        <v>94998.342092</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A18:M18"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="47" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C5" s="47" t="n">
+        <v>400</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="47" t="n">
+        <v>24500</v>
+      </c>
+      <c r="C6" s="47" t="n">
+        <v>499</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="47" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C7" s="47" t="n">
+        <v>334</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="47" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C8" s="47" t="n">
+        <v>198</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B9" s="47" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C9" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="48" t="n">
+        <f aca="false">SUM(B5:B9)</f>
+        <v>68000</v>
+      </c>
+      <c r="C10" s="48" t="n">
+        <f aca="false">SUM(C5:C9)</f>
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="31" t="n">
+        <v>106000</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="31" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">C14+B15</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <f aca="false">C15+B16</f>
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>-6400</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <f aca="false">C16+B17</f>
+        <v>78600</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B18" s="31" t="n">
+        <v>-24500</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <f aca="false">C17+B18</f>
+        <v>54100</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <f aca="false">C18+B19</f>
+        <v>41100</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B20" s="46" t="n">
+        <f aca="false">C19</f>
+        <v>41100</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <f aca="false">C19</f>
+        <v>41100</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/income_forecaster.xlsx
+++ b/income_forecaster.xlsx
@@ -17,6 +17,8 @@
     <sheet name="Cash Roll-Forward" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Debt Strategy" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="3-Year Growth" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Pipeline &amp; Capacity" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Leverage Scenarios" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="521">
   <si>
     <t xml:space="preserve">Income Forecaster — Chance Peare</t>
   </si>
@@ -1207,13 +1209,397 @@
   </si>
   <si>
     <t xml:space="preserve">• Solo 401(k) on $1099 income should be in place by Y2 — biggest tax lever, not yet modeled in the 3-yr view.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipeline Funnel + Capacity Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pessimistic conversion rates. Touchpoint and hour estimates per stage. Calculates pipeline needed to hit revenue targets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONVERSION FUNNEL (per closed deal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conv %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm/Ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hrs/stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold contacts (top of funnel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List building + outreach send. 1-2 min/contact = ~6 hrs to send 200.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replies / responses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% cold reply rate (pessimistic; benchmark 5-15%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery calls held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35% of replies convert to call. Call (60min) + prep (30min) + follow-up (30min).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid diagnostics ($997)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55% of discovery → diagnostic. Intake review + 90-min session + doc review + memo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposals sent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75% of diagnostics → proposal. Build (with templates) + walkthrough call.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signed retainers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35% close rate (CLAUDE.md). Negotiation + agreement + onboarding kick.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOURS PER CLOSED DEAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold path total hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold-path: ~65-80 hrs per close (most time spent on diagnostics and disco calls)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm path total hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm path more efficient — less prospecting needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNUAL SALES TIME (to hit close targets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target closes/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended (50/50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hrs/wk equiv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITY MODEL (hours available per month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working hours/week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realistic FT week including ops.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working weeks/year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less 4 wks PTO/holiday/sick.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total hours/year (FT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computed FT capacity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-Active-retainer hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3K retainer = 15-20 hrs/mo realistic delivery + comms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-Embedded-retainer hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$6K embedded ~30-40 hrs/mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ops/admin/finance hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bookkeeping, billing, scheduling, CRM. = 8 hrs/wk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing/content hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn, newsletter, content. = 5 hrs/wk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITY UNDER DIFFERENT STAFFING MODELS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FW Ops hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Active retainers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo + Skyright COO (Y1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 active is the ceiling per CLAUDE.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo full-time (post-Skyright)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo FT ceiling. Match to capacity flag in 3-Year Growth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo FT + Mid-tier VA ($24K/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA handles outreach + admin + template population. Frees ~30 hrs/mo for delivery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo FT + Executive VA ($48K/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exec VA does light deliverable work + sales support. Frees ~50 hrs/mo for delivery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo FT + US Ops Associate ($79K/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US Associate can do client-facing prep + deliverables + sales support. ~70 hrs/mo freed for delivery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEY TAKEAWAYS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Cold pipeline math: 1 close requires ~200 cold contacts + ~70 hrs of sales work. To close 3-4 retainers/yr cold = 4-5 hrs/wk of sales motion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Warm/referral path is 2.5x more efficient: 1 close from ~60 warm intros + ~50 hrs. Referrals are the lever.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Solo + Skyright Y1 capacity = 3 active retainers. Matches roster in 3-Year Growth tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Solo FT capacity = ~5 active retainers. This is the binding constraint without leverage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Mid VA unlocks +1-2 retainers IF you actually close them. Adds $24-29K loaded cost. Pays for itself at ~2 retainers freed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Exec VA unlocks +2-3 retainers at $48-55K loaded. Higher capacity but higher fixed cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• US Ops Associate unlocks +3-4 retainers at $79-99K loaded. Doesn't pencil until revenue passes ~$320K.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Most fractional COOs over-staff before they over-sell. Build pipeline first, hire after — not before.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leverage Scenarios — Solo vs VA vs US Associate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compares net income across staffing modes at four revenue levels. Net = Revenue − Staffing Cost − OpEx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COST ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid VA monthly cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH/LatAm mid-tier. $18-25/hr × 80-100 hrs/mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid VA mgmt overhead/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your time managing them. ~5-8 hrs/mo at $50/hr opportunity cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exec VA monthly cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LatAm senior. $30-40/hr × 100-130 hrs/mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exec VA mgmt overhead/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less mgmt needed but still real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior US Assoc monthly (loaded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$66K base × 1.20 payroll/benefits = $79K/12.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior US Assoc mgmt overhead/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onboarding-heavy first year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid US Assoc monthly (loaded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$78K base × 1.20 = $94K/12.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid US Assoc mgmt overhead/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Framework OPS OpEx (mature)/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y3 OpEx level from 3-Year Growth tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO MATRIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid VA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exec VA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jr Assoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid Assoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$180K (Y2 projected)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$230K (Y3 likely)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$280K (mature)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$350K (stretch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCREMENTAL VALUE vs SOLO (at each revenue level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid VA Δ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exec VA Δ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jr Assoc Δ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid Assoc Δ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREAK-EVEN ANALYSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual Loaded Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incremental Revenue to Break Even</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retainers Needed (at $3K/mo avg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jr US Associate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid US Associate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECOMMENDED SEQUENCING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 1 (now → Q1-27, while at Skyright): SOLO. Bottleneck is pipeline, not delivery. Build SOPs and template library. No hires.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 2 (Q2-27 → Q4-27, Skyright ending): MID VA at $2K/mo. Deploy on outreach + admin + follow-ups. Highest leverage period — every hour matters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 3 (Y3 if revenue &gt; $200K with 4+ retainers): UPGRADE to Exec VA OR add second Mid VA. Splits admin / deliverables / sales ops.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4 (Y4+ only if revenue trends &gt; $300K): JR US ASSOCIATE. By then VA stack is mature. Associate becomes the strategy/sales support layer, not admin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 5 (Y5+ if revenue &gt; $400K): Mid Associate + 2 VAs. At this point you are running an agency, not a fractional COO practice. Different business model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHAT BREAKS THIS MODEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Assumes incremental capacity converts to incremental revenue. If pipeline is the bottleneck, capacity goes idle and these numbers all overstate value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• VA mgmt overhead is conservative. First 90 days, plan for 2-3x the overhead listed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• "Capacity" assumes existing client churn replacement is humming. If you spend freed hours backfilling churned clients, no growth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Quality risk on VA-produced deliverables: a single client losing confidence in deliverable quality can cost you $36K (1 churned $3K retainer). Spec quality bar high.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• US Associate at $79K + 20% load assumes no equity, no bonus, no real benefits. If you offer health, add $500-1,500/mo. If you offer equity, the $79K becomes a cap, not a starting point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• None of these models add a sales hire. If you want &gt; $400K, the next hire is probably a part-time SDR, not another Ops person.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -1221,10 +1607,11 @@
     <numFmt numFmtId="168" formatCode="\$#,##0"/>
     <numFmt numFmtId="169" formatCode="0.00%"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1314,8 +1701,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1358,6 +1751,12 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
@@ -1393,7 +1792,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1554,6 +1953,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1562,11 +1977,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1574,15 +2005,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1590,15 +2013,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="173" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2447,6 +2874,1427 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="46" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="C6" s="47" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" s="48" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" s="48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B7" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="51" t="n">
+        <f aca="false">C6*B7</f>
+        <v>20</v>
+      </c>
+      <c r="D7" s="52" t="n">
+        <f aca="false">D6*0.25</f>
+        <v>15</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="B8" s="50" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C8" s="51" t="n">
+        <f aca="false">C7*B8</f>
+        <v>7</v>
+      </c>
+      <c r="D8" s="52" t="n">
+        <f aca="false">D7*0.45</f>
+        <v>6.75</v>
+      </c>
+      <c r="E8" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B9" s="50" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C9" s="51" t="n">
+        <f aca="false">C8*B9</f>
+        <v>3.85</v>
+      </c>
+      <c r="D9" s="52" t="n">
+        <f aca="false">D8*0.6</f>
+        <v>4.05</v>
+      </c>
+      <c r="E9" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B10" s="50" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C10" s="51" t="n">
+        <f aca="false">C9*B10</f>
+        <v>2.8875</v>
+      </c>
+      <c r="D10" s="52" t="n">
+        <f aca="false">D9*0.8</f>
+        <v>3.24</v>
+      </c>
+      <c r="E10" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="B11" s="50" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C11" s="51" t="n">
+        <f aca="false">C10*B11</f>
+        <v>1.010625</v>
+      </c>
+      <c r="D11" s="52" t="n">
+        <f aca="false">D10*0.4</f>
+        <v>1.296</v>
+      </c>
+      <c r="E11" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="46" t="s">
+        <v>414</v>
+      </c>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B14" s="53" t="n">
+        <f aca="false">6+(C7*E7)+(C8*E8)+(C9*E9)+(C10*E10)+(C11*E11)</f>
+        <v>57.681875</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B15" s="53" t="n">
+        <f aca="false">3+(D7*E7)+(D8*E8)+(D9*E9)+(D10*E10)+(D11*E11)</f>
+        <v>57.648</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="46" t="s">
+        <v>419</v>
+      </c>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="54" t="n">
+        <f aca="false">2*B14</f>
+        <v>115.36375</v>
+      </c>
+      <c r="C19" s="54" t="n">
+        <f aca="false">2*B15</f>
+        <v>115.296</v>
+      </c>
+      <c r="D19" s="54" t="n">
+        <f aca="false">AVERAGE(B19:C19)</f>
+        <v>115.329875</v>
+      </c>
+      <c r="E19" s="52" t="n">
+        <f aca="false">D19/48</f>
+        <v>2.40270572916667</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="54" t="n">
+        <f aca="false">3*B14</f>
+        <v>173.045625</v>
+      </c>
+      <c r="C20" s="54" t="n">
+        <f aca="false">3*B15</f>
+        <v>172.944</v>
+      </c>
+      <c r="D20" s="54" t="n">
+        <f aca="false">AVERAGE(B20:C20)</f>
+        <v>172.9948125</v>
+      </c>
+      <c r="E20" s="52" t="n">
+        <f aca="false">D20/48</f>
+        <v>3.60405859375</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="54" t="n">
+        <f aca="false">4*B14</f>
+        <v>230.7275</v>
+      </c>
+      <c r="C21" s="54" t="n">
+        <f aca="false">4*B15</f>
+        <v>230.592</v>
+      </c>
+      <c r="D21" s="54" t="n">
+        <f aca="false">AVERAGE(B21:C21)</f>
+        <v>230.65975</v>
+      </c>
+      <c r="E21" s="52" t="n">
+        <f aca="false">D21/48</f>
+        <v>4.80541145833333</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="54" t="n">
+        <f aca="false">5*B14</f>
+        <v>288.409375</v>
+      </c>
+      <c r="C22" s="54" t="n">
+        <f aca="false">5*B15</f>
+        <v>288.24</v>
+      </c>
+      <c r="D22" s="54" t="n">
+        <f aca="false">AVERAGE(B22:C22)</f>
+        <v>288.3246875</v>
+      </c>
+      <c r="E22" s="52" t="n">
+        <f aca="false">D22/48</f>
+        <v>6.00676432291667</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="54" t="n">
+        <f aca="false">6*B14</f>
+        <v>346.09125</v>
+      </c>
+      <c r="C23" s="54" t="n">
+        <f aca="false">6*B15</f>
+        <v>345.888</v>
+      </c>
+      <c r="D23" s="54" t="n">
+        <f aca="false">AVERAGE(B23:C23)</f>
+        <v>345.989625</v>
+      </c>
+      <c r="E23" s="52" t="n">
+        <f aca="false">D23/48</f>
+        <v>7.2081171875</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="46" t="s">
+        <v>425</v>
+      </c>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B26" s="47" t="n">
+        <v>45</v>
+      </c>
+      <c r="F26" s="49" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B27" s="47" t="n">
+        <v>48</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B28" s="51" t="n">
+        <f aca="false">B26*B27</f>
+        <v>2160</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B29" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="F29" s="49" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="B30" s="47" t="n">
+        <v>35</v>
+      </c>
+      <c r="F30" s="49" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="B31" s="47" t="n">
+        <v>32</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B32" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B36" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="C36" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" s="54" t="n">
+        <f aca="false">B36-C36-15-5</f>
+        <v>20</v>
+      </c>
+      <c r="E36" s="54" t="n">
+        <f aca="false">ROUNDDOWN(D36/B29,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="B37" s="54" t="n">
+        <f aca="false">B28/12</f>
+        <v>180</v>
+      </c>
+      <c r="C37" s="54" t="n">
+        <f aca="false">AVERAGE(D19:D22)/12</f>
+        <v>16.8189401041667</v>
+      </c>
+      <c r="D37" s="54" t="n">
+        <f aca="false">B37-C37-B31-B32</f>
+        <v>111.181059895833</v>
+      </c>
+      <c r="E37" s="54" t="n">
+        <f aca="false">ROUNDDOWN(D37/B29,0)</f>
+        <v>6</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B38" s="54" t="n">
+        <f aca="false">B28/12</f>
+        <v>180</v>
+      </c>
+      <c r="C38" s="54" t="n">
+        <f aca="false">AVERAGE(D19:D22)/12*0.5</f>
+        <v>8.40947005208333</v>
+      </c>
+      <c r="D38" s="54" t="n">
+        <f aca="false">B38-C38-B31*0.3-B32*0.4</f>
+        <v>153.990529947917</v>
+      </c>
+      <c r="E38" s="54" t="n">
+        <f aca="false">ROUNDDOWN(D38/B29,0)</f>
+        <v>8</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B39" s="54" t="n">
+        <f aca="false">B28/12</f>
+        <v>180</v>
+      </c>
+      <c r="C39" s="54" t="n">
+        <f aca="false">AVERAGE(D19:D22)/12*0.35</f>
+        <v>5.88662903645833</v>
+      </c>
+      <c r="D39" s="54" t="n">
+        <f aca="false">B39-C39-B31*0.2-B32*0.3</f>
+        <v>161.713370963542</v>
+      </c>
+      <c r="E39" s="54" t="n">
+        <f aca="false">ROUNDDOWN(D39/B29,0)</f>
+        <v>8</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B40" s="54" t="n">
+        <f aca="false">B28/12</f>
+        <v>180</v>
+      </c>
+      <c r="C40" s="54" t="n">
+        <f aca="false">AVERAGE(D19:D22)/12*0.25</f>
+        <v>4.20473502604167</v>
+      </c>
+      <c r="D40" s="54" t="n">
+        <f aca="false">B40-C40-B31*0.15-B32*0.25</f>
+        <v>165.995264973958</v>
+      </c>
+      <c r="E40" s="54" t="n">
+        <f aca="false">ROUNDDOWN(D40/B29,0)</f>
+        <v>9</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="46" t="s">
+        <v>456</v>
+      </c>
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="27" t="s">
+        <v>457</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="27" t="s">
+        <v>458</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="27" t="s">
+        <v>461</v>
+      </c>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="27" t="s">
+        <v>462</v>
+      </c>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="27" t="s">
+        <v>463</v>
+      </c>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A50:F50"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" s="55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B6" s="55" t="n">
+        <v>400</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B8" s="55" t="n">
+        <v>600</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B9" s="55" t="n">
+        <v>6583</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B10" s="55" t="n">
+        <v>400</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="B11" s="55" t="n">
+        <v>7833</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="B12" s="55" t="n">
+        <v>400</v>
+      </c>
+      <c r="C12" s="49"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B13" s="55" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="46" t="s">
+        <v>485</v>
+      </c>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>487</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="B17" s="56" t="n">
+        <f aca="false">IF(180000&lt;=180000,180000-12*$B$13,"OVER CAP")</f>
+        <v>166800</v>
+      </c>
+      <c r="C17" s="56" t="n">
+        <f aca="false">IF(180000&lt;=252000,180000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
+        <v>138000</v>
+      </c>
+      <c r="D17" s="56" t="n">
+        <f aca="false">IF(180000&lt;=288000,180000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
+        <v>111600</v>
+      </c>
+      <c r="E17" s="56" t="n">
+        <f aca="false">IF(180000&lt;=324000,180000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
+        <v>83004</v>
+      </c>
+      <c r="F17" s="56" t="n">
+        <f aca="false">IF(180000&lt;=400000,180000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
+        <v>68004</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B18" s="56" t="str">
+        <f aca="false">IF(230000&lt;=180000,230000-12*$B$13,"OVER CAP")</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="C18" s="56" t="n">
+        <f aca="false">IF(230000&lt;=252000,230000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
+        <v>188000</v>
+      </c>
+      <c r="D18" s="56" t="n">
+        <f aca="false">IF(230000&lt;=288000,230000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
+        <v>161600</v>
+      </c>
+      <c r="E18" s="56" t="n">
+        <f aca="false">IF(230000&lt;=324000,230000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
+        <v>133004</v>
+      </c>
+      <c r="F18" s="56" t="n">
+        <f aca="false">IF(230000&lt;=400000,230000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
+        <v>118004</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B19" s="56" t="str">
+        <f aca="false">IF(280000&lt;=180000,280000-12*$B$13,"OVER CAP")</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="C19" s="56" t="str">
+        <f aca="false">IF(280000&lt;=252000,280000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="D19" s="56" t="n">
+        <f aca="false">IF(280000&lt;=288000,280000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
+        <v>211600</v>
+      </c>
+      <c r="E19" s="56" t="n">
+        <f aca="false">IF(280000&lt;=324000,280000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
+        <v>183004</v>
+      </c>
+      <c r="F19" s="56" t="n">
+        <f aca="false">IF(280000&lt;=400000,280000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
+        <v>168004</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="B20" s="56" t="str">
+        <f aca="false">IF(350000&lt;=180000,350000-12*$B$13,"OVER CAP")</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="C20" s="56" t="str">
+        <f aca="false">IF(350000&lt;=252000,350000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="D20" s="56" t="str">
+        <f aca="false">IF(350000&lt;=288000,350000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="E20" s="56" t="str">
+        <f aca="false">IF(350000&lt;=324000,350000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="F20" s="56" t="n">
+        <f aca="false">IF(350000&lt;=400000,350000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
+        <v>238004</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="46" t="s">
+        <v>496</v>
+      </c>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>487</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>497</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>498</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="B24" s="57" t="n">
+        <f aca="false">B17</f>
+        <v>166800</v>
+      </c>
+      <c r="C24" s="57" t="n">
+        <f aca="false">IFERROR(C17-B17, "")</f>
+        <v>-28800</v>
+      </c>
+      <c r="D24" s="57" t="n">
+        <f aca="false">IFERROR(D17-B17, "")</f>
+        <v>-55200</v>
+      </c>
+      <c r="E24" s="57" t="n">
+        <f aca="false">IFERROR(E17-B17, "")</f>
+        <v>-83796</v>
+      </c>
+      <c r="F24" s="57" t="n">
+        <f aca="false">IFERROR(F17-B17, "")</f>
+        <v>-98796</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B25" s="57" t="str">
+        <f aca="false">B18</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="C25" s="57" t="str">
+        <f aca="false">IFERROR(C18-B18, "")</f>
+        <v/>
+      </c>
+      <c r="D25" s="57" t="str">
+        <f aca="false">IFERROR(D18-B18, "")</f>
+        <v/>
+      </c>
+      <c r="E25" s="57" t="str">
+        <f aca="false">IFERROR(E18-B18, "")</f>
+        <v/>
+      </c>
+      <c r="F25" s="57" t="str">
+        <f aca="false">IFERROR(F18-B18, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B26" s="57" t="str">
+        <f aca="false">B19</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="C26" s="57" t="str">
+        <f aca="false">IFERROR(C19-B19, "")</f>
+        <v/>
+      </c>
+      <c r="D26" s="57" t="str">
+        <f aca="false">IFERROR(D19-B19, "")</f>
+        <v/>
+      </c>
+      <c r="E26" s="57" t="str">
+        <f aca="false">IFERROR(E19-B19, "")</f>
+        <v/>
+      </c>
+      <c r="F26" s="57" t="str">
+        <f aca="false">IFERROR(F19-B19, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="B27" s="57" t="str">
+        <f aca="false">B20</f>
+        <v>OVER CAP</v>
+      </c>
+      <c r="C27" s="57" t="str">
+        <f aca="false">IFERROR(C20-B20, "")</f>
+        <v/>
+      </c>
+      <c r="D27" s="57" t="str">
+        <f aca="false">IFERROR(D20-B20, "")</f>
+        <v/>
+      </c>
+      <c r="E27" s="57" t="str">
+        <f aca="false">IFERROR(E20-B20, "")</f>
+        <v/>
+      </c>
+      <c r="F27" s="57" t="str">
+        <f aca="false">IFERROR(F20-B20, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>503</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>504</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="B32" s="58" t="n">
+        <f aca="false">12*($B$5+$B$6)</f>
+        <v>28800</v>
+      </c>
+      <c r="C32" s="58" t="n">
+        <f aca="false">B32+600*ROUNDUP(B32/36000,0)</f>
+        <v>29400</v>
+      </c>
+      <c r="D32" s="52" t="n">
+        <f aca="false">ROUNDUP(B32/36000,1)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="B33" s="58" t="n">
+        <f aca="false">12*($B$7+$B$8)</f>
+        <v>55200</v>
+      </c>
+      <c r="C33" s="58" t="n">
+        <f aca="false">B33+600*ROUNDUP(B33/36000,0)</f>
+        <v>56400</v>
+      </c>
+      <c r="D33" s="52" t="n">
+        <f aca="false">ROUNDUP(B33/36000,1)</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="B34" s="58" t="n">
+        <f aca="false">12*($B$9+$B$10)</f>
+        <v>83796</v>
+      </c>
+      <c r="C34" s="58" t="n">
+        <f aca="false">B34+600*ROUNDUP(B34/36000,0)</f>
+        <v>85596</v>
+      </c>
+      <c r="D34" s="52" t="n">
+        <f aca="false">ROUNDUP(B34/36000,1)</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="B35" s="58" t="n">
+        <f aca="false">12*($B$11+$B$12)</f>
+        <v>98796</v>
+      </c>
+      <c r="C35" s="58" t="n">
+        <f aca="false">B35+600*ROUNDUP(B35/36000,0)</f>
+        <v>100596</v>
+      </c>
+      <c r="D35" s="52" t="n">
+        <f aca="false">ROUNDUP(B35/36000,1)</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="46" t="s">
+        <v>508</v>
+      </c>
+      <c r="B38" s="46"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="27" t="s">
+        <v>509</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="27" t="s">
+        <v>510</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="27" t="s">
+        <v>511</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="27" t="s">
+        <v>513</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="46" t="s">
+        <v>514</v>
+      </c>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="27" t="s">
+        <v>517</v>
+      </c>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="27" t="s">
+        <v>519</v>
+      </c>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A52:I52"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -8013,101 +9861,101 @@
   <dimension ref="A1:AS48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="38" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="43" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="38" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="43" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="41"/>
-      <c r="AM2" s="41"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="42" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="s">
         <v>320</v>
       </c>
       <c r="B4" s="30" t="s">
@@ -8227,2412 +10075,2412 @@
       <c r="AN4" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="AP4" s="43" t="s">
+      <c r="AP4" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="AQ4" s="43"/>
-      <c r="AR4" s="43"/>
-      <c r="AS4" s="43"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="AQ4" s="4"/>
+      <c r="AR4" s="4"/>
+      <c r="AS4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="G5" s="44" t="n">
+      <c r="G5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="H5" s="44" t="n">
+      <c r="H5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="I5" s="44" t="n">
+      <c r="I5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="J5" s="44" t="n">
+      <c r="J5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="K5" s="44" t="n">
+      <c r="K5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="L5" s="44" t="n">
+      <c r="L5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="M5" s="44" t="n">
+      <c r="M5" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="N5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="44" t="n">
+      <c r="N5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="18" t="n">
         <f aca="false">SUM(B5:M5)</f>
         <v>96000</v>
       </c>
-      <c r="AM5" s="44" t="n">
+      <c r="AM5" s="18" t="n">
         <f aca="false">SUM(N5:Y5)</f>
         <v>0</v>
       </c>
-      <c r="AN5" s="44" t="n">
+      <c r="AN5" s="18" t="n">
         <f aca="false">SUM(Z5:AK5)</f>
         <v>0</v>
       </c>
-      <c r="AP5" s="42" t="s">
+      <c r="AP5" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="AQ5" s="42" t="s">
+      <c r="AQ5" s="40" t="s">
         <v>349</v>
       </c>
-      <c r="AR5" s="42" t="s">
+      <c r="AR5" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="AS5" s="42" t="s">
+      <c r="AS5" s="40" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="18" t="n">
         <v>1500</v>
       </c>
-      <c r="C6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="44" t="n">
+      <c r="C6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="18" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>1500</v>
       </c>
-      <c r="AM6" s="44" t="n">
+      <c r="AM6" s="18" t="n">
         <f aca="false">SUM(N6:Y6)</f>
         <v>0</v>
       </c>
-      <c r="AN6" s="44" t="n">
+      <c r="AN6" s="18" t="n">
         <f aca="false">SUM(Z6:AK6)</f>
         <v>0</v>
       </c>
-      <c r="AP6" s="0" t="s">
+      <c r="AP6" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AQ6" s="44" t="n">
+      <c r="AQ6" s="18" t="n">
         <f aca="false">AL5</f>
         <v>96000</v>
       </c>
-      <c r="AR6" s="44" t="n">
+      <c r="AR6" s="18" t="n">
         <f aca="false">AM5</f>
         <v>0</v>
       </c>
-      <c r="AS6" s="44" t="n">
+      <c r="AS6" s="18" t="n">
         <f aca="false">AN5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="P7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="R7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="S7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="T7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="V7" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="W7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="44" t="n">
+      <c r="B7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V7" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="18" t="n">
         <f aca="false">SUM(B7:M7)</f>
         <v>33000</v>
       </c>
-      <c r="AM7" s="44" t="n">
+      <c r="AM7" s="18" t="n">
         <f aca="false">SUM(N7:Y7)</f>
         <v>27000</v>
       </c>
-      <c r="AN7" s="44" t="n">
+      <c r="AN7" s="18" t="n">
         <f aca="false">SUM(Z7:AK7)</f>
         <v>0</v>
       </c>
-      <c r="AP7" s="0" t="s">
+      <c r="AP7" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="AQ7" s="44" t="n">
+      <c r="AQ7" s="18" t="n">
         <f aca="false">AL18-AL5</f>
         <v>98000</v>
       </c>
-      <c r="AR7" s="44" t="n">
+      <c r="AR7" s="18" t="n">
         <f aca="false">AM18-AM5</f>
         <v>169000</v>
       </c>
-      <c r="AS7" s="44" t="n">
+      <c r="AS7" s="18" t="n">
         <f aca="false">AN18-AN5</f>
         <v>195000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="P8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="R8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="S8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="T8" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="44" t="n">
+      <c r="B8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T8" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="18" t="n">
         <f aca="false">SUM(B8:M8)</f>
         <v>27000</v>
       </c>
-      <c r="AM8" s="44" t="n">
+      <c r="AM8" s="18" t="n">
         <f aca="false">SUM(N8:Y8)</f>
         <v>21000</v>
       </c>
-      <c r="AN8" s="44" t="n">
+      <c r="AN8" s="18" t="n">
         <f aca="false">SUM(Z8:AK8)</f>
         <v>0</v>
       </c>
-      <c r="AP8" s="0" t="s">
+      <c r="AP8" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="AQ8" s="44" t="n">
+      <c r="AQ8" s="18" t="n">
         <f aca="false">AL18</f>
         <v>194000</v>
       </c>
-      <c r="AR8" s="44" t="n">
+      <c r="AR8" s="18" t="n">
         <f aca="false">AM18</f>
         <v>169000</v>
       </c>
-      <c r="AS8" s="44" t="n">
+      <c r="AS8" s="18" t="n">
         <f aca="false">AN18</f>
         <v>195000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="I9" s="44" t="n">
+      <c r="I9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="J9" s="44" t="n">
+      <c r="J9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="K9" s="44" t="n">
+      <c r="K9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="L9" s="44" t="n">
+      <c r="L9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="M9" s="44" t="n">
+      <c r="M9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="N9" s="44" t="n">
+      <c r="N9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="O9" s="44" t="n">
+      <c r="O9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="P9" s="44" t="n">
+      <c r="P9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="Q9" s="44" t="n">
+      <c r="Q9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="R9" s="44" t="n">
+      <c r="R9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="S9" s="44" t="n">
+      <c r="S9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="T9" s="44" t="n">
+      <c r="T9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="U9" s="44" t="n">
+      <c r="U9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="V9" s="44" t="n">
+      <c r="V9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="W9" s="44" t="n">
+      <c r="W9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="X9" s="44" t="n">
+      <c r="X9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="Y9" s="44" t="n">
+      <c r="Y9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="Z9" s="44" t="n">
+      <c r="Z9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="AA9" s="44" t="n">
+      <c r="AA9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="AB9" s="44" t="n">
+      <c r="AB9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="AC9" s="44" t="n">
+      <c r="AC9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="AD9" s="44" t="n">
+      <c r="AD9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="AE9" s="44" t="n">
+      <c r="AE9" s="18" t="n">
         <v>2000</v>
       </c>
-      <c r="AF9" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="44" t="n">
+      <c r="AF9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="18" t="n">
         <f aca="false">SUM(B9:M9)</f>
         <v>24000</v>
       </c>
-      <c r="AM9" s="44" t="n">
+      <c r="AM9" s="18" t="n">
         <f aca="false">SUM(N9:Y9)</f>
         <v>24000</v>
       </c>
-      <c r="AN9" s="44" t="n">
+      <c r="AN9" s="18" t="n">
         <f aca="false">SUM(Z9:AK9)</f>
         <v>12000</v>
       </c>
-      <c r="AP9" s="0" t="s">
+      <c r="AP9" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AQ9" s="44" t="n">
+      <c r="AQ9" s="18" t="n">
         <f aca="false">AL23</f>
         <v>-6312</v>
       </c>
-      <c r="AR9" s="44" t="n">
+      <c r="AR9" s="18" t="n">
         <f aca="false">AM23</f>
         <v>-9000</v>
       </c>
-      <c r="AS9" s="44" t="n">
+      <c r="AS9" s="18" t="n">
         <f aca="false">AN23</f>
         <v>-13200</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="44" t="n">
+      <c r="B10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="L10" s="44" t="n">
+      <c r="L10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="M10" s="44" t="n">
+      <c r="M10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="N10" s="44" t="n">
+      <c r="N10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="O10" s="44" t="n">
+      <c r="O10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="P10" s="44" t="n">
+      <c r="P10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="Q10" s="44" t="n">
+      <c r="Q10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="R10" s="44" t="n">
+      <c r="R10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="S10" s="44" t="n">
+      <c r="S10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="T10" s="44" t="n">
+      <c r="T10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="U10" s="44" t="n">
+      <c r="U10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="V10" s="44" t="n">
+      <c r="V10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="W10" s="44" t="n">
+      <c r="W10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="X10" s="44" t="n">
+      <c r="X10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="Y10" s="44" t="n">
+      <c r="Y10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="Z10" s="44" t="n">
+      <c r="Z10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AA10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="44" t="n">
+      <c r="AA10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="18" t="n">
         <f aca="false">SUM(B10:M10)</f>
         <v>12500</v>
       </c>
-      <c r="AM10" s="44" t="n">
+      <c r="AM10" s="18" t="n">
         <f aca="false">SUM(N10:Y10)</f>
         <v>30000</v>
       </c>
-      <c r="AN10" s="44" t="n">
+      <c r="AN10" s="18" t="n">
         <f aca="false">SUM(Z10:AK10)</f>
         <v>2500</v>
       </c>
-      <c r="AP10" s="45" t="s">
+      <c r="AP10" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="AQ10" s="46" t="n">
+      <c r="AQ10" s="19" t="n">
         <f aca="false">AL24</f>
         <v>187688</v>
       </c>
-      <c r="AR10" s="46" t="n">
+      <c r="AR10" s="19" t="n">
         <f aca="false">AM24</f>
         <v>160000</v>
       </c>
-      <c r="AS10" s="46" t="n">
+      <c r="AS10" s="19" t="n">
         <f aca="false">AN24</f>
         <v>181800</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="P11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="R11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="S11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="T11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="V11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="W11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="X11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Z11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AA11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AB11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AC11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AD11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AE11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AF11" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AG11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="44" t="n">
+      <c r="B11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="X11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Z11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AB11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AD11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AE11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF11" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AG11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="18" t="n">
         <f aca="false">SUM(B11:M11)</f>
         <v>0</v>
       </c>
-      <c r="AM11" s="44" t="n">
+      <c r="AM11" s="18" t="n">
         <f aca="false">SUM(N11:Y11)</f>
         <v>33000</v>
       </c>
-      <c r="AN11" s="44" t="n">
+      <c r="AN11" s="18" t="n">
         <f aca="false">SUM(Z11:AK11)</f>
         <v>21000</v>
       </c>
-      <c r="AP11" s="0" t="s">
+      <c r="AP11" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="AQ11" s="0" t="s">
+      <c r="AQ11" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="AR11" s="47" t="n">
+      <c r="AR11" s="23" t="n">
         <f aca="false">AM24/AL24-1</f>
         <v>-0.14752141852436</v>
       </c>
-      <c r="AS11" s="47" t="n">
+      <c r="AS11" s="23" t="n">
         <f aca="false">AN24/AM24-1</f>
         <v>0.13625</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="T12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="V12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="W12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="X12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Z12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AA12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AB12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AC12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AD12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AE12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AF12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AG12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AH12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AI12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AJ12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AK12" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AL12" s="44" t="n">
+      <c r="B12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="X12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Z12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AB12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AD12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AE12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AF12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AG12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AH12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AI12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AJ12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AK12" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AL12" s="18" t="n">
         <f aca="false">SUM(B12:M12)</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="44" t="n">
+      <c r="AM12" s="18" t="n">
         <f aca="false">SUM(N12:Y12)</f>
         <v>21000</v>
       </c>
-      <c r="AN12" s="44" t="n">
+      <c r="AN12" s="18" t="n">
         <f aca="false">SUM(Z12:AK12)</f>
         <v>36000</v>
       </c>
-      <c r="AP12" s="0" t="s">
+      <c r="AP12" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="AQ12" s="48" t="n">
+      <c r="AQ12" s="41" t="n">
         <f aca="false">M20</f>
         <v>3</v>
       </c>
-      <c r="AR12" s="48" t="n">
+      <c r="AR12" s="41" t="n">
         <f aca="false">Y20</f>
         <v>5</v>
       </c>
-      <c r="AS12" s="48" t="n">
+      <c r="AS12" s="41" t="n">
         <f aca="false">AK20</f>
         <v>5</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="44" t="n">
+      <c r="B13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="X13" s="44" t="n">
+      <c r="X13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="Y13" s="44" t="n">
+      <c r="Y13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="Z13" s="44" t="n">
+      <c r="Z13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AA13" s="44" t="n">
+      <c r="AA13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AB13" s="44" t="n">
+      <c r="AB13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AC13" s="44" t="n">
+      <c r="AC13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AD13" s="44" t="n">
+      <c r="AD13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AE13" s="44" t="n">
+      <c r="AE13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AF13" s="44" t="n">
+      <c r="AF13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AG13" s="44" t="n">
+      <c r="AG13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AH13" s="44" t="n">
+      <c r="AH13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AI13" s="44" t="n">
+      <c r="AI13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AJ13" s="44" t="n">
+      <c r="AJ13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AK13" s="44" t="n">
+      <c r="AK13" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AL13" s="44" t="n">
+      <c r="AL13" s="18" t="n">
         <f aca="false">SUM(B13:M13)</f>
         <v>0</v>
       </c>
-      <c r="AM13" s="44" t="n">
+      <c r="AM13" s="18" t="n">
         <f aca="false">SUM(N13:Y13)</f>
         <v>10500</v>
       </c>
-      <c r="AN13" s="44" t="n">
+      <c r="AN13" s="18" t="n">
         <f aca="false">SUM(Z13:AK13)</f>
         <v>42000</v>
       </c>
-      <c r="AP13" s="0" t="s">
+      <c r="AP13" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="AQ13" s="49" t="n">
+      <c r="AQ13" s="42" t="n">
         <f aca="false">AVERAGE(B20:M20)</f>
         <v>2.08333333333333</v>
       </c>
-      <c r="AR13" s="49" t="n">
+      <c r="AR13" s="42" t="n">
         <f aca="false">AVERAGE(N20:Y20)</f>
         <v>4.16666666666667</v>
       </c>
-      <c r="AS13" s="49" t="n">
+      <c r="AS13" s="42" t="n">
         <f aca="false">AVERAGE(Z20:AK20)</f>
         <v>4.83333333333333</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="44" t="n">
+      <c r="B14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="Z14" s="44" t="n">
+      <c r="Z14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AA14" s="44" t="n">
+      <c r="AA14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AB14" s="44" t="n">
+      <c r="AB14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AC14" s="44" t="n">
+      <c r="AC14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AD14" s="44" t="n">
+      <c r="AD14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AE14" s="44" t="n">
+      <c r="AE14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AF14" s="44" t="n">
+      <c r="AF14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AG14" s="44" t="n">
+      <c r="AG14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AH14" s="44" t="n">
+      <c r="AH14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AI14" s="44" t="n">
+      <c r="AI14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AJ14" s="44" t="n">
+      <c r="AJ14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AK14" s="44" t="n">
+      <c r="AK14" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="AL14" s="44" t="n">
+      <c r="AL14" s="18" t="n">
         <f aca="false">SUM(B14:M14)</f>
         <v>0</v>
       </c>
-      <c r="AM14" s="44" t="n">
+      <c r="AM14" s="18" t="n">
         <f aca="false">SUM(N14:Y14)</f>
         <v>2500</v>
       </c>
-      <c r="AN14" s="44" t="n">
+      <c r="AN14" s="18" t="n">
         <f aca="false">SUM(Z14:AK14)</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="44" t="n">
+      <c r="B15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AD15" s="44" t="n">
+      <c r="AD15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AE15" s="44" t="n">
+      <c r="AE15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AF15" s="44" t="n">
+      <c r="AF15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AG15" s="44" t="n">
+      <c r="AG15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AH15" s="44" t="n">
+      <c r="AH15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AI15" s="44" t="n">
+      <c r="AI15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AJ15" s="44" t="n">
+      <c r="AJ15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AK15" s="44" t="n">
+      <c r="AK15" s="18" t="n">
         <v>3500</v>
       </c>
-      <c r="AL15" s="44" t="n">
+      <c r="AL15" s="18" t="n">
         <f aca="false">SUM(B15:M15)</f>
         <v>0</v>
       </c>
-      <c r="AM15" s="44" t="n">
+      <c r="AM15" s="18" t="n">
         <f aca="false">SUM(N15:Y15)</f>
         <v>0</v>
       </c>
-      <c r="AN15" s="44" t="n">
+      <c r="AN15" s="18" t="n">
         <f aca="false">SUM(Z15:AK15)</f>
         <v>31500</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="44" t="n">
+      <c r="B16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="AH16" s="44" t="n">
+      <c r="AH16" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="AI16" s="44" t="n">
+      <c r="AI16" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="AJ16" s="44" t="n">
+      <c r="AJ16" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="AK16" s="44" t="n">
+      <c r="AK16" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="AL16" s="44" t="n">
+      <c r="AL16" s="18" t="n">
         <f aca="false">SUM(B16:M16)</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="44" t="n">
+      <c r="AM16" s="18" t="n">
         <f aca="false">SUM(N16:Y16)</f>
         <v>0</v>
       </c>
-      <c r="AN16" s="44" t="n">
+      <c r="AN16" s="18" t="n">
         <f aca="false">SUM(Z16:AK16)</f>
         <v>20000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="B18" s="46" t="n">
+      <c r="B18" s="19" t="n">
         <f aca="false">SUM(B5:B16)</f>
         <v>11500</v>
       </c>
-      <c r="C18" s="46" t="n">
+      <c r="C18" s="19" t="n">
         <f aca="false">SUM(C5:C16)</f>
         <v>13000</v>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="19" t="n">
         <f aca="false">SUM(D5:D16)</f>
         <v>13000</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="19" t="n">
         <f aca="false">SUM(E5:E16)</f>
         <v>16000</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="19" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>16000</v>
       </c>
-      <c r="G18" s="46" t="n">
+      <c r="G18" s="19" t="n">
         <f aca="false">SUM(G5:G16)</f>
         <v>16000</v>
       </c>
-      <c r="H18" s="46" t="n">
+      <c r="H18" s="19" t="n">
         <f aca="false">SUM(H5:H16)</f>
         <v>16000</v>
       </c>
-      <c r="I18" s="46" t="n">
+      <c r="I18" s="19" t="n">
         <f aca="false">SUM(I5:I16)</f>
         <v>18500</v>
       </c>
-      <c r="J18" s="46" t="n">
+      <c r="J18" s="19" t="n">
         <f aca="false">SUM(J5:J16)</f>
         <v>18500</v>
       </c>
-      <c r="K18" s="46" t="n">
+      <c r="K18" s="19" t="n">
         <f aca="false">SUM(K5:K16)</f>
         <v>18500</v>
       </c>
-      <c r="L18" s="46" t="n">
+      <c r="L18" s="19" t="n">
         <f aca="false">SUM(L5:L16)</f>
         <v>18500</v>
       </c>
-      <c r="M18" s="46" t="n">
+      <c r="M18" s="19" t="n">
         <f aca="false">SUM(M5:M16)</f>
         <v>18500</v>
       </c>
-      <c r="N18" s="46" t="n">
+      <c r="N18" s="19" t="n">
         <f aca="false">SUM(N5:N16)</f>
         <v>10500</v>
       </c>
-      <c r="O18" s="46" t="n">
+      <c r="O18" s="19" t="n">
         <f aca="false">SUM(O5:O16)</f>
         <v>13500</v>
       </c>
-      <c r="P18" s="46" t="n">
+      <c r="P18" s="19" t="n">
         <f aca="false">SUM(P5:P16)</f>
         <v>13500</v>
       </c>
-      <c r="Q18" s="46" t="n">
+      <c r="Q18" s="19" t="n">
         <f aca="false">SUM(Q5:Q16)</f>
         <v>13500</v>
       </c>
-      <c r="R18" s="46" t="n">
+      <c r="R18" s="19" t="n">
         <f aca="false">SUM(R5:R16)</f>
         <v>13500</v>
       </c>
-      <c r="S18" s="46" t="n">
+      <c r="S18" s="19" t="n">
         <f aca="false">SUM(S5:S16)</f>
         <v>16500</v>
       </c>
-      <c r="T18" s="46" t="n">
+      <c r="T18" s="19" t="n">
         <f aca="false">SUM(T5:T16)</f>
         <v>16500</v>
       </c>
-      <c r="U18" s="46" t="n">
+      <c r="U18" s="19" t="n">
         <f aca="false">SUM(U5:U16)</f>
         <v>13500</v>
       </c>
-      <c r="V18" s="46" t="n">
+      <c r="V18" s="19" t="n">
         <f aca="false">SUM(V5:V16)</f>
         <v>13500</v>
       </c>
-      <c r="W18" s="46" t="n">
+      <c r="W18" s="19" t="n">
         <f aca="false">SUM(W5:W16)</f>
         <v>14000</v>
       </c>
-      <c r="X18" s="46" t="n">
+      <c r="X18" s="19" t="n">
         <f aca="false">SUM(X5:X16)</f>
         <v>14000</v>
       </c>
-      <c r="Y18" s="46" t="n">
+      <c r="Y18" s="19" t="n">
         <f aca="false">SUM(Y5:Y16)</f>
         <v>16500</v>
       </c>
-      <c r="Z18" s="46" t="n">
+      <c r="Z18" s="19" t="n">
         <f aca="false">SUM(Z5:Z16)</f>
         <v>16500</v>
       </c>
-      <c r="AA18" s="46" t="n">
+      <c r="AA18" s="19" t="n">
         <f aca="false">SUM(AA5:AA16)</f>
         <v>14000</v>
       </c>
-      <c r="AB18" s="46" t="n">
+      <c r="AB18" s="19" t="n">
         <f aca="false">SUM(AB5:AB16)</f>
         <v>14000</v>
       </c>
-      <c r="AC18" s="46" t="n">
+      <c r="AC18" s="19" t="n">
         <f aca="false">SUM(AC5:AC16)</f>
         <v>17500</v>
       </c>
-      <c r="AD18" s="46" t="n">
+      <c r="AD18" s="19" t="n">
         <f aca="false">SUM(AD5:AD16)</f>
         <v>17500</v>
       </c>
-      <c r="AE18" s="46" t="n">
+      <c r="AE18" s="19" t="n">
         <f aca="false">SUM(AE5:AE16)</f>
         <v>17500</v>
       </c>
-      <c r="AF18" s="46" t="n">
+      <c r="AF18" s="19" t="n">
         <f aca="false">SUM(AF5:AF16)</f>
         <v>15500</v>
       </c>
-      <c r="AG18" s="46" t="n">
+      <c r="AG18" s="19" t="n">
         <f aca="false">SUM(AG5:AG16)</f>
         <v>16500</v>
       </c>
-      <c r="AH18" s="46" t="n">
+      <c r="AH18" s="19" t="n">
         <f aca="false">SUM(AH5:AH16)</f>
         <v>16500</v>
       </c>
-      <c r="AI18" s="46" t="n">
+      <c r="AI18" s="19" t="n">
         <f aca="false">SUM(AI5:AI16)</f>
         <v>16500</v>
       </c>
-      <c r="AJ18" s="46" t="n">
+      <c r="AJ18" s="19" t="n">
         <f aca="false">SUM(AJ5:AJ16)</f>
         <v>16500</v>
       </c>
-      <c r="AK18" s="46" t="n">
+      <c r="AK18" s="19" t="n">
         <f aca="false">SUM(AK5:AK16)</f>
         <v>16500</v>
       </c>
-      <c r="AL18" s="46" t="n">
+      <c r="AL18" s="19" t="n">
         <f aca="false">SUM(B18:M18)</f>
         <v>194000</v>
       </c>
-      <c r="AM18" s="46" t="n">
+      <c r="AM18" s="19" t="n">
         <f aca="false">SUM(N18:Y18)</f>
         <v>169000</v>
       </c>
-      <c r="AN18" s="46" t="n">
+      <c r="AN18" s="19" t="n">
         <f aca="false">SUM(Z18:AK18)</f>
         <v>195000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="s">
         <v>369</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <f aca="false">IF(B7&gt;0,1,0)+IF(B8&gt;0,1,0)+IF(B10&gt;0,1,0)+IF(B11&gt;0,1,0)+IF(B12&gt;0,1,0)+IF(B13&gt;0,1,0)+IF(B14&gt;0,1,0)+IF(B15&gt;0,1,0)+IF(B16&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <f aca="false">IF(C7&gt;0,1,0)+IF(C8&gt;0,1,0)+IF(C10&gt;0,1,0)+IF(C11&gt;0,1,0)+IF(C12&gt;0,1,0)+IF(C13&gt;0,1,0)+IF(C14&gt;0,1,0)+IF(C15&gt;0,1,0)+IF(C16&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <f aca="false">IF(D7&gt;0,1,0)+IF(D8&gt;0,1,0)+IF(D10&gt;0,1,0)+IF(D11&gt;0,1,0)+IF(D12&gt;0,1,0)+IF(D13&gt;0,1,0)+IF(D14&gt;0,1,0)+IF(D15&gt;0,1,0)+IF(D16&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <f aca="false">IF(E7&gt;0,1,0)+IF(E8&gt;0,1,0)+IF(E10&gt;0,1,0)+IF(E11&gt;0,1,0)+IF(E12&gt;0,1,0)+IF(E13&gt;0,1,0)+IF(E14&gt;0,1,0)+IF(E15&gt;0,1,0)+IF(E16&gt;0,1,0)</f>
         <v>2</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <f aca="false">IF(F7&gt;0,1,0)+IF(F8&gt;0,1,0)+IF(F10&gt;0,1,0)+IF(F11&gt;0,1,0)+IF(F12&gt;0,1,0)+IF(F13&gt;0,1,0)+IF(F14&gt;0,1,0)+IF(F15&gt;0,1,0)+IF(F16&gt;0,1,0)</f>
         <v>2</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <f aca="false">IF(G7&gt;0,1,0)+IF(G8&gt;0,1,0)+IF(G10&gt;0,1,0)+IF(G11&gt;0,1,0)+IF(G12&gt;0,1,0)+IF(G13&gt;0,1,0)+IF(G14&gt;0,1,0)+IF(G15&gt;0,1,0)+IF(G16&gt;0,1,0)</f>
         <v>2</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <f aca="false">IF(H7&gt;0,1,0)+IF(H8&gt;0,1,0)+IF(H10&gt;0,1,0)+IF(H11&gt;0,1,0)+IF(H12&gt;0,1,0)+IF(H13&gt;0,1,0)+IF(H14&gt;0,1,0)+IF(H15&gt;0,1,0)+IF(H16&gt;0,1,0)</f>
         <v>2</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="I20" s="1" t="n">
         <f aca="false">IF(I7&gt;0,1,0)+IF(I8&gt;0,1,0)+IF(I10&gt;0,1,0)+IF(I11&gt;0,1,0)+IF(I12&gt;0,1,0)+IF(I13&gt;0,1,0)+IF(I14&gt;0,1,0)+IF(I15&gt;0,1,0)+IF(I16&gt;0,1,0)</f>
         <v>3</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J20" s="1" t="n">
         <f aca="false">IF(J7&gt;0,1,0)+IF(J8&gt;0,1,0)+IF(J10&gt;0,1,0)+IF(J11&gt;0,1,0)+IF(J12&gt;0,1,0)+IF(J13&gt;0,1,0)+IF(J14&gt;0,1,0)+IF(J15&gt;0,1,0)+IF(J16&gt;0,1,0)</f>
         <v>3</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20" s="1" t="n">
         <f aca="false">IF(K7&gt;0,1,0)+IF(K8&gt;0,1,0)+IF(K10&gt;0,1,0)+IF(K11&gt;0,1,0)+IF(K12&gt;0,1,0)+IF(K13&gt;0,1,0)+IF(K14&gt;0,1,0)+IF(K15&gt;0,1,0)+IF(K16&gt;0,1,0)</f>
         <v>3</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="1" t="n">
         <f aca="false">IF(L7&gt;0,1,0)+IF(L8&gt;0,1,0)+IF(L10&gt;0,1,0)+IF(L11&gt;0,1,0)+IF(L12&gt;0,1,0)+IF(L13&gt;0,1,0)+IF(L14&gt;0,1,0)+IF(L15&gt;0,1,0)+IF(L16&gt;0,1,0)</f>
         <v>3</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="1" t="n">
         <f aca="false">IF(M7&gt;0,1,0)+IF(M8&gt;0,1,0)+IF(M10&gt;0,1,0)+IF(M11&gt;0,1,0)+IF(M12&gt;0,1,0)+IF(M13&gt;0,1,0)+IF(M14&gt;0,1,0)+IF(M15&gt;0,1,0)+IF(M16&gt;0,1,0)</f>
         <v>3</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="1" t="n">
         <f aca="false">IF(N7&gt;0,1,0)+IF(N8&gt;0,1,0)+IF(N10&gt;0,1,0)+IF(N11&gt;0,1,0)+IF(N12&gt;0,1,0)+IF(N13&gt;0,1,0)+IF(N14&gt;0,1,0)+IF(N15&gt;0,1,0)+IF(N16&gt;0,1,0)</f>
         <v>3</v>
       </c>
-      <c r="O20" s="0" t="n">
+      <c r="O20" s="1" t="n">
         <f aca="false">IF(O7&gt;0,1,0)+IF(O8&gt;0,1,0)+IF(O10&gt;0,1,0)+IF(O11&gt;0,1,0)+IF(O12&gt;0,1,0)+IF(O13&gt;0,1,0)+IF(O14&gt;0,1,0)+IF(O15&gt;0,1,0)+IF(O16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="P20" s="0" t="n">
+      <c r="P20" s="1" t="n">
         <f aca="false">IF(P7&gt;0,1,0)+IF(P8&gt;0,1,0)+IF(P10&gt;0,1,0)+IF(P11&gt;0,1,0)+IF(P12&gt;0,1,0)+IF(P13&gt;0,1,0)+IF(P14&gt;0,1,0)+IF(P15&gt;0,1,0)+IF(P16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="Q20" s="0" t="n">
+      <c r="Q20" s="1" t="n">
         <f aca="false">IF(Q7&gt;0,1,0)+IF(Q8&gt;0,1,0)+IF(Q10&gt;0,1,0)+IF(Q11&gt;0,1,0)+IF(Q12&gt;0,1,0)+IF(Q13&gt;0,1,0)+IF(Q14&gt;0,1,0)+IF(Q15&gt;0,1,0)+IF(Q16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="R20" s="0" t="n">
+      <c r="R20" s="1" t="n">
         <f aca="false">IF(R7&gt;0,1,0)+IF(R8&gt;0,1,0)+IF(R10&gt;0,1,0)+IF(R11&gt;0,1,0)+IF(R12&gt;0,1,0)+IF(R13&gt;0,1,0)+IF(R14&gt;0,1,0)+IF(R15&gt;0,1,0)+IF(R16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="S20" s="0" t="n">
+      <c r="S20" s="1" t="n">
         <f aca="false">IF(S7&gt;0,1,0)+IF(S8&gt;0,1,0)+IF(S10&gt;0,1,0)+IF(S11&gt;0,1,0)+IF(S12&gt;0,1,0)+IF(S13&gt;0,1,0)+IF(S14&gt;0,1,0)+IF(S15&gt;0,1,0)+IF(S16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="T20" s="0" t="n">
+      <c r="T20" s="1" t="n">
         <f aca="false">IF(T7&gt;0,1,0)+IF(T8&gt;0,1,0)+IF(T10&gt;0,1,0)+IF(T11&gt;0,1,0)+IF(T12&gt;0,1,0)+IF(T13&gt;0,1,0)+IF(T14&gt;0,1,0)+IF(T15&gt;0,1,0)+IF(T16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="U20" s="0" t="n">
+      <c r="U20" s="1" t="n">
         <f aca="false">IF(U7&gt;0,1,0)+IF(U8&gt;0,1,0)+IF(U10&gt;0,1,0)+IF(U11&gt;0,1,0)+IF(U12&gt;0,1,0)+IF(U13&gt;0,1,0)+IF(U14&gt;0,1,0)+IF(U15&gt;0,1,0)+IF(U16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="V20" s="0" t="n">
+      <c r="V20" s="1" t="n">
         <f aca="false">IF(V7&gt;0,1,0)+IF(V8&gt;0,1,0)+IF(V10&gt;0,1,0)+IF(V11&gt;0,1,0)+IF(V12&gt;0,1,0)+IF(V13&gt;0,1,0)+IF(V14&gt;0,1,0)+IF(V15&gt;0,1,0)+IF(V16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="W20" s="0" t="n">
+      <c r="W20" s="1" t="n">
         <f aca="false">IF(W7&gt;0,1,0)+IF(W8&gt;0,1,0)+IF(W10&gt;0,1,0)+IF(W11&gt;0,1,0)+IF(W12&gt;0,1,0)+IF(W13&gt;0,1,0)+IF(W14&gt;0,1,0)+IF(W15&gt;0,1,0)+IF(W16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="X20" s="0" t="n">
+      <c r="X20" s="1" t="n">
         <f aca="false">IF(X7&gt;0,1,0)+IF(X8&gt;0,1,0)+IF(X10&gt;0,1,0)+IF(X11&gt;0,1,0)+IF(X12&gt;0,1,0)+IF(X13&gt;0,1,0)+IF(X14&gt;0,1,0)+IF(X15&gt;0,1,0)+IF(X16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="Y20" s="0" t="n">
+      <c r="Y20" s="1" t="n">
         <f aca="false">IF(Y7&gt;0,1,0)+IF(Y8&gt;0,1,0)+IF(Y10&gt;0,1,0)+IF(Y11&gt;0,1,0)+IF(Y12&gt;0,1,0)+IF(Y13&gt;0,1,0)+IF(Y14&gt;0,1,0)+IF(Y15&gt;0,1,0)+IF(Y16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="Z20" s="0" t="n">
+      <c r="Z20" s="1" t="n">
         <f aca="false">IF(Z7&gt;0,1,0)+IF(Z8&gt;0,1,0)+IF(Z10&gt;0,1,0)+IF(Z11&gt;0,1,0)+IF(Z12&gt;0,1,0)+IF(Z13&gt;0,1,0)+IF(Z14&gt;0,1,0)+IF(Z15&gt;0,1,0)+IF(Z16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AA20" s="0" t="n">
+      <c r="AA20" s="1" t="n">
         <f aca="false">IF(AA7&gt;0,1,0)+IF(AA8&gt;0,1,0)+IF(AA10&gt;0,1,0)+IF(AA11&gt;0,1,0)+IF(AA12&gt;0,1,0)+IF(AA13&gt;0,1,0)+IF(AA14&gt;0,1,0)+IF(AA15&gt;0,1,0)+IF(AA16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="AB20" s="0" t="n">
+      <c r="AB20" s="1" t="n">
         <f aca="false">IF(AB7&gt;0,1,0)+IF(AB8&gt;0,1,0)+IF(AB10&gt;0,1,0)+IF(AB11&gt;0,1,0)+IF(AB12&gt;0,1,0)+IF(AB13&gt;0,1,0)+IF(AB14&gt;0,1,0)+IF(AB15&gt;0,1,0)+IF(AB16&gt;0,1,0)</f>
         <v>4</v>
       </c>
-      <c r="AC20" s="0" t="n">
+      <c r="AC20" s="1" t="n">
         <f aca="false">IF(AC7&gt;0,1,0)+IF(AC8&gt;0,1,0)+IF(AC10&gt;0,1,0)+IF(AC11&gt;0,1,0)+IF(AC12&gt;0,1,0)+IF(AC13&gt;0,1,0)+IF(AC14&gt;0,1,0)+IF(AC15&gt;0,1,0)+IF(AC16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AD20" s="0" t="n">
+      <c r="AD20" s="1" t="n">
         <f aca="false">IF(AD7&gt;0,1,0)+IF(AD8&gt;0,1,0)+IF(AD10&gt;0,1,0)+IF(AD11&gt;0,1,0)+IF(AD12&gt;0,1,0)+IF(AD13&gt;0,1,0)+IF(AD14&gt;0,1,0)+IF(AD15&gt;0,1,0)+IF(AD16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AE20" s="0" t="n">
+      <c r="AE20" s="1" t="n">
         <f aca="false">IF(AE7&gt;0,1,0)+IF(AE8&gt;0,1,0)+IF(AE10&gt;0,1,0)+IF(AE11&gt;0,1,0)+IF(AE12&gt;0,1,0)+IF(AE13&gt;0,1,0)+IF(AE14&gt;0,1,0)+IF(AE15&gt;0,1,0)+IF(AE16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AF20" s="0" t="n">
+      <c r="AF20" s="1" t="n">
         <f aca="false">IF(AF7&gt;0,1,0)+IF(AF8&gt;0,1,0)+IF(AF10&gt;0,1,0)+IF(AF11&gt;0,1,0)+IF(AF12&gt;0,1,0)+IF(AF13&gt;0,1,0)+IF(AF14&gt;0,1,0)+IF(AF15&gt;0,1,0)+IF(AF16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AG20" s="0" t="n">
+      <c r="AG20" s="1" t="n">
         <f aca="false">IF(AG7&gt;0,1,0)+IF(AG8&gt;0,1,0)+IF(AG10&gt;0,1,0)+IF(AG11&gt;0,1,0)+IF(AG12&gt;0,1,0)+IF(AG13&gt;0,1,0)+IF(AG14&gt;0,1,0)+IF(AG15&gt;0,1,0)+IF(AG16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AH20" s="0" t="n">
+      <c r="AH20" s="1" t="n">
         <f aca="false">IF(AH7&gt;0,1,0)+IF(AH8&gt;0,1,0)+IF(AH10&gt;0,1,0)+IF(AH11&gt;0,1,0)+IF(AH12&gt;0,1,0)+IF(AH13&gt;0,1,0)+IF(AH14&gt;0,1,0)+IF(AH15&gt;0,1,0)+IF(AH16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AI20" s="0" t="n">
+      <c r="AI20" s="1" t="n">
         <f aca="false">IF(AI7&gt;0,1,0)+IF(AI8&gt;0,1,0)+IF(AI10&gt;0,1,0)+IF(AI11&gt;0,1,0)+IF(AI12&gt;0,1,0)+IF(AI13&gt;0,1,0)+IF(AI14&gt;0,1,0)+IF(AI15&gt;0,1,0)+IF(AI16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AJ20" s="0" t="n">
+      <c r="AJ20" s="1" t="n">
         <f aca="false">IF(AJ7&gt;0,1,0)+IF(AJ8&gt;0,1,0)+IF(AJ10&gt;0,1,0)+IF(AJ11&gt;0,1,0)+IF(AJ12&gt;0,1,0)+IF(AJ13&gt;0,1,0)+IF(AJ14&gt;0,1,0)+IF(AJ15&gt;0,1,0)+IF(AJ16&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="AK20" s="0" t="n">
+      <c r="AK20" s="1" t="n">
         <f aca="false">IF(AK7&gt;0,1,0)+IF(AK8&gt;0,1,0)+IF(AK10&gt;0,1,0)+IF(AK11&gt;0,1,0)+IF(AK12&gt;0,1,0)+IF(AK13&gt;0,1,0)+IF(AK14&gt;0,1,0)+IF(AK15&gt;0,1,0)+IF(AK16&gt;0,1,0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
         <v>370</v>
       </c>
-      <c r="B21" s="50" t="str">
+      <c r="B21" s="43" t="str">
         <f aca="false">IF(1&lt;=12,IF(B20&gt;3,"OVER",""),IF(B20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="C21" s="50" t="str">
+      <c r="C21" s="43" t="str">
         <f aca="false">IF(2&lt;=12,IF(C20&gt;3,"OVER",""),IF(C20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="D21" s="50" t="str">
+      <c r="D21" s="43" t="str">
         <f aca="false">IF(3&lt;=12,IF(D20&gt;3,"OVER",""),IF(D20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="E21" s="50" t="str">
+      <c r="E21" s="43" t="str">
         <f aca="false">IF(4&lt;=12,IF(E20&gt;3,"OVER",""),IF(E20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="F21" s="50" t="str">
+      <c r="F21" s="43" t="str">
         <f aca="false">IF(5&lt;=12,IF(F20&gt;3,"OVER",""),IF(F20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="G21" s="50" t="str">
+      <c r="G21" s="43" t="str">
         <f aca="false">IF(6&lt;=12,IF(G20&gt;3,"OVER",""),IF(G20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="H21" s="50" t="str">
+      <c r="H21" s="43" t="str">
         <f aca="false">IF(7&lt;=12,IF(H20&gt;3,"OVER",""),IF(H20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="I21" s="50" t="str">
+      <c r="I21" s="43" t="str">
         <f aca="false">IF(8&lt;=12,IF(I20&gt;3,"OVER",""),IF(I20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="J21" s="50" t="str">
+      <c r="J21" s="43" t="str">
         <f aca="false">IF(9&lt;=12,IF(J20&gt;3,"OVER",""),IF(J20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="K21" s="50" t="str">
+      <c r="K21" s="43" t="str">
         <f aca="false">IF(10&lt;=12,IF(K20&gt;3,"OVER",""),IF(K20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="L21" s="50" t="str">
+      <c r="L21" s="43" t="str">
         <f aca="false">IF(11&lt;=12,IF(L20&gt;3,"OVER",""),IF(L20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="M21" s="50" t="str">
+      <c r="M21" s="43" t="str">
         <f aca="false">IF(12&lt;=12,IF(M20&gt;3,"OVER",""),IF(M20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="N21" s="50" t="str">
+      <c r="N21" s="43" t="str">
         <f aca="false">IF(13&lt;=12,IF(N20&gt;3,"OVER",""),IF(N20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="O21" s="50" t="str">
+      <c r="O21" s="43" t="str">
         <f aca="false">IF(14&lt;=12,IF(O20&gt;3,"OVER",""),IF(O20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="P21" s="50" t="str">
+      <c r="P21" s="43" t="str">
         <f aca="false">IF(15&lt;=12,IF(P20&gt;3,"OVER",""),IF(P20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="Q21" s="50" t="str">
+      <c r="Q21" s="43" t="str">
         <f aca="false">IF(16&lt;=12,IF(Q20&gt;3,"OVER",""),IF(Q20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="R21" s="50" t="str">
+      <c r="R21" s="43" t="str">
         <f aca="false">IF(17&lt;=12,IF(R20&gt;3,"OVER",""),IF(R20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="S21" s="50" t="str">
+      <c r="S21" s="43" t="str">
         <f aca="false">IF(18&lt;=12,IF(S20&gt;3,"OVER",""),IF(S20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="T21" s="50" t="str">
+      <c r="T21" s="43" t="str">
         <f aca="false">IF(19&lt;=12,IF(T20&gt;3,"OVER",""),IF(T20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="U21" s="50" t="str">
+      <c r="U21" s="43" t="str">
         <f aca="false">IF(20&lt;=12,IF(U20&gt;3,"OVER",""),IF(U20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="V21" s="50" t="str">
+      <c r="V21" s="43" t="str">
         <f aca="false">IF(21&lt;=12,IF(V20&gt;3,"OVER",""),IF(V20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="W21" s="50" t="str">
+      <c r="W21" s="43" t="str">
         <f aca="false">IF(22&lt;=12,IF(W20&gt;3,"OVER",""),IF(W20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="X21" s="50" t="str">
+      <c r="X21" s="43" t="str">
         <f aca="false">IF(23&lt;=12,IF(X20&gt;3,"OVER",""),IF(X20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="Y21" s="50" t="str">
+      <c r="Y21" s="43" t="str">
         <f aca="false">IF(24&lt;=12,IF(Y20&gt;3,"OVER",""),IF(Y20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="Z21" s="50" t="str">
+      <c r="Z21" s="43" t="str">
         <f aca="false">IF(25&lt;=12,IF(Z20&gt;3,"OVER",""),IF(Z20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AA21" s="50" t="str">
+      <c r="AA21" s="43" t="str">
         <f aca="false">IF(26&lt;=12,IF(AA20&gt;3,"OVER",""),IF(AA20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AB21" s="50" t="str">
+      <c r="AB21" s="43" t="str">
         <f aca="false">IF(27&lt;=12,IF(AB20&gt;3,"OVER",""),IF(AB20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AC21" s="50" t="str">
+      <c r="AC21" s="43" t="str">
         <f aca="false">IF(28&lt;=12,IF(AC20&gt;3,"OVER",""),IF(AC20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AD21" s="50" t="str">
+      <c r="AD21" s="43" t="str">
         <f aca="false">IF(29&lt;=12,IF(AD20&gt;3,"OVER",""),IF(AD20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AE21" s="50" t="str">
+      <c r="AE21" s="43" t="str">
         <f aca="false">IF(30&lt;=12,IF(AE20&gt;3,"OVER",""),IF(AE20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AF21" s="50" t="str">
+      <c r="AF21" s="43" t="str">
         <f aca="false">IF(31&lt;=12,IF(AF20&gt;3,"OVER",""),IF(AF20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AG21" s="50" t="str">
+      <c r="AG21" s="43" t="str">
         <f aca="false">IF(32&lt;=12,IF(AG20&gt;3,"OVER",""),IF(AG20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AH21" s="50" t="str">
+      <c r="AH21" s="43" t="str">
         <f aca="false">IF(33&lt;=12,IF(AH20&gt;3,"OVER",""),IF(AH20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AI21" s="50" t="str">
+      <c r="AI21" s="43" t="str">
         <f aca="false">IF(34&lt;=12,IF(AI20&gt;3,"OVER",""),IF(AI20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AJ21" s="50" t="str">
+      <c r="AJ21" s="43" t="str">
         <f aca="false">IF(35&lt;=12,IF(AJ20&gt;3,"OVER",""),IF(AJ20&gt;5,"OVER",""))</f>
         <v/>
       </c>
-      <c r="AK21" s="50" t="str">
+      <c r="AK21" s="43" t="str">
         <f aca="false">IF(36&lt;=12,IF(AK20&gt;3,"OVER",""),IF(AK20&gt;5,"OVER",""))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24" t="s">
         <v>371</v>
       </c>
-      <c r="B23" s="51" t="n">
+      <c r="B23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="C23" s="51" t="n">
+      <c r="C23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="D23" s="51" t="n">
+      <c r="D23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="E23" s="51" t="n">
+      <c r="E23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="F23" s="51" t="n">
+      <c r="F23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="G23" s="51" t="n">
+      <c r="G23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="H23" s="51" t="n">
+      <c r="H23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="I23" s="51" t="n">
+      <c r="I23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="J23" s="51" t="n">
+      <c r="J23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="K23" s="51" t="n">
+      <c r="K23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="L23" s="51" t="n">
+      <c r="L23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="M23" s="51" t="n">
+      <c r="M23" s="5" t="n">
         <v>-526</v>
       </c>
-      <c r="N23" s="51" t="n">
+      <c r="N23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="O23" s="51" t="n">
+      <c r="O23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="P23" s="51" t="n">
+      <c r="P23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="Q23" s="51" t="n">
+      <c r="Q23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="R23" s="51" t="n">
+      <c r="R23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="S23" s="51" t="n">
+      <c r="S23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="T23" s="51" t="n">
+      <c r="T23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="U23" s="51" t="n">
+      <c r="U23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="V23" s="51" t="n">
+      <c r="V23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="W23" s="51" t="n">
+      <c r="W23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="X23" s="51" t="n">
+      <c r="X23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="Y23" s="51" t="n">
+      <c r="Y23" s="5" t="n">
         <v>-750</v>
       </c>
-      <c r="Z23" s="51" t="n">
+      <c r="Z23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="51" t="n">
+      <c r="AA23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AB23" s="51" t="n">
+      <c r="AB23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AC23" s="51" t="n">
+      <c r="AC23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AD23" s="51" t="n">
+      <c r="AD23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AE23" s="51" t="n">
+      <c r="AE23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AF23" s="51" t="n">
+      <c r="AF23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AG23" s="51" t="n">
+      <c r="AG23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AH23" s="51" t="n">
+      <c r="AH23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AI23" s="51" t="n">
+      <c r="AI23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AJ23" s="51" t="n">
+      <c r="AJ23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AK23" s="51" t="n">
+      <c r="AK23" s="5" t="n">
         <v>-1100</v>
       </c>
-      <c r="AL23" s="44" t="n">
+      <c r="AL23" s="18" t="n">
         <f aca="false">SUM(B23:M23)</f>
         <v>-6312</v>
       </c>
-      <c r="AM23" s="44" t="n">
+      <c r="AM23" s="18" t="n">
         <f aca="false">SUM(N23:Y23)</f>
         <v>-9000</v>
       </c>
-      <c r="AN23" s="44" t="n">
+      <c r="AN23" s="18" t="n">
         <f aca="false">SUM(Z23:AK23)</f>
         <v>-13200</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="s">
         <v>372</v>
       </c>
-      <c r="B24" s="46" t="n">
+      <c r="B24" s="19" t="n">
         <f aca="false">B18+B23</f>
         <v>10974</v>
       </c>
-      <c r="C24" s="46" t="n">
+      <c r="C24" s="19" t="n">
         <f aca="false">C18+C23</f>
         <v>12474</v>
       </c>
-      <c r="D24" s="46" t="n">
+      <c r="D24" s="19" t="n">
         <f aca="false">D18+D23</f>
         <v>12474</v>
       </c>
-      <c r="E24" s="46" t="n">
+      <c r="E24" s="19" t="n">
         <f aca="false">E18+E23</f>
         <v>15474</v>
       </c>
-      <c r="F24" s="46" t="n">
+      <c r="F24" s="19" t="n">
         <f aca="false">F18+F23</f>
         <v>15474</v>
       </c>
-      <c r="G24" s="46" t="n">
+      <c r="G24" s="19" t="n">
         <f aca="false">G18+G23</f>
         <v>15474</v>
       </c>
-      <c r="H24" s="46" t="n">
+      <c r="H24" s="19" t="n">
         <f aca="false">H18+H23</f>
         <v>15474</v>
       </c>
-      <c r="I24" s="46" t="n">
+      <c r="I24" s="19" t="n">
         <f aca="false">I18+I23</f>
         <v>17974</v>
       </c>
-      <c r="J24" s="46" t="n">
+      <c r="J24" s="19" t="n">
         <f aca="false">J18+J23</f>
         <v>17974</v>
       </c>
-      <c r="K24" s="46" t="n">
+      <c r="K24" s="19" t="n">
         <f aca="false">K18+K23</f>
         <v>17974</v>
       </c>
-      <c r="L24" s="46" t="n">
+      <c r="L24" s="19" t="n">
         <f aca="false">L18+L23</f>
         <v>17974</v>
       </c>
-      <c r="M24" s="46" t="n">
+      <c r="M24" s="19" t="n">
         <f aca="false">M18+M23</f>
         <v>17974</v>
       </c>
-      <c r="N24" s="46" t="n">
+      <c r="N24" s="19" t="n">
         <f aca="false">N18+N23</f>
         <v>9750</v>
       </c>
-      <c r="O24" s="46" t="n">
+      <c r="O24" s="19" t="n">
         <f aca="false">O18+O23</f>
         <v>12750</v>
       </c>
-      <c r="P24" s="46" t="n">
+      <c r="P24" s="19" t="n">
         <f aca="false">P18+P23</f>
         <v>12750</v>
       </c>
-      <c r="Q24" s="46" t="n">
+      <c r="Q24" s="19" t="n">
         <f aca="false">Q18+Q23</f>
         <v>12750</v>
       </c>
-      <c r="R24" s="46" t="n">
+      <c r="R24" s="19" t="n">
         <f aca="false">R18+R23</f>
         <v>12750</v>
       </c>
-      <c r="S24" s="46" t="n">
+      <c r="S24" s="19" t="n">
         <f aca="false">S18+S23</f>
         <v>15750</v>
       </c>
-      <c r="T24" s="46" t="n">
+      <c r="T24" s="19" t="n">
         <f aca="false">T18+T23</f>
         <v>15750</v>
       </c>
-      <c r="U24" s="46" t="n">
+      <c r="U24" s="19" t="n">
         <f aca="false">U18+U23</f>
         <v>12750</v>
       </c>
-      <c r="V24" s="46" t="n">
+      <c r="V24" s="19" t="n">
         <f aca="false">V18+V23</f>
         <v>12750</v>
       </c>
-      <c r="W24" s="46" t="n">
+      <c r="W24" s="19" t="n">
         <f aca="false">W18+W23</f>
         <v>13250</v>
       </c>
-      <c r="X24" s="46" t="n">
+      <c r="X24" s="19" t="n">
         <f aca="false">X18+X23</f>
         <v>13250</v>
       </c>
-      <c r="Y24" s="46" t="n">
+      <c r="Y24" s="19" t="n">
         <f aca="false">Y18+Y23</f>
         <v>15750</v>
       </c>
-      <c r="Z24" s="46" t="n">
+      <c r="Z24" s="19" t="n">
         <f aca="false">Z18+Z23</f>
         <v>15400</v>
       </c>
-      <c r="AA24" s="46" t="n">
+      <c r="AA24" s="19" t="n">
         <f aca="false">AA18+AA23</f>
         <v>12900</v>
       </c>
-      <c r="AB24" s="46" t="n">
+      <c r="AB24" s="19" t="n">
         <f aca="false">AB18+AB23</f>
         <v>12900</v>
       </c>
-      <c r="AC24" s="46" t="n">
+      <c r="AC24" s="19" t="n">
         <f aca="false">AC18+AC23</f>
         <v>16400</v>
       </c>
-      <c r="AD24" s="46" t="n">
+      <c r="AD24" s="19" t="n">
         <f aca="false">AD18+AD23</f>
         <v>16400</v>
       </c>
-      <c r="AE24" s="46" t="n">
+      <c r="AE24" s="19" t="n">
         <f aca="false">AE18+AE23</f>
         <v>16400</v>
       </c>
-      <c r="AF24" s="46" t="n">
+      <c r="AF24" s="19" t="n">
         <f aca="false">AF18+AF23</f>
         <v>14400</v>
       </c>
-      <c r="AG24" s="46" t="n">
+      <c r="AG24" s="19" t="n">
         <f aca="false">AG18+AG23</f>
         <v>15400</v>
       </c>
-      <c r="AH24" s="46" t="n">
+      <c r="AH24" s="19" t="n">
         <f aca="false">AH18+AH23</f>
         <v>15400</v>
       </c>
-      <c r="AI24" s="46" t="n">
+      <c r="AI24" s="19" t="n">
         <f aca="false">AI18+AI23</f>
         <v>15400</v>
       </c>
-      <c r="AJ24" s="46" t="n">
+      <c r="AJ24" s="19" t="n">
         <f aca="false">AJ18+AJ23</f>
         <v>15400</v>
       </c>
-      <c r="AK24" s="46" t="n">
+      <c r="AK24" s="19" t="n">
         <f aca="false">AK18+AK23</f>
         <v>15400</v>
       </c>
-      <c r="AL24" s="46" t="n">
+      <c r="AL24" s="19" t="n">
         <f aca="false">AL18+AL23</f>
         <v>187688</v>
       </c>
-      <c r="AM24" s="46" t="n">
+      <c r="AM24" s="19" t="n">
         <f aca="false">AM18+AM23</f>
         <v>160000</v>
       </c>
-      <c r="AN24" s="46" t="n">
+      <c r="AN24" s="19" t="n">
         <f aca="false">AN18+AN23</f>
         <v>181800</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="43" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="43"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
@@ -10874,29 +12722,29 @@
       <c r="S37" s="27"/>
       <c r="T37" s="27"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
-      <c r="O40" s="43"/>
-      <c r="P40" s="43"/>
-      <c r="Q40" s="43"/>
-      <c r="R40" s="43"/>
-      <c r="S40" s="43"/>
-      <c r="T40" s="43"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">

--- a/income_forecaster.xlsx
+++ b/income_forecaster.xlsx
@@ -19,6 +19,7 @@
     <sheet name="3-Year Growth" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Pipeline &amp; Capacity" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Leverage Scenarios" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Skyright Sale Scenarios" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="598">
   <si>
     <t xml:space="preserve">Income Forecaster — Chance Peare</t>
   </si>
@@ -1593,6 +1594,237 @@
   </si>
   <si>
     <t xml:space="preserve">• None of these models add a sales hire. If you want &gt; $400K, the next hire is probably a part-time SDR, not another Ops person.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright Sale Scenarios — 24-Month View</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 scenarios: A) Stay at NewCo W2  B) Skyright becomes Embedded retainer  C) Clean exit. Equity payment $125K (editable) at sale month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALE EVENT INPUTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale close month (1=Jun26, 5=Oct26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pessimistic: Oct-26.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity payment (gross)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5% stake. Mid-low of $100-200K range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTCG tax rate (federal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15% MFJ for AGI &lt; $583K. Assumes &gt;1-yr holding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity payment (net of tax)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net cash to bank.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright Embedded retainer rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per CLAUDE.md $6K Embedded tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright retainer duration (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pessimistic: 18 months. New owner installs own ops.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA hire month (timed with sale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct-26. Costs $2K/mo + $400 mgmt overhead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA monthly cost (loaded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct cost + management time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright admin automation savings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours saved on Skyright work via VA + Make automation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours/mo on Skyright Embedded (without leverage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded tier standard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours/mo on Skyright Embedded (with VA + automation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective ~21 hrs/mo with VA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO A — Stay at NewCo as W2 COO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright/NewCo W2 ($8K/mo, continues)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity payment (net of LTCG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FW Ops retainer/variable revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO B — Skyright transitions to Embedded retainer (RECOMMENDED PLANNING CASE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright W2 ($8K/mo, ends sale month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright Embedded retainer ($6K/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other FW Ops revenue (clients + variable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA cost (loaded, from sale month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total gross income (B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO C — Clean exit (W2 ends, no Skyright relationship)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright W2 (ends sale month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FW Ops revenue (aggressive growth path)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total gross income (C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO COMPARISON SUMMARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 Gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y2 Gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-Mo Gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active retainers end Y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A — Stay at NewCo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-4 (W2 caps capacity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safe. Equity is bonus. FW Ops grows slowly under W2 demands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B — Skyright as Embedded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-5 (incl. Skyright)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best risk-adjusted. $6K/mo + $106K equity + VA leverage. 18-mo Skyright relationship runway.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C — Clean exit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-6 (aggressive)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$106K equity = 12-15 mo runway. Higher acquisition pace possible. Higher risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITY CHECK (Scenario B with VA + automation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyright Embedded hrs/mo (with VA + automation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced from 35 to ~21 hrs/mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other retainer hrs/mo (3 retainers × 18 hrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active tier ~18 hrs/mo each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales hrs/mo (3 closes/yr target)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Pipeline &amp; Capacity tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin + marketing hrs/mo (with VA help)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA absorbs ~50% of original 52 hrs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL hours/mo required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available hrs/mo (FT post-sale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same FT capacity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive = fits. Negative = need to drop a retainer or hire more.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRATEGIC NOTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Equity tax treatment: assumes LTCG (&gt;1-yr holding). Federal 15% MFJ at AGI &lt;$583K. Verify cost basis with CPA — could be lower than gross if exercised options.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Scenario B (Skyright as Embedded) requires the BUYER to want this arrangement. Most likely if buyer is owner-operator or strategic acquirer who values continuity. PE buyers typically install own ops team — Scenario B unlikely with PE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Skyright Embedded duration (18 months default) is aggressive. Reality: transition retainers often end in 6-12 months once new ops team is in place. Edit Assumptions B10 to test 12-mo case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• VA hired at sale month to absorb Skyright admin/operational work. Make automations + ServiceTitan integrations + report automation = the 40% time savings on Skyright retainer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• In Scenario B, Skyright becomes both an income source AND your capacity sink. If they need 21 hrs/mo, you only have ~159 hrs/mo for everything else. Tight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Scenario C buys runway with equity but requires faster client acquisition to compensate for lost Skyright income. Aggressive growth path assumes 6 active retainers by end Y2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Equity payment goes into Mercury business account if treated as business income, OR personal if treated as capital gains on personal investment. Most likely the latter (personal LTCG). Confirm with CPA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Health insurance: Scenario A keeps Skyright/NewCo employer coverage. B and C trigger ACA ($1,500-2,500/mo family of 6) starting sale month. NOT modeled here — add $18-30K/yr cost to B and C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Tax estimate on Y1 numbers gets complicated: W2 portion withheld, 1099 portion + equity (LTCG) require separate quarterly payments. Cleanup at year-end could be a $10K+ surprise either direction.</t>
   </si>
 </sst>
 </file>
@@ -1792,7 +2024,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="72">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1969,6 +2201,22 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1981,11 +2229,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1993,7 +2237,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2001,11 +2265,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2013,19 +2305,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2882,44 +3166,44 @@
   <dimension ref="A1:F50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
         <v>396</v>
       </c>
@@ -2939,175 +3223,175 @@
         <v>401</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="33" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="44" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="44" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="6" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="36" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="45" t="n">
         <f aca="false">C6*B7</f>
         <v>20</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="42" t="n">
         <f aca="false">D6*0.25</f>
         <v>15</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="6" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B8" s="50" t="n">
+      <c r="B8" s="36" t="n">
         <v>0.35</v>
       </c>
-      <c r="C8" s="51" t="n">
+      <c r="C8" s="45" t="n">
         <f aca="false">C7*B8</f>
         <v>7</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="42" t="n">
         <f aca="false">D7*0.45</f>
         <v>6.75</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="6" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B9" s="50" t="n">
+      <c r="B9" s="36" t="n">
         <v>0.55</v>
       </c>
-      <c r="C9" s="51" t="n">
+      <c r="C9" s="45" t="n">
         <f aca="false">C8*B9</f>
         <v>3.85</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="42" t="n">
         <f aca="false">D8*0.6</f>
         <v>4.05</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="49" t="s">
+      <c r="F9" s="6" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B10" s="50" t="n">
+      <c r="B10" s="36" t="n">
         <v>0.75</v>
       </c>
-      <c r="C10" s="51" t="n">
+      <c r="C10" s="45" t="n">
         <f aca="false">C9*B10</f>
         <v>2.8875</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="42" t="n">
         <f aca="false">D9*0.8</f>
         <v>3.24</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="6" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B11" s="50" t="n">
+      <c r="B11" s="36" t="n">
         <v>0.35</v>
       </c>
-      <c r="C11" s="51" t="n">
+      <c r="C11" s="45" t="n">
         <f aca="false">C10*B11</f>
         <v>1.010625</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="42" t="n">
         <f aca="false">D10*0.4</f>
         <v>1.296</v>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="6" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B14" s="53" t="n">
+      <c r="B14" s="46" t="n">
         <f aca="false">6+(C7*E7)+(C8*E8)+(C9*E9)+(C10*E10)+(C11*E11)</f>
         <v>57.681875</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B15" s="53" t="n">
+      <c r="B15" s="46" t="n">
         <f aca="false">3+(D7*E7)+(D8*E8)+(D9*E9)+(D10*E10)+(D11*E11)</f>
         <v>57.648</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="46" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="30" t="s">
         <v>420</v>
       </c>
@@ -3124,210 +3408,210 @@
         <v>424</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="54" t="n">
+      <c r="B19" s="41" t="n">
         <f aca="false">2*B14</f>
         <v>115.36375</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="41" t="n">
         <f aca="false">2*B15</f>
         <v>115.296</v>
       </c>
-      <c r="D19" s="54" t="n">
+      <c r="D19" s="41" t="n">
         <f aca="false">AVERAGE(B19:C19)</f>
         <v>115.329875</v>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E19" s="42" t="n">
         <f aca="false">D19/48</f>
         <v>2.40270572916667</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="54" t="n">
+      <c r="B20" s="41" t="n">
         <f aca="false">3*B14</f>
         <v>173.045625</v>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="41" t="n">
         <f aca="false">3*B15</f>
         <v>172.944</v>
       </c>
-      <c r="D20" s="54" t="n">
+      <c r="D20" s="41" t="n">
         <f aca="false">AVERAGE(B20:C20)</f>
         <v>172.9948125</v>
       </c>
-      <c r="E20" s="52" t="n">
+      <c r="E20" s="42" t="n">
         <f aca="false">D20/48</f>
         <v>3.60405859375</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="54" t="n">
+      <c r="B21" s="41" t="n">
         <f aca="false">4*B14</f>
         <v>230.7275</v>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="41" t="n">
         <f aca="false">4*B15</f>
         <v>230.592</v>
       </c>
-      <c r="D21" s="54" t="n">
+      <c r="D21" s="41" t="n">
         <f aca="false">AVERAGE(B21:C21)</f>
         <v>230.65975</v>
       </c>
-      <c r="E21" s="52" t="n">
+      <c r="E21" s="42" t="n">
         <f aca="false">D21/48</f>
         <v>4.80541145833333</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="54" t="n">
+      <c r="B22" s="41" t="n">
         <f aca="false">5*B14</f>
         <v>288.409375</v>
       </c>
-      <c r="C22" s="54" t="n">
+      <c r="C22" s="41" t="n">
         <f aca="false">5*B15</f>
         <v>288.24</v>
       </c>
-      <c r="D22" s="54" t="n">
+      <c r="D22" s="41" t="n">
         <f aca="false">AVERAGE(B22:C22)</f>
         <v>288.3246875</v>
       </c>
-      <c r="E22" s="52" t="n">
+      <c r="E22" s="42" t="n">
         <f aca="false">D22/48</f>
         <v>6.00676432291667</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="54" t="n">
+      <c r="B23" s="41" t="n">
         <f aca="false">6*B14</f>
         <v>346.09125</v>
       </c>
-      <c r="C23" s="54" t="n">
+      <c r="C23" s="41" t="n">
         <f aca="false">6*B15</f>
         <v>345.888</v>
       </c>
-      <c r="D23" s="54" t="n">
+      <c r="D23" s="41" t="n">
         <f aca="false">AVERAGE(B23:C23)</f>
         <v>345.989625</v>
       </c>
-      <c r="E23" s="52" t="n">
+      <c r="E23" s="42" t="n">
         <f aca="false">D23/48</f>
         <v>7.2081171875</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B26" s="47" t="n">
+      <c r="B26" s="33" t="n">
         <v>45</v>
       </c>
-      <c r="F26" s="49" t="s">
+      <c r="F26" s="6" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="F27" s="49" t="s">
+      <c r="F27" s="6" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B28" s="51" t="n">
+      <c r="B28" s="45" t="n">
         <f aca="false">B26*B27</f>
         <v>2160</v>
       </c>
-      <c r="F28" s="49" t="s">
+      <c r="F28" s="6" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="6" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B30" s="47" t="n">
+      <c r="B30" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="F30" s="49" t="s">
+      <c r="F30" s="6" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B31" s="47" t="n">
+      <c r="B31" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="6" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B32" s="47" t="n">
+      <c r="B32" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="F32" s="6" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="46" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="30" t="s">
         <v>441</v>
       </c>
@@ -3347,133 +3631,133 @@
         <v>401</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B36" s="47" t="n">
+      <c r="B36" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="C36" s="54" t="n">
+      <c r="C36" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="54" t="n">
+      <c r="D36" s="41" t="n">
         <f aca="false">B36-C36-15-5</f>
         <v>20</v>
       </c>
-      <c r="E36" s="54" t="n">
+      <c r="E36" s="41" t="n">
         <f aca="false">ROUNDDOWN(D36/B29,0)</f>
         <v>1</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B37" s="54" t="n">
+      <c r="B37" s="41" t="n">
         <f aca="false">B28/12</f>
         <v>180</v>
       </c>
-      <c r="C37" s="54" t="n">
+      <c r="C37" s="41" t="n">
         <f aca="false">AVERAGE(D19:D22)/12</f>
         <v>16.8189401041667</v>
       </c>
-      <c r="D37" s="54" t="n">
+      <c r="D37" s="41" t="n">
         <f aca="false">B37-C37-B31-B32</f>
         <v>111.181059895833</v>
       </c>
-      <c r="E37" s="54" t="n">
+      <c r="E37" s="41" t="n">
         <f aca="false">ROUNDDOWN(D37/B29,0)</f>
         <v>6</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B38" s="54" t="n">
+      <c r="B38" s="41" t="n">
         <f aca="false">B28/12</f>
         <v>180</v>
       </c>
-      <c r="C38" s="54" t="n">
+      <c r="C38" s="41" t="n">
         <f aca="false">AVERAGE(D19:D22)/12*0.5</f>
         <v>8.40947005208333</v>
       </c>
-      <c r="D38" s="54" t="n">
+      <c r="D38" s="41" t="n">
         <f aca="false">B38-C38-B31*0.3-B32*0.4</f>
         <v>153.990529947917</v>
       </c>
-      <c r="E38" s="54" t="n">
+      <c r="E38" s="41" t="n">
         <f aca="false">ROUNDDOWN(D38/B29,0)</f>
         <v>8</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B39" s="54" t="n">
+      <c r="B39" s="41" t="n">
         <f aca="false">B28/12</f>
         <v>180</v>
       </c>
-      <c r="C39" s="54" t="n">
+      <c r="C39" s="41" t="n">
         <f aca="false">AVERAGE(D19:D22)/12*0.35</f>
         <v>5.88662903645833</v>
       </c>
-      <c r="D39" s="54" t="n">
+      <c r="D39" s="41" t="n">
         <f aca="false">B39-C39-B31*0.2-B32*0.3</f>
         <v>161.713370963542</v>
       </c>
-      <c r="E39" s="54" t="n">
+      <c r="E39" s="41" t="n">
         <f aca="false">ROUNDDOWN(D39/B29,0)</f>
         <v>8</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B40" s="54" t="n">
+      <c r="B40" s="41" t="n">
         <f aca="false">B28/12</f>
         <v>180</v>
       </c>
-      <c r="C40" s="54" t="n">
+      <c r="C40" s="41" t="n">
         <f aca="false">AVERAGE(D19:D22)/12*0.25</f>
         <v>4.20473502604167</v>
       </c>
-      <c r="D40" s="54" t="n">
+      <c r="D40" s="41" t="n">
         <f aca="false">B40-C40-B31*0.15-B32*0.25</f>
         <v>165.995264973958</v>
       </c>
-      <c r="E40" s="54" t="n">
+      <c r="E40" s="41" t="n">
         <f aca="false">ROUNDDOWN(D40/B29,0)</f>
         <v>9</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="46" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
@@ -3592,161 +3876,161 @@
   <dimension ref="A1:I52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B5" s="55" t="n">
+      <c r="B5" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="6" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B6" s="55" t="n">
+      <c r="B6" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="6" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B7" s="55" t="n">
+      <c r="B7" s="15" t="n">
         <v>4000</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="6" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B8" s="55" t="n">
+      <c r="B8" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="6" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B9" s="55" t="n">
+      <c r="B9" s="15" t="n">
         <v>6583</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="6" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B10" s="55" t="n">
+      <c r="B10" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="6" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B11" s="55" t="n">
+      <c r="B11" s="15" t="n">
         <v>7833</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B12" s="55" t="n">
+      <c r="B12" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="C12" s="49"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B13" s="55" t="n">
+      <c r="B13" s="15" t="n">
         <v>1100</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="6" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30" t="s">
         <v>486</v>
       </c>
@@ -3766,120 +4050,120 @@
         <v>491</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B17" s="56" t="n">
+      <c r="B17" s="47" t="n">
         <f aca="false">IF(180000&lt;=180000,180000-12*$B$13,"OVER CAP")</f>
         <v>166800</v>
       </c>
-      <c r="C17" s="56" t="n">
+      <c r="C17" s="47" t="n">
         <f aca="false">IF(180000&lt;=252000,180000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
         <v>138000</v>
       </c>
-      <c r="D17" s="56" t="n">
+      <c r="D17" s="47" t="n">
         <f aca="false">IF(180000&lt;=288000,180000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
         <v>111600</v>
       </c>
-      <c r="E17" s="56" t="n">
+      <c r="E17" s="47" t="n">
         <f aca="false">IF(180000&lt;=324000,180000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
         <v>83004</v>
       </c>
-      <c r="F17" s="56" t="n">
+      <c r="F17" s="47" t="n">
         <f aca="false">IF(180000&lt;=400000,180000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
         <v>68004</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B18" s="56" t="str">
+      <c r="B18" s="47" t="str">
         <f aca="false">IF(230000&lt;=180000,230000-12*$B$13,"OVER CAP")</f>
         <v>OVER CAP</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="47" t="n">
         <f aca="false">IF(230000&lt;=252000,230000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
         <v>188000</v>
       </c>
-      <c r="D18" s="56" t="n">
+      <c r="D18" s="47" t="n">
         <f aca="false">IF(230000&lt;=288000,230000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
         <v>161600</v>
       </c>
-      <c r="E18" s="56" t="n">
+      <c r="E18" s="47" t="n">
         <f aca="false">IF(230000&lt;=324000,230000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
         <v>133004</v>
       </c>
-      <c r="F18" s="56" t="n">
+      <c r="F18" s="47" t="n">
         <f aca="false">IF(230000&lt;=400000,230000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
         <v>118004</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B19" s="56" t="str">
+      <c r="B19" s="47" t="str">
         <f aca="false">IF(280000&lt;=180000,280000-12*$B$13,"OVER CAP")</f>
         <v>OVER CAP</v>
       </c>
-      <c r="C19" s="56" t="str">
+      <c r="C19" s="47" t="str">
         <f aca="false">IF(280000&lt;=252000,280000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
         <v>OVER CAP</v>
       </c>
-      <c r="D19" s="56" t="n">
+      <c r="D19" s="47" t="n">
         <f aca="false">IF(280000&lt;=288000,280000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
         <v>211600</v>
       </c>
-      <c r="E19" s="56" t="n">
+      <c r="E19" s="47" t="n">
         <f aca="false">IF(280000&lt;=324000,280000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
         <v>183004</v>
       </c>
-      <c r="F19" s="56" t="n">
+      <c r="F19" s="47" t="n">
         <f aca="false">IF(280000&lt;=400000,280000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
         <v>168004</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B20" s="56" t="str">
+      <c r="B20" s="47" t="str">
         <f aca="false">IF(350000&lt;=180000,350000-12*$B$13,"OVER CAP")</f>
         <v>OVER CAP</v>
       </c>
-      <c r="C20" s="56" t="str">
+      <c r="C20" s="47" t="str">
         <f aca="false">IF(350000&lt;=252000,350000-12*($B$5+$B$6)-12*$B$13,"OVER CAP")</f>
         <v>OVER CAP</v>
       </c>
-      <c r="D20" s="56" t="str">
+      <c r="D20" s="47" t="str">
         <f aca="false">IF(350000&lt;=288000,350000-12*($B$7+$B$8)-12*$B$13,"OVER CAP")</f>
         <v>OVER CAP</v>
       </c>
-      <c r="E20" s="56" t="str">
+      <c r="E20" s="47" t="str">
         <f aca="false">IF(350000&lt;=324000,350000-12*($B$9+$B$10)-12*$B$13,"OVER CAP")</f>
         <v>OVER CAP</v>
       </c>
-      <c r="F20" s="56" t="n">
+      <c r="F20" s="47" t="n">
         <f aca="false">IF(350000&lt;=400000,350000-12*($B$11+$B$12)-12*$B$13,"OVER CAP")</f>
         <v>238004</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="46" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
         <v>486</v>
       </c>
@@ -3899,120 +4183,120 @@
         <v>500</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B24" s="57" t="n">
+      <c r="B24" s="18" t="n">
         <f aca="false">B17</f>
         <v>166800</v>
       </c>
-      <c r="C24" s="57" t="n">
+      <c r="C24" s="18" t="n">
         <f aca="false">IFERROR(C17-B17, "")</f>
         <v>-28800</v>
       </c>
-      <c r="D24" s="57" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">IFERROR(D17-B17, "")</f>
         <v>-55200</v>
       </c>
-      <c r="E24" s="57" t="n">
+      <c r="E24" s="18" t="n">
         <f aca="false">IFERROR(E17-B17, "")</f>
         <v>-83796</v>
       </c>
-      <c r="F24" s="57" t="n">
+      <c r="F24" s="18" t="n">
         <f aca="false">IFERROR(F17-B17, "")</f>
         <v>-98796</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B25" s="57" t="str">
+      <c r="B25" s="18" t="str">
         <f aca="false">B18</f>
         <v>OVER CAP</v>
       </c>
-      <c r="C25" s="57" t="str">
+      <c r="C25" s="18" t="str">
         <f aca="false">IFERROR(C18-B18, "")</f>
         <v/>
       </c>
-      <c r="D25" s="57" t="str">
+      <c r="D25" s="18" t="str">
         <f aca="false">IFERROR(D18-B18, "")</f>
         <v/>
       </c>
-      <c r="E25" s="57" t="str">
+      <c r="E25" s="18" t="str">
         <f aca="false">IFERROR(E18-B18, "")</f>
         <v/>
       </c>
-      <c r="F25" s="57" t="str">
+      <c r="F25" s="18" t="str">
         <f aca="false">IFERROR(F18-B18, "")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B26" s="57" t="str">
+      <c r="B26" s="18" t="str">
         <f aca="false">B19</f>
         <v>OVER CAP</v>
       </c>
-      <c r="C26" s="57" t="str">
+      <c r="C26" s="18" t="str">
         <f aca="false">IFERROR(C19-B19, "")</f>
         <v/>
       </c>
-      <c r="D26" s="57" t="str">
+      <c r="D26" s="18" t="str">
         <f aca="false">IFERROR(D19-B19, "")</f>
         <v/>
       </c>
-      <c r="E26" s="57" t="str">
+      <c r="E26" s="18" t="str">
         <f aca="false">IFERROR(E19-B19, "")</f>
         <v/>
       </c>
-      <c r="F26" s="57" t="str">
+      <c r="F26" s="18" t="str">
         <f aca="false">IFERROR(F19-B19, "")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B27" s="57" t="str">
+      <c r="B27" s="18" t="str">
         <f aca="false">B20</f>
         <v>OVER CAP</v>
       </c>
-      <c r="C27" s="57" t="str">
+      <c r="C27" s="18" t="str">
         <f aca="false">IFERROR(C20-B20, "")</f>
         <v/>
       </c>
-      <c r="D27" s="57" t="str">
+      <c r="D27" s="18" t="str">
         <f aca="false">IFERROR(D20-B20, "")</f>
         <v/>
       </c>
-      <c r="E27" s="57" t="str">
+      <c r="E27" s="18" t="str">
         <f aca="false">IFERROR(E20-B20, "")</f>
         <v/>
       </c>
-      <c r="F27" s="57" t="str">
+      <c r="F27" s="18" t="str">
         <f aca="false">IFERROR(F20-B20, "")</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="46" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="s">
         <v>502</v>
       </c>
@@ -4026,86 +4310,86 @@
         <v>505</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B32" s="58" t="n">
+      <c r="B32" s="38" t="n">
         <f aca="false">12*($B$5+$B$6)</f>
         <v>28800</v>
       </c>
-      <c r="C32" s="58" t="n">
+      <c r="C32" s="38" t="n">
         <f aca="false">B32+600*ROUNDUP(B32/36000,0)</f>
         <v>29400</v>
       </c>
-      <c r="D32" s="52" t="n">
+      <c r="D32" s="42" t="n">
         <f aca="false">ROUNDUP(B32/36000,1)</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B33" s="58" t="n">
+      <c r="B33" s="38" t="n">
         <f aca="false">12*($B$7+$B$8)</f>
         <v>55200</v>
       </c>
-      <c r="C33" s="58" t="n">
+      <c r="C33" s="38" t="n">
         <f aca="false">B33+600*ROUNDUP(B33/36000,0)</f>
         <v>56400</v>
       </c>
-      <c r="D33" s="52" t="n">
+      <c r="D33" s="42" t="n">
         <f aca="false">ROUNDUP(B33/36000,1)</f>
         <v>1.6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B34" s="58" t="n">
+      <c r="B34" s="38" t="n">
         <f aca="false">12*($B$9+$B$10)</f>
         <v>83796</v>
       </c>
-      <c r="C34" s="58" t="n">
+      <c r="C34" s="38" t="n">
         <f aca="false">B34+600*ROUNDUP(B34/36000,0)</f>
         <v>85596</v>
       </c>
-      <c r="D34" s="52" t="n">
+      <c r="D34" s="42" t="n">
         <f aca="false">ROUNDUP(B34/36000,1)</f>
         <v>2.4</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B35" s="58" t="n">
+      <c r="B35" s="38" t="n">
         <f aca="false">12*($B$11+$B$12)</f>
         <v>98796</v>
       </c>
-      <c r="C35" s="58" t="n">
+      <c r="C35" s="38" t="n">
         <f aca="false">B35+600*ROUNDUP(B35/36000,0)</f>
         <v>100596</v>
       </c>
-      <c r="D35" s="52" t="n">
+      <c r="D35" s="42" t="n">
         <f aca="false">ROUNDUP(B35/36000,1)</f>
         <v>2.8</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="46" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
@@ -4120,7 +4404,7 @@
       <c r="H39" s="27"/>
       <c r="I39" s="27"/>
     </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
         <v>510</v>
       </c>
@@ -4146,7 +4430,7 @@
       <c r="H41" s="27"/>
       <c r="I41" s="27"/>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="27" t="s">
         <v>512</v>
       </c>
@@ -4159,7 +4443,7 @@
       <c r="H42" s="27"/>
       <c r="I42" s="27"/>
     </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
         <v>513</v>
       </c>
@@ -4172,20 +4456,20 @@
       <c r="H43" s="27"/>
       <c r="I43" s="27"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="46" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="46"/>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
         <v>515</v>
       </c>
@@ -4224,7 +4508,7 @@
       <c r="H49" s="27"/>
       <c r="I49" s="27"/>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
         <v>518</v>
       </c>
@@ -4237,7 +4521,7 @@
       <c r="H50" s="27"/>
       <c r="I50" s="27"/>
     </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
         <v>519</v>
       </c>
@@ -4284,6 +4568,2339 @@
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="A51:I51"/>
     <mergeCell ref="A52:I52"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AB64"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="48" t="s">
+        <v>521</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="50" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="B5" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>526</v>
+      </c>
+      <c r="B6" s="53" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B7" s="54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B8" s="55" t="n">
+        <f aca="false">B6*(1-B7)</f>
+        <v>106250</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="B9" s="56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B10" s="51" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B11" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>538</v>
+      </c>
+      <c r="B12" s="56" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="B13" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="B14" s="58" t="n">
+        <v>35</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="B15" s="59" t="n">
+        <f aca="false">B14*(1-B13)</f>
+        <v>21</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="60" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="M17" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="N17" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="O17" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="P17" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q17" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="R17" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="S17" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="T17" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="U17" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="V17" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="W17" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="X17" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y17" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z17" s="60" t="s">
+        <v>345</v>
+      </c>
+      <c r="AA17" s="60" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="50" t="s">
+        <v>546</v>
+      </c>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="50"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="50"/>
+      <c r="Y19" s="50"/>
+      <c r="Z19" s="50"/>
+      <c r="AA19" s="50"/>
+      <c r="AB19" s="50"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="B20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="P20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Q20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="V20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="X20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y20" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z20" s="55" t="n">
+        <f aca="false">SUM(B20:M20)</f>
+        <v>96000</v>
+      </c>
+      <c r="AA20" s="55" t="n">
+        <f aca="false">SUM(N20:Y20)</f>
+        <v>96000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="B21" s="61" t="n">
+        <f aca="false">IF(1=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="61" t="n">
+        <f aca="false">IF(2=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="61" t="n">
+        <f aca="false">IF(3=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="61" t="n">
+        <f aca="false">IF(4=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="61" t="n">
+        <f aca="false">IF(5=$B$5,$B$8,0)</f>
+        <v>106250</v>
+      </c>
+      <c r="G21" s="61" t="n">
+        <f aca="false">IF(6=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="61" t="n">
+        <f aca="false">IF(7=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="61" t="n">
+        <f aca="false">IF(8=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="61" t="n">
+        <f aca="false">IF(9=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="61" t="n">
+        <f aca="false">IF(10=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="61" t="n">
+        <f aca="false">IF(11=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="61" t="n">
+        <f aca="false">IF(12=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="61" t="n">
+        <f aca="false">IF(13=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="61" t="n">
+        <f aca="false">IF(14=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="61" t="n">
+        <f aca="false">IF(15=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="61" t="n">
+        <f aca="false">IF(16=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="61" t="n">
+        <f aca="false">IF(17=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="61" t="n">
+        <f aca="false">IF(18=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="61" t="n">
+        <f aca="false">IF(19=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U21" s="61" t="n">
+        <f aca="false">IF(20=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V21" s="61" t="n">
+        <f aca="false">IF(21=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W21" s="61" t="n">
+        <f aca="false">IF(22=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="61" t="n">
+        <f aca="false">IF(23=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="61" t="n">
+        <f aca="false">IF(24=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="55" t="n">
+        <f aca="false">SUM(B21:M21)</f>
+        <v>106250</v>
+      </c>
+      <c r="AA21" s="55" t="n">
+        <f aca="false">SUM(N21:Y21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>549</v>
+      </c>
+      <c r="B22" s="61" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C22" s="61" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="61" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E22" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F22" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G22" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H22" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I22" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J22" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="K22" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="L22" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="M22" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="N22" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="O22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="P22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Q22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="R22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="S22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="T22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="U22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="V22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="W22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="X22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Y22" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Z22" s="55" t="n">
+        <f aca="false">SUM(B22:M22)</f>
+        <v>98000</v>
+      </c>
+      <c r="AA22" s="55" t="n">
+        <f aca="false">SUM(N22:Y22)</f>
+        <v>159000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" s="63" t="n">
+        <f aca="false">B20+B21+B22</f>
+        <v>11500</v>
+      </c>
+      <c r="C23" s="63" t="n">
+        <f aca="false">C20+C21+C22</f>
+        <v>13000</v>
+      </c>
+      <c r="D23" s="63" t="n">
+        <f aca="false">D20+D21+D22</f>
+        <v>13000</v>
+      </c>
+      <c r="E23" s="63" t="n">
+        <f aca="false">E20+E21+E22</f>
+        <v>16000</v>
+      </c>
+      <c r="F23" s="63" t="n">
+        <f aca="false">F20+F21+F22</f>
+        <v>122250</v>
+      </c>
+      <c r="G23" s="63" t="n">
+        <f aca="false">G20+G21+G22</f>
+        <v>16000</v>
+      </c>
+      <c r="H23" s="63" t="n">
+        <f aca="false">H20+H21+H22</f>
+        <v>16000</v>
+      </c>
+      <c r="I23" s="63" t="n">
+        <f aca="false">I20+I21+I22</f>
+        <v>18500</v>
+      </c>
+      <c r="J23" s="63" t="n">
+        <f aca="false">J20+J21+J22</f>
+        <v>18500</v>
+      </c>
+      <c r="K23" s="63" t="n">
+        <f aca="false">K20+K21+K22</f>
+        <v>18500</v>
+      </c>
+      <c r="L23" s="63" t="n">
+        <f aca="false">L20+L21+L22</f>
+        <v>18500</v>
+      </c>
+      <c r="M23" s="63" t="n">
+        <f aca="false">M20+M21+M22</f>
+        <v>18500</v>
+      </c>
+      <c r="N23" s="63" t="n">
+        <f aca="false">N20+N21+N22</f>
+        <v>18500</v>
+      </c>
+      <c r="O23" s="63" t="n">
+        <f aca="false">O20+O21+O22</f>
+        <v>21500</v>
+      </c>
+      <c r="P23" s="63" t="n">
+        <f aca="false">P20+P21+P22</f>
+        <v>21500</v>
+      </c>
+      <c r="Q23" s="63" t="n">
+        <f aca="false">Q20+Q21+Q22</f>
+        <v>21500</v>
+      </c>
+      <c r="R23" s="63" t="n">
+        <f aca="false">R20+R21+R22</f>
+        <v>21500</v>
+      </c>
+      <c r="S23" s="63" t="n">
+        <f aca="false">S20+S21+S22</f>
+        <v>21500</v>
+      </c>
+      <c r="T23" s="63" t="n">
+        <f aca="false">T20+T21+T22</f>
+        <v>21500</v>
+      </c>
+      <c r="U23" s="63" t="n">
+        <f aca="false">U20+U21+U22</f>
+        <v>21500</v>
+      </c>
+      <c r="V23" s="63" t="n">
+        <f aca="false">V20+V21+V22</f>
+        <v>21500</v>
+      </c>
+      <c r="W23" s="63" t="n">
+        <f aca="false">W20+W21+W22</f>
+        <v>21500</v>
+      </c>
+      <c r="X23" s="63" t="n">
+        <f aca="false">X20+X21+X22</f>
+        <v>21500</v>
+      </c>
+      <c r="Y23" s="63" t="n">
+        <f aca="false">Y20+Y21+Y22</f>
+        <v>21500</v>
+      </c>
+      <c r="Z23" s="63" t="n">
+        <f aca="false">SUM(B23:M23)</f>
+        <v>300250</v>
+      </c>
+      <c r="AA23" s="63" t="n">
+        <f aca="false">SUM(N23:Y23)</f>
+        <v>255000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="50" t="s">
+        <v>550</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="50"/>
+      <c r="O25" s="50"/>
+      <c r="P25" s="50"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="50"/>
+      <c r="S25" s="50"/>
+      <c r="T25" s="50"/>
+      <c r="U25" s="50"/>
+      <c r="V25" s="50"/>
+      <c r="W25" s="50"/>
+      <c r="X25" s="50"/>
+      <c r="Y25" s="50"/>
+      <c r="Z25" s="50"/>
+      <c r="AA25" s="50"/>
+      <c r="AB25" s="50"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="B26" s="61" t="n">
+        <f aca="false">IF(1&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="C26" s="61" t="n">
+        <f aca="false">IF(2&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="D26" s="61" t="n">
+        <f aca="false">IF(3&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E26" s="61" t="n">
+        <f aca="false">IF(4&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="F26" s="61" t="n">
+        <f aca="false">IF(5&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="61" t="n">
+        <f aca="false">IF(6&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="61" t="n">
+        <f aca="false">IF(7&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="61" t="n">
+        <f aca="false">IF(8&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="61" t="n">
+        <f aca="false">IF(9&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="61" t="n">
+        <f aca="false">IF(10&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="61" t="n">
+        <f aca="false">IF(11&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="61" t="n">
+        <f aca="false">IF(12&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="61" t="n">
+        <f aca="false">IF(13&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="61" t="n">
+        <f aca="false">IF(14&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="61" t="n">
+        <f aca="false">IF(15&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="61" t="n">
+        <f aca="false">IF(16&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="61" t="n">
+        <f aca="false">IF(17&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="61" t="n">
+        <f aca="false">IF(18&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T26" s="61" t="n">
+        <f aca="false">IF(19&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U26" s="61" t="n">
+        <f aca="false">IF(20&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="61" t="n">
+        <f aca="false">IF(21&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W26" s="61" t="n">
+        <f aca="false">IF(22&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X26" s="61" t="n">
+        <f aca="false">IF(23&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="61" t="n">
+        <f aca="false">IF(24&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="64" t="n">
+        <f aca="false">SUM(B26:M26)</f>
+        <v>32000</v>
+      </c>
+      <c r="AA26" s="64" t="n">
+        <f aca="false">SUM(N26:Y26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="B27" s="61" t="n">
+        <f aca="false">IF(1=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="61" t="n">
+        <f aca="false">IF(2=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="61" t="n">
+        <f aca="false">IF(3=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="61" t="n">
+        <f aca="false">IF(4=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="61" t="n">
+        <f aca="false">IF(5=$B$5,$B$8,0)</f>
+        <v>106250</v>
+      </c>
+      <c r="G27" s="61" t="n">
+        <f aca="false">IF(6=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="61" t="n">
+        <f aca="false">IF(7=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="61" t="n">
+        <f aca="false">IF(8=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="61" t="n">
+        <f aca="false">IF(9=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="61" t="n">
+        <f aca="false">IF(10=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="61" t="n">
+        <f aca="false">IF(11=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="61" t="n">
+        <f aca="false">IF(12=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="61" t="n">
+        <f aca="false">IF(13=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="61" t="n">
+        <f aca="false">IF(14=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="61" t="n">
+        <f aca="false">IF(15=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="61" t="n">
+        <f aca="false">IF(16=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="61" t="n">
+        <f aca="false">IF(17=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="61" t="n">
+        <f aca="false">IF(18=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T27" s="61" t="n">
+        <f aca="false">IF(19=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U27" s="61" t="n">
+        <f aca="false">IF(20=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V27" s="61" t="n">
+        <f aca="false">IF(21=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W27" s="61" t="n">
+        <f aca="false">IF(22=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X27" s="61" t="n">
+        <f aca="false">IF(23=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="61" t="n">
+        <f aca="false">IF(24=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="64" t="n">
+        <f aca="false">SUM(B27:M27)</f>
+        <v>106250</v>
+      </c>
+      <c r="AA27" s="64" t="n">
+        <f aca="false">SUM(N27:Y27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="B28" s="61" t="n">
+        <f aca="false">IF(AND(1&gt;$B$5,1&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="61" t="n">
+        <f aca="false">IF(AND(2&gt;$B$5,2&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="61" t="n">
+        <f aca="false">IF(AND(3&gt;$B$5,3&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="61" t="n">
+        <f aca="false">IF(AND(4&gt;$B$5,4&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="61" t="n">
+        <f aca="false">IF(AND(5&gt;$B$5,5&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="61" t="n">
+        <f aca="false">IF(AND(6&gt;$B$5,6&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="H28" s="61" t="n">
+        <f aca="false">IF(AND(7&gt;$B$5,7&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="I28" s="61" t="n">
+        <f aca="false">IF(AND(8&gt;$B$5,8&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="J28" s="61" t="n">
+        <f aca="false">IF(AND(9&gt;$B$5,9&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="K28" s="61" t="n">
+        <f aca="false">IF(AND(10&gt;$B$5,10&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="L28" s="61" t="n">
+        <f aca="false">IF(AND(11&gt;$B$5,11&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="M28" s="61" t="n">
+        <f aca="false">IF(AND(12&gt;$B$5,12&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="N28" s="61" t="n">
+        <f aca="false">IF(AND(13&gt;$B$5,13&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="O28" s="61" t="n">
+        <f aca="false">IF(AND(14&gt;$B$5,14&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="P28" s="61" t="n">
+        <f aca="false">IF(AND(15&gt;$B$5,15&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="Q28" s="61" t="n">
+        <f aca="false">IF(AND(16&gt;$B$5,16&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="R28" s="61" t="n">
+        <f aca="false">IF(AND(17&gt;$B$5,17&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="S28" s="61" t="n">
+        <f aca="false">IF(AND(18&gt;$B$5,18&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="T28" s="61" t="n">
+        <f aca="false">IF(AND(19&gt;$B$5,19&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="U28" s="61" t="n">
+        <f aca="false">IF(AND(20&gt;$B$5,20&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="V28" s="61" t="n">
+        <f aca="false">IF(AND(21&gt;$B$5,21&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="W28" s="61" t="n">
+        <f aca="false">IF(AND(22&gt;$B$5,22&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="X28" s="61" t="n">
+        <f aca="false">IF(AND(23&gt;$B$5,23&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="Y28" s="61" t="n">
+        <f aca="false">IF(AND(24&gt;$B$5,24&lt;=$B$5+$B$10),$B$9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="64" t="n">
+        <f aca="false">SUM(B28:M28)</f>
+        <v>42000</v>
+      </c>
+      <c r="AA28" s="64" t="n">
+        <f aca="false">SUM(N28:Y28)</f>
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="B29" s="61" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C29" s="61" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D29" s="61" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E29" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F29" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G29" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H29" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I29" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J29" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="K29" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="L29" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="M29" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="N29" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="O29" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="P29" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Q29" s="61" t="n">
+        <v>16500</v>
+      </c>
+      <c r="R29" s="61" t="n">
+        <v>16500</v>
+      </c>
+      <c r="S29" s="61" t="n">
+        <v>16500</v>
+      </c>
+      <c r="T29" s="61" t="n">
+        <v>16500</v>
+      </c>
+      <c r="U29" s="61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="V29" s="61" t="n">
+        <v>17000</v>
+      </c>
+      <c r="W29" s="61" t="n">
+        <v>17000</v>
+      </c>
+      <c r="X29" s="61" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Y29" s="61" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Z29" s="64" t="n">
+        <f aca="false">SUM(B29:M29)</f>
+        <v>104000</v>
+      </c>
+      <c r="AA29" s="64" t="n">
+        <f aca="false">SUM(N29:Y29)</f>
+        <v>188500</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="B30" s="64" t="n">
+        <f aca="false">IF(1&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="64" t="n">
+        <f aca="false">IF(2&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="64" t="n">
+        <f aca="false">IF(3&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="64" t="n">
+        <f aca="false">IF(4&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="64" t="n">
+        <f aca="false">IF(5&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="G30" s="64" t="n">
+        <f aca="false">IF(6&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="H30" s="64" t="n">
+        <f aca="false">IF(7&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="I30" s="64" t="n">
+        <f aca="false">IF(8&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="J30" s="64" t="n">
+        <f aca="false">IF(9&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="K30" s="64" t="n">
+        <f aca="false">IF(10&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="L30" s="64" t="n">
+        <f aca="false">IF(11&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="M30" s="64" t="n">
+        <f aca="false">IF(12&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="N30" s="64" t="n">
+        <f aca="false">IF(13&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="O30" s="64" t="n">
+        <f aca="false">IF(14&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="P30" s="64" t="n">
+        <f aca="false">IF(15&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="Q30" s="64" t="n">
+        <f aca="false">IF(16&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="R30" s="64" t="n">
+        <f aca="false">IF(17&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="S30" s="64" t="n">
+        <f aca="false">IF(18&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="T30" s="64" t="n">
+        <f aca="false">IF(19&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="U30" s="64" t="n">
+        <f aca="false">IF(20&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="V30" s="64" t="n">
+        <f aca="false">IF(21&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="W30" s="64" t="n">
+        <f aca="false">IF(22&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="X30" s="64" t="n">
+        <f aca="false">IF(23&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="Y30" s="64" t="n">
+        <f aca="false">IF(24&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="Z30" s="64" t="n">
+        <f aca="false">SUM(B30:M30)</f>
+        <v>-19200</v>
+      </c>
+      <c r="AA30" s="64" t="n">
+        <f aca="false">SUM(N30:Y30)</f>
+        <v>-28800</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="62" t="s">
+        <v>555</v>
+      </c>
+      <c r="B31" s="65" t="n">
+        <f aca="false">B26+B27+B28+B29+B30</f>
+        <v>11500</v>
+      </c>
+      <c r="C31" s="65" t="n">
+        <f aca="false">C26+C27+C28+C29+C30</f>
+        <v>13000</v>
+      </c>
+      <c r="D31" s="65" t="n">
+        <f aca="false">D26+D27+D28+D29+D30</f>
+        <v>13000</v>
+      </c>
+      <c r="E31" s="65" t="n">
+        <f aca="false">E26+E27+E28+E29+E30</f>
+        <v>16000</v>
+      </c>
+      <c r="F31" s="65" t="n">
+        <f aca="false">F26+F27+F28+F29+F30</f>
+        <v>111850</v>
+      </c>
+      <c r="G31" s="65" t="n">
+        <f aca="false">G26+G27+G28+G29+G30</f>
+        <v>11600</v>
+      </c>
+      <c r="H31" s="65" t="n">
+        <f aca="false">H26+H27+H28+H29+H30</f>
+        <v>11600</v>
+      </c>
+      <c r="I31" s="65" t="n">
+        <f aca="false">I26+I27+I28+I29+I30</f>
+        <v>14100</v>
+      </c>
+      <c r="J31" s="65" t="n">
+        <f aca="false">J26+J27+J28+J29+J30</f>
+        <v>14100</v>
+      </c>
+      <c r="K31" s="65" t="n">
+        <f aca="false">K26+K27+K28+K29+K30</f>
+        <v>14100</v>
+      </c>
+      <c r="L31" s="65" t="n">
+        <f aca="false">L26+L27+L28+L29+L30</f>
+        <v>17100</v>
+      </c>
+      <c r="M31" s="65" t="n">
+        <f aca="false">M26+M27+M28+M29+M30</f>
+        <v>17100</v>
+      </c>
+      <c r="N31" s="65" t="n">
+        <f aca="false">N26+N27+N28+N29+N30</f>
+        <v>17100</v>
+      </c>
+      <c r="O31" s="65" t="n">
+        <f aca="false">O26+O27+O28+O29+O30</f>
+        <v>17100</v>
+      </c>
+      <c r="P31" s="65" t="n">
+        <f aca="false">P26+P27+P28+P29+P30</f>
+        <v>17100</v>
+      </c>
+      <c r="Q31" s="65" t="n">
+        <f aca="false">Q26+Q27+Q28+Q29+Q30</f>
+        <v>20100</v>
+      </c>
+      <c r="R31" s="65" t="n">
+        <f aca="false">R26+R27+R28+R29+R30</f>
+        <v>20100</v>
+      </c>
+      <c r="S31" s="65" t="n">
+        <f aca="false">S26+S27+S28+S29+S30</f>
+        <v>20100</v>
+      </c>
+      <c r="T31" s="65" t="n">
+        <f aca="false">T26+T27+T28+T29+T30</f>
+        <v>20100</v>
+      </c>
+      <c r="U31" s="65" t="n">
+        <f aca="false">U26+U27+U28+U29+U30</f>
+        <v>23600</v>
+      </c>
+      <c r="V31" s="65" t="n">
+        <f aca="false">V26+V27+V28+V29+V30</f>
+        <v>20600</v>
+      </c>
+      <c r="W31" s="65" t="n">
+        <f aca="false">W26+W27+W28+W29+W30</f>
+        <v>20600</v>
+      </c>
+      <c r="X31" s="65" t="n">
+        <f aca="false">X26+X27+X28+X29+X30</f>
+        <v>17600</v>
+      </c>
+      <c r="Y31" s="65" t="n">
+        <f aca="false">Y26+Y27+Y28+Y29+Y30</f>
+        <v>11600</v>
+      </c>
+      <c r="Z31" s="65" t="n">
+        <f aca="false">SUM(B31:M31)</f>
+        <v>265050</v>
+      </c>
+      <c r="AA31" s="65" t="n">
+        <f aca="false">SUM(N31:Y31)</f>
+        <v>225700</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="50" t="s">
+        <v>556</v>
+      </c>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="50"/>
+      <c r="W33" s="50"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="50"/>
+      <c r="AA33" s="50"/>
+      <c r="AB33" s="50"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="B34" s="61" t="n">
+        <f aca="false">IF(1&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="C34" s="61" t="n">
+        <f aca="false">IF(2&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="D34" s="61" t="n">
+        <f aca="false">IF(3&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="E34" s="61" t="n">
+        <f aca="false">IF(4&lt;$B$5,8000,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="F34" s="61" t="n">
+        <f aca="false">IF(5&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="61" t="n">
+        <f aca="false">IF(6&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="61" t="n">
+        <f aca="false">IF(7&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="61" t="n">
+        <f aca="false">IF(8&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="61" t="n">
+        <f aca="false">IF(9&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="61" t="n">
+        <f aca="false">IF(10&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="61" t="n">
+        <f aca="false">IF(11&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="61" t="n">
+        <f aca="false">IF(12&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="61" t="n">
+        <f aca="false">IF(13&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="61" t="n">
+        <f aca="false">IF(14&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="61" t="n">
+        <f aca="false">IF(15&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="61" t="n">
+        <f aca="false">IF(16&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="61" t="n">
+        <f aca="false">IF(17&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S34" s="61" t="n">
+        <f aca="false">IF(18&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T34" s="61" t="n">
+        <f aca="false">IF(19&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U34" s="61" t="n">
+        <f aca="false">IF(20&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V34" s="61" t="n">
+        <f aca="false">IF(21&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="61" t="n">
+        <f aca="false">IF(22&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X34" s="61" t="n">
+        <f aca="false">IF(23&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="61" t="n">
+        <f aca="false">IF(24&lt;$B$5,8000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="64" t="n">
+        <f aca="false">SUM(B34:M34)</f>
+        <v>32000</v>
+      </c>
+      <c r="AA34" s="64" t="n">
+        <f aca="false">SUM(N34:Y34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="B35" s="61" t="n">
+        <f aca="false">IF(1=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="61" t="n">
+        <f aca="false">IF(2=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="61" t="n">
+        <f aca="false">IF(3=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="61" t="n">
+        <f aca="false">IF(4=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="61" t="n">
+        <f aca="false">IF(5=$B$5,$B$8,0)</f>
+        <v>106250</v>
+      </c>
+      <c r="G35" s="61" t="n">
+        <f aca="false">IF(6=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="61" t="n">
+        <f aca="false">IF(7=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="61" t="n">
+        <f aca="false">IF(8=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="61" t="n">
+        <f aca="false">IF(9=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="61" t="n">
+        <f aca="false">IF(10=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="61" t="n">
+        <f aca="false">IF(11=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="61" t="n">
+        <f aca="false">IF(12=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="61" t="n">
+        <f aca="false">IF(13=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="61" t="n">
+        <f aca="false">IF(14=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="61" t="n">
+        <f aca="false">IF(15=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="61" t="n">
+        <f aca="false">IF(16=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="61" t="n">
+        <f aca="false">IF(17=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S35" s="61" t="n">
+        <f aca="false">IF(18=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T35" s="61" t="n">
+        <f aca="false">IF(19=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U35" s="61" t="n">
+        <f aca="false">IF(20=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V35" s="61" t="n">
+        <f aca="false">IF(21=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W35" s="61" t="n">
+        <f aca="false">IF(22=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X35" s="61" t="n">
+        <f aca="false">IF(23=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="61" t="n">
+        <f aca="false">IF(24=$B$5,$B$8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="64" t="n">
+        <f aca="false">SUM(B35:M35)</f>
+        <v>106250</v>
+      </c>
+      <c r="AA35" s="64" t="n">
+        <f aca="false">SUM(N35:Y35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="B36" s="61" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C36" s="61" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D36" s="61" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E36" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F36" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G36" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H36" s="61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I36" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J36" s="61" t="n">
+        <v>10500</v>
+      </c>
+      <c r="K36" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="L36" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="M36" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="N36" s="61" t="n">
+        <v>13500</v>
+      </c>
+      <c r="O36" s="61" t="n">
+        <v>16500</v>
+      </c>
+      <c r="P36" s="61" t="n">
+        <v>16500</v>
+      </c>
+      <c r="Q36" s="61" t="n">
+        <v>16500</v>
+      </c>
+      <c r="R36" s="61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S36" s="61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T36" s="61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="U36" s="61" t="n">
+        <v>23000</v>
+      </c>
+      <c r="V36" s="61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="W36" s="61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="X36" s="61" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Y36" s="61" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Z36" s="64" t="n">
+        <f aca="false">SUM(B36:M36)</f>
+        <v>107000</v>
+      </c>
+      <c r="AA36" s="64" t="n">
+        <f aca="false">SUM(N36:Y36)</f>
+        <v>227000</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="B37" s="64" t="n">
+        <f aca="false">IF(1&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="64" t="n">
+        <f aca="false">IF(2&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="64" t="n">
+        <f aca="false">IF(3&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="64" t="n">
+        <f aca="false">IF(4&gt;=$B$11,-$B$12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="64" t="n">
+        <f aca="false">IF(5&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="G37" s="64" t="n">
+        <f aca="false">IF(6&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="H37" s="64" t="n">
+        <f aca="false">IF(7&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="I37" s="64" t="n">
+        <f aca="false">IF(8&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="J37" s="64" t="n">
+        <f aca="false">IF(9&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="K37" s="64" t="n">
+        <f aca="false">IF(10&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="L37" s="64" t="n">
+        <f aca="false">IF(11&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="M37" s="64" t="n">
+        <f aca="false">IF(12&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="N37" s="64" t="n">
+        <f aca="false">IF(13&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="O37" s="64" t="n">
+        <f aca="false">IF(14&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="P37" s="64" t="n">
+        <f aca="false">IF(15&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="Q37" s="64" t="n">
+        <f aca="false">IF(16&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="R37" s="64" t="n">
+        <f aca="false">IF(17&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="S37" s="64" t="n">
+        <f aca="false">IF(18&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="T37" s="64" t="n">
+        <f aca="false">IF(19&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="U37" s="64" t="n">
+        <f aca="false">IF(20&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="V37" s="64" t="n">
+        <f aca="false">IF(21&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="W37" s="64" t="n">
+        <f aca="false">IF(22&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="X37" s="64" t="n">
+        <f aca="false">IF(23&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="Y37" s="64" t="n">
+        <f aca="false">IF(24&gt;=$B$11,-$B$12,0)</f>
+        <v>-2400</v>
+      </c>
+      <c r="Z37" s="64" t="n">
+        <f aca="false">SUM(B37:M37)</f>
+        <v>-19200</v>
+      </c>
+      <c r="AA37" s="64" t="n">
+        <f aca="false">SUM(N37:Y37)</f>
+        <v>-28800</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="62" t="s">
+        <v>559</v>
+      </c>
+      <c r="B38" s="65" t="n">
+        <f aca="false">B34+B35+B36+B37</f>
+        <v>11500</v>
+      </c>
+      <c r="C38" s="65" t="n">
+        <f aca="false">C34+C35+C36+C37</f>
+        <v>13000</v>
+      </c>
+      <c r="D38" s="65" t="n">
+        <f aca="false">D34+D35+D36+D37</f>
+        <v>13000</v>
+      </c>
+      <c r="E38" s="65" t="n">
+        <f aca="false">E34+E35+E36+E37</f>
+        <v>16000</v>
+      </c>
+      <c r="F38" s="65" t="n">
+        <f aca="false">F34+F35+F36+F37</f>
+        <v>111850</v>
+      </c>
+      <c r="G38" s="65" t="n">
+        <f aca="false">G34+G35+G36+G37</f>
+        <v>5600</v>
+      </c>
+      <c r="H38" s="65" t="n">
+        <f aca="false">H34+H35+H36+H37</f>
+        <v>5600</v>
+      </c>
+      <c r="I38" s="65" t="n">
+        <f aca="false">I34+I35+I36+I37</f>
+        <v>8100</v>
+      </c>
+      <c r="J38" s="65" t="n">
+        <f aca="false">J34+J35+J36+J37</f>
+        <v>8100</v>
+      </c>
+      <c r="K38" s="65" t="n">
+        <f aca="false">K34+K35+K36+K37</f>
+        <v>11100</v>
+      </c>
+      <c r="L38" s="65" t="n">
+        <f aca="false">L34+L35+L36+L37</f>
+        <v>11100</v>
+      </c>
+      <c r="M38" s="65" t="n">
+        <f aca="false">M34+M35+M36+M37</f>
+        <v>11100</v>
+      </c>
+      <c r="N38" s="65" t="n">
+        <f aca="false">N34+N35+N36+N37</f>
+        <v>11100</v>
+      </c>
+      <c r="O38" s="65" t="n">
+        <f aca="false">O34+O35+O36+O37</f>
+        <v>14100</v>
+      </c>
+      <c r="P38" s="65" t="n">
+        <f aca="false">P34+P35+P36+P37</f>
+        <v>14100</v>
+      </c>
+      <c r="Q38" s="65" t="n">
+        <f aca="false">Q34+Q35+Q36+Q37</f>
+        <v>14100</v>
+      </c>
+      <c r="R38" s="65" t="n">
+        <f aca="false">R34+R35+R36+R37</f>
+        <v>17600</v>
+      </c>
+      <c r="S38" s="65" t="n">
+        <f aca="false">S34+S35+S36+S37</f>
+        <v>17600</v>
+      </c>
+      <c r="T38" s="65" t="n">
+        <f aca="false">T34+T35+T36+T37</f>
+        <v>17600</v>
+      </c>
+      <c r="U38" s="65" t="n">
+        <f aca="false">U34+U35+U36+U37</f>
+        <v>20600</v>
+      </c>
+      <c r="V38" s="65" t="n">
+        <f aca="false">V34+V35+V36+V37</f>
+        <v>17600</v>
+      </c>
+      <c r="W38" s="65" t="n">
+        <f aca="false">W34+W35+W36+W37</f>
+        <v>17600</v>
+      </c>
+      <c r="X38" s="65" t="n">
+        <f aca="false">X34+X35+X36+X37</f>
+        <v>18100</v>
+      </c>
+      <c r="Y38" s="65" t="n">
+        <f aca="false">Y34+Y35+Y36+Y37</f>
+        <v>18100</v>
+      </c>
+      <c r="Z38" s="65" t="n">
+        <f aca="false">SUM(B38:M38)</f>
+        <v>226050</v>
+      </c>
+      <c r="AA38" s="65" t="n">
+        <f aca="false">SUM(N38:Y38)</f>
+        <v>198200</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B40" s="50"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>561</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>562</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>563</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>564</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>565</v>
+      </c>
+      <c r="B42" s="66" t="n">
+        <f aca="false">Z23</f>
+        <v>300250</v>
+      </c>
+      <c r="C42" s="66" t="n">
+        <f aca="false">AA23</f>
+        <v>255000</v>
+      </c>
+      <c r="D42" s="66" t="n">
+        <f aca="false">B42+C42</f>
+        <v>555250</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="67" t="s">
+        <v>568</v>
+      </c>
+      <c r="B43" s="68" t="n">
+        <f aca="false">Z31</f>
+        <v>265050</v>
+      </c>
+      <c r="C43" s="68" t="n">
+        <f aca="false">AA31</f>
+        <v>225700</v>
+      </c>
+      <c r="D43" s="68" t="n">
+        <f aca="false">B43+C43</f>
+        <v>490750</v>
+      </c>
+      <c r="E43" s="67" t="s">
+        <v>569</v>
+      </c>
+      <c r="F43" s="67" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>571</v>
+      </c>
+      <c r="B44" s="66" t="n">
+        <f aca="false">Z38</f>
+        <v>226050</v>
+      </c>
+      <c r="C44" s="66" t="n">
+        <f aca="false">AA38</f>
+        <v>198200</v>
+      </c>
+      <c r="D44" s="66" t="n">
+        <f aca="false">B44+C44</f>
+        <v>424250</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="50" t="s">
+        <v>574</v>
+      </c>
+      <c r="B46" s="50"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="B47" s="69" t="n">
+        <f aca="false">B15</f>
+        <v>21</v>
+      </c>
+      <c r="C47" s="52" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="B48" s="69" t="n">
+        <f aca="false">3*18</f>
+        <v>54</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="B49" s="69" t="n">
+        <f aca="false">173/12</f>
+        <v>14.4166666666667</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="B50" s="69" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" s="52" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="62" t="s">
+        <v>583</v>
+      </c>
+      <c r="B51" s="70" t="n">
+        <f aca="false">B47+B48+B49+B50</f>
+        <v>119.416666666667</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="B52" s="69" t="n">
+        <v>180</v>
+      </c>
+      <c r="C52" s="52" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="62" t="s">
+        <v>586</v>
+      </c>
+      <c r="B53" s="71" t="n">
+        <f aca="false">B52-B51</f>
+        <v>60.5833333333333</v>
+      </c>
+      <c r="C53" s="52" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="50" t="s">
+        <v>588</v>
+      </c>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="50"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="27" t="s">
+        <v>589</v>
+      </c>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="27"/>
+      <c r="L56" s="27"/>
+      <c r="M56" s="27"/>
+      <c r="N56" s="27"/>
+      <c r="O56" s="27"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="27"/>
+      <c r="K57" s="27"/>
+      <c r="L57" s="27"/>
+      <c r="M57" s="27"/>
+      <c r="N57" s="27"/>
+      <c r="O57" s="27"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="27" t="s">
+        <v>591</v>
+      </c>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+      <c r="K58" s="27"/>
+      <c r="L58" s="27"/>
+      <c r="M58" s="27"/>
+      <c r="N58" s="27"/>
+      <c r="O58" s="27"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="27" t="s">
+        <v>592</v>
+      </c>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
+      <c r="N59" s="27"/>
+      <c r="O59" s="27"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="27"/>
+      <c r="J60" s="27"/>
+      <c r="K60" s="27"/>
+      <c r="L60" s="27"/>
+      <c r="M60" s="27"/>
+      <c r="N60" s="27"/>
+      <c r="O60" s="27"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="27" t="s">
+        <v>594</v>
+      </c>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="27" t="s">
+        <v>595</v>
+      </c>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="27"/>
+      <c r="K62" s="27"/>
+      <c r="L62" s="27"/>
+      <c r="M62" s="27"/>
+      <c r="N62" s="27"/>
+      <c r="O62" s="27"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="27" t="s">
+        <v>596</v>
+      </c>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="27"/>
+      <c r="K63" s="27"/>
+      <c r="L63" s="27"/>
+      <c r="M63" s="27"/>
+      <c r="N63" s="27"/>
+      <c r="O63" s="27"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="27" t="s">
+        <v>597</v>
+      </c>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="27"/>
+      <c r="K64" s="27"/>
+      <c r="L64" s="27"/>
+      <c r="M64" s="27"/>
+      <c r="N64" s="27"/>
+      <c r="O64" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A19:AB19"/>
+    <mergeCell ref="A25:AB25"/>
+    <mergeCell ref="A33:AB33"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A56:O56"/>
+    <mergeCell ref="A57:O57"/>
+    <mergeCell ref="A58:O58"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="A60:O60"/>
+    <mergeCell ref="A61:O61"/>
+    <mergeCell ref="A62:O62"/>
+    <mergeCell ref="A63:O63"/>
+    <mergeCell ref="A64:O64"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/income_forecaster.xlsx
+++ b/income_forecaster.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="606">
   <si>
     <t xml:space="preserve">Income Forecaster — Chance Peare</t>
   </si>
@@ -174,7 +174,7 @@
     <t xml:space="preserve">Health insurance (paycheck)</t>
   </si>
   <si>
-    <t xml:space="preserve">Midpoint of $200–600 range.</t>
+    <t xml:space="preserve">Currently $400 (Skyright payroll). Post-sale (Scenarios B/C): $600 health sharing ministry, $7.2K/yr — saves $15-23K vs ACA but NOT insurance.</t>
   </si>
   <si>
     <t xml:space="preserve">Auto loan payment</t>
@@ -1614,16 +1614,16 @@
     <t xml:space="preserve">Equity payment (gross)</t>
   </si>
   <si>
-    <t xml:space="preserve">5% stake. Mid-low of $100-200K range.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LTCG tax rate (federal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15% MFJ for AGI &lt; $583K. Assumes &gt;1-yr holding.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity payment (net of tax)</t>
+    <t xml:space="preserve">5% phantom equity. Working equity, no basis. Taxable as ordinary income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective tax on equity (ordinary income + FICA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phantom/ghost equity = W2 wages. 22-24% federal + 7.65% FICA at this income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity payment (net of tax &amp; FICA)</t>
   </si>
   <si>
     <t xml:space="preserve">Net cash to bank.</t>
@@ -1764,7 +1764,7 @@
     <t xml:space="preserve">Reduced from 35 to ~21 hrs/mo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Other retainer hrs/mo (3 retainers × 18 hrs)</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">Active tier ~18 hrs/mo each.</t>
@@ -1797,34 +1797,58 @@
     <t xml:space="preserve">Positive = fits. Negative = need to drop a retainer or hire more.</t>
   </si>
   <si>
-    <t xml:space="preserve">STRATEGIC NOTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Equity tax treatment: assumes LTCG (&gt;1-yr holding). Federal 15% MFJ at AGI &lt;$583K. Verify cost basis with CPA — could be lower than gross if exercised options.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Scenario B (Skyright as Embedded) requires the BUYER to want this arrangement. Most likely if buyer is owner-operator or strategic acquirer who values continuity. PE buyers typically install own ops team — Scenario B unlikely with PE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Skyright Embedded duration (18 months default) is aggressive. Reality: transition retainers often end in 6-12 months once new ops team is in place. Edit Assumptions B10 to test 12-mo case.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• VA hired at sale month to absorb Skyright admin/operational work. Make automations + ServiceTitan integrations + report automation = the 40% time savings on Skyright retainer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• In Scenario B, Skyright becomes both an income source AND your capacity sink. If they need 21 hrs/mo, you only have ~159 hrs/mo for everything else. Tight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Scenario C buys runway with equity but requires faster client acquisition to compensate for lost Skyright income. Aggressive growth path assumes 6 active retainers by end Y2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Equity payment goes into Mercury business account if treated as business income, OR personal if treated as capital gains on personal investment. Most likely the latter (personal LTCG). Confirm with CPA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Health insurance: Scenario A keeps Skyright/NewCo employer coverage. B and C trigger ACA ($1,500-2,500/mo family of 6) starting sale month. NOT modeled here — add $18-30K/yr cost to B and C.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Tax estimate on Y1 numbers gets complicated: W2 portion withheld, 1099 portion + equity (LTCG) require separate quarterly payments. Cleanup at year-end could be a $10K+ surprise either direction.</t>
+    <t xml:space="preserve">STRATEGIC NOTES (UPDATED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Equity is PHANTOM/GHOST equity — taxed as W2 ordinary income + FICA. ~30% effective rate at this income. Net = ~$87.5K on $125K gross. NOT LTCG.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Confirm with CPA whether equity payment can use §409A structuring to defer or restructure timing. Could push payment to following tax year if you want to manage AGI for QBI / ACA / etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Health coverage: Health sharing ministry at $600/mo (~$7,200/yr) for Scenarios B and C. Saves $15-23K vs ACA — but health sharing is NOT insurance, has limits, may not cover pre-existing conditions. Material risk for family of 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Buyer is likely strategic or owner-operator (per discussion). Scenario B (Skyright as Embedded) is REALISTIC, not aspirational. Now actively negotiate the retainer arrangement with current owner BEFORE sale — write it into sale documents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Push for premium Embedded $8-10K/mo for first 12 months, stepping down to $6K thereafter. Current owner can include this as a transition condition in the sale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• You are already building JobNimbus estimating tools + office automation at Skyright. CRITICAL — clarify IP ownership NOW. Workflows in JobNimbus stay with Skyright (their seat). Make/Zapier automations under your accounts could be portable. Best path: document everything as Skyright IP, license-back through retainer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Automation work you're doing reduces Skyright Embedded hours needed post-sale (already estimated at 40% reduction). Good — but means the buyer values this automation portfolio. Don't under-price the retainer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• If buyer turns out to be PE (unlikely per your read but possible), Scenario B falls apart — PE installs own ops team. Plan B fallback should be Scenario C (clean exit on equity runway).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Year 1 tax with equity = COMPLICATED. W2 income (Skyright $96K + equity $125K = $221K) + 1099 ($85.5K) = $306K gross. Marginal rate hits 24%. Effective rate ~22-25%. Quarterly estimated payments need to scale up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Cash inflow concentration: home sale ($95K July) + equity ($87.5K Oct) + retainer income = ~$200K of one-time cash in Q3-Q4 2026. Deploy intentionally: debt payoff first, emergency fund second, business reserves third, retirement contribution fourth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEIGHTED SCENARIO (planning baseline)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability A (Stay at NewCo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability B (Skyright as Embedded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability C (Clean exit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weighted Y1 Gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weighted Y2 Gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weighted 24-mo Total</t>
   </si>
 </sst>
 </file>
@@ -1840,8 +1864,8 @@
     <numFmt numFmtId="169" formatCode="0.00%"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
     <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0"/>
-    <numFmt numFmtId="173" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -2024,7 +2048,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2217,11 +2241,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2229,47 +2273,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="172" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2277,39 +2281,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="173" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4584,215 +4556,215 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB64"/>
+  <dimension ref="A1:AB82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="49"/>
-      <c r="V2" s="49"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="49"/>
-      <c r="AA2" s="49"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B5" s="51" t="n">
+      <c r="B5" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="6" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B6" s="53" t="n">
+      <c r="B6" s="15" t="n">
         <v>125000</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="6" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B7" s="54" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C7" s="52" t="s">
+      <c r="B7" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B8" s="55" t="n">
+      <c r="B8" s="48" t="n">
         <f aca="false">B6*(1-B7)</f>
-        <v>106250</v>
-      </c>
-      <c r="C8" s="52" t="s">
+        <v>87500</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="14" t="n">
         <v>6000</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="6" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B10" s="51" t="n">
+      <c r="B10" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="6" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B11" s="51" t="n">
+      <c r="B11" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="6" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="14" t="n">
         <v>2400</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="6" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B13" s="57" t="n">
+      <c r="B13" s="36" t="n">
         <v>0.4</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="6" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B14" s="58" t="n">
+      <c r="B14" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="6" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B15" s="59" t="n">
+      <c r="B15" s="45" t="n">
         <f aca="false">B14*(1-B13)</f>
         <v>21</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="6" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="60" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
         <v>192</v>
       </c>
       <c r="B17" s="30" t="s">
@@ -4867,1660 +4839,1660 @@
       <c r="Y17" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="Z17" s="60" t="s">
+      <c r="Z17" s="40" t="s">
         <v>345</v>
       </c>
-      <c r="AA17" s="60" t="s">
+      <c r="AA17" s="40" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="50" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="50"/>
-      <c r="Y19" s="50"/>
-      <c r="Z19" s="50"/>
-      <c r="AA19" s="50"/>
-      <c r="AB19" s="50"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B20" s="61" t="n">
+      <c r="B20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="C20" s="61" t="n">
+      <c r="C20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="D20" s="61" t="n">
+      <c r="D20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="E20" s="61" t="n">
+      <c r="E20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="F20" s="61" t="n">
+      <c r="F20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="G20" s="61" t="n">
+      <c r="G20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="H20" s="61" t="n">
+      <c r="H20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="I20" s="61" t="n">
+      <c r="I20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="J20" s="61" t="n">
+      <c r="J20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="K20" s="61" t="n">
+      <c r="K20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="L20" s="61" t="n">
+      <c r="L20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="M20" s="61" t="n">
+      <c r="M20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="N20" s="61" t="n">
+      <c r="N20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="O20" s="61" t="n">
+      <c r="O20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="P20" s="61" t="n">
+      <c r="P20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="Q20" s="61" t="n">
+      <c r="Q20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="R20" s="61" t="n">
+      <c r="R20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="S20" s="61" t="n">
+      <c r="S20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="T20" s="61" t="n">
+      <c r="T20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="U20" s="61" t="n">
+      <c r="U20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="V20" s="61" t="n">
+      <c r="V20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="W20" s="61" t="n">
+      <c r="W20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="X20" s="61" t="n">
+      <c r="X20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="Y20" s="61" t="n">
+      <c r="Y20" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="Z20" s="55" t="n">
+      <c r="Z20" s="48" t="n">
         <f aca="false">SUM(B20:M20)</f>
         <v>96000</v>
       </c>
-      <c r="AA20" s="55" t="n">
+      <c r="AA20" s="48" t="n">
         <f aca="false">SUM(N20:Y20)</f>
         <v>96000</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B21" s="61" t="n">
+      <c r="B21" s="38" t="n">
         <f aca="false">IF(1=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="61" t="n">
+      <c r="C21" s="38" t="n">
         <f aca="false">IF(2=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="61" t="n">
+      <c r="D21" s="38" t="n">
         <f aca="false">IF(3=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="61" t="n">
+      <c r="E21" s="38" t="n">
         <f aca="false">IF(4=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="61" t="n">
+      <c r="F21" s="38" t="n">
         <f aca="false">IF(5=$B$5,$B$8,0)</f>
-        <v>106250</v>
-      </c>
-      <c r="G21" s="61" t="n">
+        <v>87500</v>
+      </c>
+      <c r="G21" s="38" t="n">
         <f aca="false">IF(6=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="61" t="n">
+      <c r="H21" s="38" t="n">
         <f aca="false">IF(7=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="61" t="n">
+      <c r="I21" s="38" t="n">
         <f aca="false">IF(8=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="61" t="n">
+      <c r="J21" s="38" t="n">
         <f aca="false">IF(9=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="K21" s="61" t="n">
+      <c r="K21" s="38" t="n">
         <f aca="false">IF(10=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="L21" s="61" t="n">
+      <c r="L21" s="38" t="n">
         <f aca="false">IF(11=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="M21" s="61" t="n">
+      <c r="M21" s="38" t="n">
         <f aca="false">IF(12=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="61" t="n">
+      <c r="N21" s="38" t="n">
         <f aca="false">IF(13=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="O21" s="61" t="n">
+      <c r="O21" s="38" t="n">
         <f aca="false">IF(14=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="P21" s="61" t="n">
+      <c r="P21" s="38" t="n">
         <f aca="false">IF(15=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="61" t="n">
+      <c r="Q21" s="38" t="n">
         <f aca="false">IF(16=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="R21" s="61" t="n">
+      <c r="R21" s="38" t="n">
         <f aca="false">IF(17=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="S21" s="61" t="n">
+      <c r="S21" s="38" t="n">
         <f aca="false">IF(18=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="T21" s="61" t="n">
+      <c r="T21" s="38" t="n">
         <f aca="false">IF(19=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="U21" s="61" t="n">
+      <c r="U21" s="38" t="n">
         <f aca="false">IF(20=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="V21" s="61" t="n">
+      <c r="V21" s="38" t="n">
         <f aca="false">IF(21=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="W21" s="61" t="n">
+      <c r="W21" s="38" t="n">
         <f aca="false">IF(22=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="X21" s="61" t="n">
+      <c r="X21" s="38" t="n">
         <f aca="false">IF(23=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Y21" s="61" t="n">
+      <c r="Y21" s="38" t="n">
         <f aca="false">IF(24=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Z21" s="55" t="n">
+      <c r="Z21" s="48" t="n">
         <f aca="false">SUM(B21:M21)</f>
-        <v>106250</v>
-      </c>
-      <c r="AA21" s="55" t="n">
+        <v>87500</v>
+      </c>
+      <c r="AA21" s="48" t="n">
         <f aca="false">SUM(N21:Y21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B22" s="61" t="n">
+      <c r="B22" s="38" t="n">
         <v>3500</v>
       </c>
-      <c r="C22" s="61" t="n">
+      <c r="C22" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="D22" s="61" t="n">
+      <c r="D22" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="E22" s="61" t="n">
+      <c r="E22" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="F22" s="61" t="n">
+      <c r="F22" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="G22" s="61" t="n">
+      <c r="G22" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="H22" s="61" t="n">
+      <c r="H22" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="I22" s="61" t="n">
+      <c r="I22" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="J22" s="61" t="n">
+      <c r="J22" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="K22" s="61" t="n">
+      <c r="K22" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="L22" s="61" t="n">
+      <c r="L22" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="M22" s="61" t="n">
+      <c r="M22" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="N22" s="61" t="n">
+      <c r="N22" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="O22" s="61" t="n">
+      <c r="O22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="P22" s="61" t="n">
+      <c r="P22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="Q22" s="61" t="n">
+      <c r="Q22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="R22" s="61" t="n">
+      <c r="R22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="S22" s="61" t="n">
+      <c r="S22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="T22" s="61" t="n">
+      <c r="T22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="U22" s="61" t="n">
+      <c r="U22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="V22" s="61" t="n">
+      <c r="V22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="W22" s="61" t="n">
+      <c r="W22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="X22" s="61" t="n">
+      <c r="X22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="Y22" s="61" t="n">
+      <c r="Y22" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="Z22" s="55" t="n">
+      <c r="Z22" s="48" t="n">
         <f aca="false">SUM(B22:M22)</f>
         <v>98000</v>
       </c>
-      <c r="AA22" s="55" t="n">
+      <c r="AA22" s="48" t="n">
         <f aca="false">SUM(N22:Y22)</f>
         <v>159000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="62" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="63" t="n">
+      <c r="B23" s="49" t="n">
         <f aca="false">B20+B21+B22</f>
         <v>11500</v>
       </c>
-      <c r="C23" s="63" t="n">
+      <c r="C23" s="49" t="n">
         <f aca="false">C20+C21+C22</f>
         <v>13000</v>
       </c>
-      <c r="D23" s="63" t="n">
+      <c r="D23" s="49" t="n">
         <f aca="false">D20+D21+D22</f>
         <v>13000</v>
       </c>
-      <c r="E23" s="63" t="n">
+      <c r="E23" s="49" t="n">
         <f aca="false">E20+E21+E22</f>
         <v>16000</v>
       </c>
-      <c r="F23" s="63" t="n">
+      <c r="F23" s="49" t="n">
         <f aca="false">F20+F21+F22</f>
-        <v>122250</v>
-      </c>
-      <c r="G23" s="63" t="n">
+        <v>103500</v>
+      </c>
+      <c r="G23" s="49" t="n">
         <f aca="false">G20+G21+G22</f>
         <v>16000</v>
       </c>
-      <c r="H23" s="63" t="n">
+      <c r="H23" s="49" t="n">
         <f aca="false">H20+H21+H22</f>
         <v>16000</v>
       </c>
-      <c r="I23" s="63" t="n">
+      <c r="I23" s="49" t="n">
         <f aca="false">I20+I21+I22</f>
         <v>18500</v>
       </c>
-      <c r="J23" s="63" t="n">
+      <c r="J23" s="49" t="n">
         <f aca="false">J20+J21+J22</f>
         <v>18500</v>
       </c>
-      <c r="K23" s="63" t="n">
+      <c r="K23" s="49" t="n">
         <f aca="false">K20+K21+K22</f>
         <v>18500</v>
       </c>
-      <c r="L23" s="63" t="n">
+      <c r="L23" s="49" t="n">
         <f aca="false">L20+L21+L22</f>
         <v>18500</v>
       </c>
-      <c r="M23" s="63" t="n">
+      <c r="M23" s="49" t="n">
         <f aca="false">M20+M21+M22</f>
         <v>18500</v>
       </c>
-      <c r="N23" s="63" t="n">
+      <c r="N23" s="49" t="n">
         <f aca="false">N20+N21+N22</f>
         <v>18500</v>
       </c>
-      <c r="O23" s="63" t="n">
+      <c r="O23" s="49" t="n">
         <f aca="false">O20+O21+O22</f>
         <v>21500</v>
       </c>
-      <c r="P23" s="63" t="n">
+      <c r="P23" s="49" t="n">
         <f aca="false">P20+P21+P22</f>
         <v>21500</v>
       </c>
-      <c r="Q23" s="63" t="n">
+      <c r="Q23" s="49" t="n">
         <f aca="false">Q20+Q21+Q22</f>
         <v>21500</v>
       </c>
-      <c r="R23" s="63" t="n">
+      <c r="R23" s="49" t="n">
         <f aca="false">R20+R21+R22</f>
         <v>21500</v>
       </c>
-      <c r="S23" s="63" t="n">
+      <c r="S23" s="49" t="n">
         <f aca="false">S20+S21+S22</f>
         <v>21500</v>
       </c>
-      <c r="T23" s="63" t="n">
+      <c r="T23" s="49" t="n">
         <f aca="false">T20+T21+T22</f>
         <v>21500</v>
       </c>
-      <c r="U23" s="63" t="n">
+      <c r="U23" s="49" t="n">
         <f aca="false">U20+U21+U22</f>
         <v>21500</v>
       </c>
-      <c r="V23" s="63" t="n">
+      <c r="V23" s="49" t="n">
         <f aca="false">V20+V21+V22</f>
         <v>21500</v>
       </c>
-      <c r="W23" s="63" t="n">
+      <c r="W23" s="49" t="n">
         <f aca="false">W20+W21+W22</f>
         <v>21500</v>
       </c>
-      <c r="X23" s="63" t="n">
+      <c r="X23" s="49" t="n">
         <f aca="false">X20+X21+X22</f>
         <v>21500</v>
       </c>
-      <c r="Y23" s="63" t="n">
+      <c r="Y23" s="49" t="n">
         <f aca="false">Y20+Y21+Y22</f>
         <v>21500</v>
       </c>
-      <c r="Z23" s="63" t="n">
+      <c r="Z23" s="49" t="n">
         <f aca="false">SUM(B23:M23)</f>
-        <v>300250</v>
-      </c>
-      <c r="AA23" s="63" t="n">
+        <v>281500</v>
+      </c>
+      <c r="AA23" s="49" t="n">
         <f aca="false">SUM(N23:Y23)</f>
         <v>255000</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="50" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="50"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50"/>
-      <c r="S25" s="50"/>
-      <c r="T25" s="50"/>
-      <c r="U25" s="50"/>
-      <c r="V25" s="50"/>
-      <c r="W25" s="50"/>
-      <c r="X25" s="50"/>
-      <c r="Y25" s="50"/>
-      <c r="Z25" s="50"/>
-      <c r="AA25" s="50"/>
-      <c r="AB25" s="50"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B26" s="61" t="n">
+      <c r="B26" s="38" t="n">
         <f aca="false">IF(1&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="C26" s="61" t="n">
+      <c r="C26" s="38" t="n">
         <f aca="false">IF(2&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="D26" s="61" t="n">
+      <c r="D26" s="38" t="n">
         <f aca="false">IF(3&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="E26" s="61" t="n">
+      <c r="E26" s="38" t="n">
         <f aca="false">IF(4&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="F26" s="61" t="n">
+      <c r="F26" s="38" t="n">
         <f aca="false">IF(5&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="61" t="n">
+      <c r="G26" s="38" t="n">
         <f aca="false">IF(6&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="61" t="n">
+      <c r="H26" s="38" t="n">
         <f aca="false">IF(7&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="61" t="n">
+      <c r="I26" s="38" t="n">
         <f aca="false">IF(8&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="61" t="n">
+      <c r="J26" s="38" t="n">
         <f aca="false">IF(9&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="61" t="n">
+      <c r="K26" s="38" t="n">
         <f aca="false">IF(10&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="L26" s="61" t="n">
+      <c r="L26" s="38" t="n">
         <f aca="false">IF(11&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="61" t="n">
+      <c r="M26" s="38" t="n">
         <f aca="false">IF(12&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="61" t="n">
+      <c r="N26" s="38" t="n">
         <f aca="false">IF(13&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="61" t="n">
+      <c r="O26" s="38" t="n">
         <f aca="false">IF(14&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="P26" s="61" t="n">
+      <c r="P26" s="38" t="n">
         <f aca="false">IF(15&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="61" t="n">
+      <c r="Q26" s="38" t="n">
         <f aca="false">IF(16&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="R26" s="61" t="n">
+      <c r="R26" s="38" t="n">
         <f aca="false">IF(17&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="S26" s="61" t="n">
+      <c r="S26" s="38" t="n">
         <f aca="false">IF(18&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="T26" s="61" t="n">
+      <c r="T26" s="38" t="n">
         <f aca="false">IF(19&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="U26" s="61" t="n">
+      <c r="U26" s="38" t="n">
         <f aca="false">IF(20&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="V26" s="61" t="n">
+      <c r="V26" s="38" t="n">
         <f aca="false">IF(21&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="W26" s="61" t="n">
+      <c r="W26" s="38" t="n">
         <f aca="false">IF(22&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="X26" s="61" t="n">
+      <c r="X26" s="38" t="n">
         <f aca="false">IF(23&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="Y26" s="61" t="n">
+      <c r="Y26" s="38" t="n">
         <f aca="false">IF(24&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="Z26" s="64" t="n">
+      <c r="Z26" s="18" t="n">
         <f aca="false">SUM(B26:M26)</f>
         <v>32000</v>
       </c>
-      <c r="AA26" s="64" t="n">
+      <c r="AA26" s="18" t="n">
         <f aca="false">SUM(N26:Y26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B27" s="61" t="n">
+      <c r="B27" s="38" t="n">
         <f aca="false">IF(1=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="61" t="n">
+      <c r="C27" s="38" t="n">
         <f aca="false">IF(2=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="61" t="n">
+      <c r="D27" s="38" t="n">
         <f aca="false">IF(3=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="61" t="n">
+      <c r="E27" s="38" t="n">
         <f aca="false">IF(4=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="61" t="n">
+      <c r="F27" s="38" t="n">
         <f aca="false">IF(5=$B$5,$B$8,0)</f>
-        <v>106250</v>
-      </c>
-      <c r="G27" s="61" t="n">
+        <v>87500</v>
+      </c>
+      <c r="G27" s="38" t="n">
         <f aca="false">IF(6=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="61" t="n">
+      <c r="H27" s="38" t="n">
         <f aca="false">IF(7=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="61" t="n">
+      <c r="I27" s="38" t="n">
         <f aca="false">IF(8=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="61" t="n">
+      <c r="J27" s="38" t="n">
         <f aca="false">IF(9=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="61" t="n">
+      <c r="K27" s="38" t="n">
         <f aca="false">IF(10=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="61" t="n">
+      <c r="L27" s="38" t="n">
         <f aca="false">IF(11=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="M27" s="61" t="n">
+      <c r="M27" s="38" t="n">
         <f aca="false">IF(12=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="61" t="n">
+      <c r="N27" s="38" t="n">
         <f aca="false">IF(13=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="O27" s="61" t="n">
+      <c r="O27" s="38" t="n">
         <f aca="false">IF(14=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="P27" s="61" t="n">
+      <c r="P27" s="38" t="n">
         <f aca="false">IF(15=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="61" t="n">
+      <c r="Q27" s="38" t="n">
         <f aca="false">IF(16=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="R27" s="61" t="n">
+      <c r="R27" s="38" t="n">
         <f aca="false">IF(17=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="S27" s="61" t="n">
+      <c r="S27" s="38" t="n">
         <f aca="false">IF(18=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="61" t="n">
+      <c r="T27" s="38" t="n">
         <f aca="false">IF(19=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="U27" s="61" t="n">
+      <c r="U27" s="38" t="n">
         <f aca="false">IF(20=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="V27" s="61" t="n">
+      <c r="V27" s="38" t="n">
         <f aca="false">IF(21=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="W27" s="61" t="n">
+      <c r="W27" s="38" t="n">
         <f aca="false">IF(22=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="X27" s="61" t="n">
+      <c r="X27" s="38" t="n">
         <f aca="false">IF(23=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Y27" s="61" t="n">
+      <c r="Y27" s="38" t="n">
         <f aca="false">IF(24=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Z27" s="64" t="n">
+      <c r="Z27" s="18" t="n">
         <f aca="false">SUM(B27:M27)</f>
-        <v>106250</v>
-      </c>
-      <c r="AA27" s="64" t="n">
+        <v>87500</v>
+      </c>
+      <c r="AA27" s="18" t="n">
         <f aca="false">SUM(N27:Y27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B28" s="61" t="n">
+      <c r="B28" s="38" t="n">
         <f aca="false">IF(AND(1&gt;$B$5,1&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="61" t="n">
+      <c r="C28" s="38" t="n">
         <f aca="false">IF(AND(2&gt;$B$5,2&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="61" t="n">
+      <c r="D28" s="38" t="n">
         <f aca="false">IF(AND(3&gt;$B$5,3&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="61" t="n">
+      <c r="E28" s="38" t="n">
         <f aca="false">IF(AND(4&gt;$B$5,4&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="61" t="n">
+      <c r="F28" s="38" t="n">
         <f aca="false">IF(AND(5&gt;$B$5,5&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="61" t="n">
+      <c r="G28" s="38" t="n">
         <f aca="false">IF(AND(6&gt;$B$5,6&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="H28" s="61" t="n">
+      <c r="H28" s="38" t="n">
         <f aca="false">IF(AND(7&gt;$B$5,7&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="I28" s="61" t="n">
+      <c r="I28" s="38" t="n">
         <f aca="false">IF(AND(8&gt;$B$5,8&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="J28" s="61" t="n">
+      <c r="J28" s="38" t="n">
         <f aca="false">IF(AND(9&gt;$B$5,9&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="K28" s="61" t="n">
+      <c r="K28" s="38" t="n">
         <f aca="false">IF(AND(10&gt;$B$5,10&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="L28" s="61" t="n">
+      <c r="L28" s="38" t="n">
         <f aca="false">IF(AND(11&gt;$B$5,11&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="M28" s="61" t="n">
+      <c r="M28" s="38" t="n">
         <f aca="false">IF(AND(12&gt;$B$5,12&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="N28" s="61" t="n">
+      <c r="N28" s="38" t="n">
         <f aca="false">IF(AND(13&gt;$B$5,13&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="O28" s="61" t="n">
+      <c r="O28" s="38" t="n">
         <f aca="false">IF(AND(14&gt;$B$5,14&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="P28" s="61" t="n">
+      <c r="P28" s="38" t="n">
         <f aca="false">IF(AND(15&gt;$B$5,15&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="Q28" s="61" t="n">
+      <c r="Q28" s="38" t="n">
         <f aca="false">IF(AND(16&gt;$B$5,16&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="R28" s="61" t="n">
+      <c r="R28" s="38" t="n">
         <f aca="false">IF(AND(17&gt;$B$5,17&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="S28" s="61" t="n">
+      <c r="S28" s="38" t="n">
         <f aca="false">IF(AND(18&gt;$B$5,18&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="T28" s="61" t="n">
+      <c r="T28" s="38" t="n">
         <f aca="false">IF(AND(19&gt;$B$5,19&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="U28" s="61" t="n">
+      <c r="U28" s="38" t="n">
         <f aca="false">IF(AND(20&gt;$B$5,20&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="V28" s="61" t="n">
+      <c r="V28" s="38" t="n">
         <f aca="false">IF(AND(21&gt;$B$5,21&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="W28" s="61" t="n">
+      <c r="W28" s="38" t="n">
         <f aca="false">IF(AND(22&gt;$B$5,22&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="X28" s="61" t="n">
+      <c r="X28" s="38" t="n">
         <f aca="false">IF(AND(23&gt;$B$5,23&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>6000</v>
       </c>
-      <c r="Y28" s="61" t="n">
+      <c r="Y28" s="38" t="n">
         <f aca="false">IF(AND(24&gt;$B$5,24&lt;=$B$5+$B$10),$B$9,0)</f>
         <v>0</v>
       </c>
-      <c r="Z28" s="64" t="n">
+      <c r="Z28" s="18" t="n">
         <f aca="false">SUM(B28:M28)</f>
         <v>42000</v>
       </c>
-      <c r="AA28" s="64" t="n">
+      <c r="AA28" s="18" t="n">
         <f aca="false">SUM(N28:Y28)</f>
         <v>66000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B29" s="61" t="n">
+      <c r="B29" s="38" t="n">
         <v>3500</v>
       </c>
-      <c r="C29" s="61" t="n">
+      <c r="C29" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="D29" s="61" t="n">
+      <c r="D29" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="E29" s="61" t="n">
+      <c r="E29" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="F29" s="61" t="n">
+      <c r="F29" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="G29" s="61" t="n">
+      <c r="G29" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="H29" s="61" t="n">
+      <c r="H29" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="I29" s="61" t="n">
+      <c r="I29" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="J29" s="61" t="n">
+      <c r="J29" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="K29" s="61" t="n">
+      <c r="K29" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="L29" s="61" t="n">
+      <c r="L29" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="M29" s="61" t="n">
+      <c r="M29" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="N29" s="61" t="n">
+      <c r="N29" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="O29" s="61" t="n">
+      <c r="O29" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="P29" s="61" t="n">
+      <c r="P29" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="Q29" s="61" t="n">
+      <c r="Q29" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="R29" s="61" t="n">
+      <c r="R29" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="S29" s="61" t="n">
+      <c r="S29" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="T29" s="61" t="n">
+      <c r="T29" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="U29" s="61" t="n">
+      <c r="U29" s="38" t="n">
         <v>20000</v>
       </c>
-      <c r="V29" s="61" t="n">
+      <c r="V29" s="38" t="n">
         <v>17000</v>
       </c>
-      <c r="W29" s="61" t="n">
+      <c r="W29" s="38" t="n">
         <v>17000</v>
       </c>
-      <c r="X29" s="61" t="n">
+      <c r="X29" s="38" t="n">
         <v>14000</v>
       </c>
-      <c r="Y29" s="61" t="n">
+      <c r="Y29" s="38" t="n">
         <v>14000</v>
       </c>
-      <c r="Z29" s="64" t="n">
+      <c r="Z29" s="18" t="n">
         <f aca="false">SUM(B29:M29)</f>
         <v>104000</v>
       </c>
-      <c r="AA29" s="64" t="n">
+      <c r="AA29" s="18" t="n">
         <f aca="false">SUM(N29:Y29)</f>
         <v>188500</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B30" s="64" t="n">
+      <c r="B30" s="18" t="n">
         <f aca="false">IF(1&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="64" t="n">
+      <c r="C30" s="18" t="n">
         <f aca="false">IF(2&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="64" t="n">
+      <c r="D30" s="18" t="n">
         <f aca="false">IF(3&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="64" t="n">
+      <c r="E30" s="18" t="n">
         <f aca="false">IF(4&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="64" t="n">
+      <c r="F30" s="18" t="n">
         <f aca="false">IF(5&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="G30" s="64" t="n">
+      <c r="G30" s="18" t="n">
         <f aca="false">IF(6&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="H30" s="64" t="n">
+      <c r="H30" s="18" t="n">
         <f aca="false">IF(7&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="I30" s="64" t="n">
+      <c r="I30" s="18" t="n">
         <f aca="false">IF(8&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="J30" s="64" t="n">
+      <c r="J30" s="18" t="n">
         <f aca="false">IF(9&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="K30" s="64" t="n">
+      <c r="K30" s="18" t="n">
         <f aca="false">IF(10&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="L30" s="64" t="n">
+      <c r="L30" s="18" t="n">
         <f aca="false">IF(11&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="M30" s="64" t="n">
+      <c r="M30" s="18" t="n">
         <f aca="false">IF(12&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="N30" s="64" t="n">
+      <c r="N30" s="18" t="n">
         <f aca="false">IF(13&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="O30" s="64" t="n">
+      <c r="O30" s="18" t="n">
         <f aca="false">IF(14&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="P30" s="64" t="n">
+      <c r="P30" s="18" t="n">
         <f aca="false">IF(15&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="Q30" s="64" t="n">
+      <c r="Q30" s="18" t="n">
         <f aca="false">IF(16&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="R30" s="64" t="n">
+      <c r="R30" s="18" t="n">
         <f aca="false">IF(17&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="S30" s="64" t="n">
+      <c r="S30" s="18" t="n">
         <f aca="false">IF(18&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="T30" s="64" t="n">
+      <c r="T30" s="18" t="n">
         <f aca="false">IF(19&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="U30" s="64" t="n">
+      <c r="U30" s="18" t="n">
         <f aca="false">IF(20&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="V30" s="64" t="n">
+      <c r="V30" s="18" t="n">
         <f aca="false">IF(21&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="W30" s="64" t="n">
+      <c r="W30" s="18" t="n">
         <f aca="false">IF(22&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="X30" s="64" t="n">
+      <c r="X30" s="18" t="n">
         <f aca="false">IF(23&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="Y30" s="64" t="n">
+      <c r="Y30" s="18" t="n">
         <f aca="false">IF(24&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="Z30" s="64" t="n">
+      <c r="Z30" s="18" t="n">
         <f aca="false">SUM(B30:M30)</f>
         <v>-19200</v>
       </c>
-      <c r="AA30" s="64" t="n">
+      <c r="AA30" s="18" t="n">
         <f aca="false">SUM(N30:Y30)</f>
         <v>-28800</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="62" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24" t="s">
         <v>555</v>
       </c>
-      <c r="B31" s="65" t="n">
+      <c r="B31" s="19" t="n">
         <f aca="false">B26+B27+B28+B29+B30</f>
         <v>11500</v>
       </c>
-      <c r="C31" s="65" t="n">
+      <c r="C31" s="19" t="n">
         <f aca="false">C26+C27+C28+C29+C30</f>
         <v>13000</v>
       </c>
-      <c r="D31" s="65" t="n">
+      <c r="D31" s="19" t="n">
         <f aca="false">D26+D27+D28+D29+D30</f>
         <v>13000</v>
       </c>
-      <c r="E31" s="65" t="n">
+      <c r="E31" s="19" t="n">
         <f aca="false">E26+E27+E28+E29+E30</f>
         <v>16000</v>
       </c>
-      <c r="F31" s="65" t="n">
+      <c r="F31" s="19" t="n">
         <f aca="false">F26+F27+F28+F29+F30</f>
-        <v>111850</v>
-      </c>
-      <c r="G31" s="65" t="n">
+        <v>93100</v>
+      </c>
+      <c r="G31" s="19" t="n">
         <f aca="false">G26+G27+G28+G29+G30</f>
         <v>11600</v>
       </c>
-      <c r="H31" s="65" t="n">
+      <c r="H31" s="19" t="n">
         <f aca="false">H26+H27+H28+H29+H30</f>
         <v>11600</v>
       </c>
-      <c r="I31" s="65" t="n">
+      <c r="I31" s="19" t="n">
         <f aca="false">I26+I27+I28+I29+I30</f>
         <v>14100</v>
       </c>
-      <c r="J31" s="65" t="n">
+      <c r="J31" s="19" t="n">
         <f aca="false">J26+J27+J28+J29+J30</f>
         <v>14100</v>
       </c>
-      <c r="K31" s="65" t="n">
+      <c r="K31" s="19" t="n">
         <f aca="false">K26+K27+K28+K29+K30</f>
         <v>14100</v>
       </c>
-      <c r="L31" s="65" t="n">
+      <c r="L31" s="19" t="n">
         <f aca="false">L26+L27+L28+L29+L30</f>
         <v>17100</v>
       </c>
-      <c r="M31" s="65" t="n">
+      <c r="M31" s="19" t="n">
         <f aca="false">M26+M27+M28+M29+M30</f>
         <v>17100</v>
       </c>
-      <c r="N31" s="65" t="n">
+      <c r="N31" s="19" t="n">
         <f aca="false">N26+N27+N28+N29+N30</f>
         <v>17100</v>
       </c>
-      <c r="O31" s="65" t="n">
+      <c r="O31" s="19" t="n">
         <f aca="false">O26+O27+O28+O29+O30</f>
         <v>17100</v>
       </c>
-      <c r="P31" s="65" t="n">
+      <c r="P31" s="19" t="n">
         <f aca="false">P26+P27+P28+P29+P30</f>
         <v>17100</v>
       </c>
-      <c r="Q31" s="65" t="n">
+      <c r="Q31" s="19" t="n">
         <f aca="false">Q26+Q27+Q28+Q29+Q30</f>
         <v>20100</v>
       </c>
-      <c r="R31" s="65" t="n">
+      <c r="R31" s="19" t="n">
         <f aca="false">R26+R27+R28+R29+R30</f>
         <v>20100</v>
       </c>
-      <c r="S31" s="65" t="n">
+      <c r="S31" s="19" t="n">
         <f aca="false">S26+S27+S28+S29+S30</f>
         <v>20100</v>
       </c>
-      <c r="T31" s="65" t="n">
+      <c r="T31" s="19" t="n">
         <f aca="false">T26+T27+T28+T29+T30</f>
         <v>20100</v>
       </c>
-      <c r="U31" s="65" t="n">
+      <c r="U31" s="19" t="n">
         <f aca="false">U26+U27+U28+U29+U30</f>
         <v>23600</v>
       </c>
-      <c r="V31" s="65" t="n">
+      <c r="V31" s="19" t="n">
         <f aca="false">V26+V27+V28+V29+V30</f>
         <v>20600</v>
       </c>
-      <c r="W31" s="65" t="n">
+      <c r="W31" s="19" t="n">
         <f aca="false">W26+W27+W28+W29+W30</f>
         <v>20600</v>
       </c>
-      <c r="X31" s="65" t="n">
+      <c r="X31" s="19" t="n">
         <f aca="false">X26+X27+X28+X29+X30</f>
         <v>17600</v>
       </c>
-      <c r="Y31" s="65" t="n">
+      <c r="Y31" s="19" t="n">
         <f aca="false">Y26+Y27+Y28+Y29+Y30</f>
         <v>11600</v>
       </c>
-      <c r="Z31" s="65" t="n">
+      <c r="Z31" s="19" t="n">
         <f aca="false">SUM(B31:M31)</f>
-        <v>265050</v>
-      </c>
-      <c r="AA31" s="65" t="n">
+        <v>246300</v>
+      </c>
+      <c r="AA31" s="19" t="n">
         <f aca="false">SUM(N31:Y31)</f>
         <v>225700</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="50" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="50"/>
-      <c r="P33" s="50"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50"/>
-      <c r="S33" s="50"/>
-      <c r="T33" s="50"/>
-      <c r="U33" s="50"/>
-      <c r="V33" s="50"/>
-      <c r="W33" s="50"/>
-      <c r="X33" s="50"/>
-      <c r="Y33" s="50"/>
-      <c r="Z33" s="50"/>
-      <c r="AA33" s="50"/>
-      <c r="AB33" s="50"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B34" s="61" t="n">
+      <c r="B34" s="38" t="n">
         <f aca="false">IF(1&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="C34" s="61" t="n">
+      <c r="C34" s="38" t="n">
         <f aca="false">IF(2&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="D34" s="61" t="n">
+      <c r="D34" s="38" t="n">
         <f aca="false">IF(3&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="E34" s="61" t="n">
+      <c r="E34" s="38" t="n">
         <f aca="false">IF(4&lt;$B$5,8000,0)</f>
         <v>8000</v>
       </c>
-      <c r="F34" s="61" t="n">
+      <c r="F34" s="38" t="n">
         <f aca="false">IF(5&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="61" t="n">
+      <c r="G34" s="38" t="n">
         <f aca="false">IF(6&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="61" t="n">
+      <c r="H34" s="38" t="n">
         <f aca="false">IF(7&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="61" t="n">
+      <c r="I34" s="38" t="n">
         <f aca="false">IF(8&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="61" t="n">
+      <c r="J34" s="38" t="n">
         <f aca="false">IF(9&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="61" t="n">
+      <c r="K34" s="38" t="n">
         <f aca="false">IF(10&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="L34" s="61" t="n">
+      <c r="L34" s="38" t="n">
         <f aca="false">IF(11&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="M34" s="61" t="n">
+      <c r="M34" s="38" t="n">
         <f aca="false">IF(12&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="N34" s="61" t="n">
+      <c r="N34" s="38" t="n">
         <f aca="false">IF(13&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="O34" s="61" t="n">
+      <c r="O34" s="38" t="n">
         <f aca="false">IF(14&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="P34" s="61" t="n">
+      <c r="P34" s="38" t="n">
         <f aca="false">IF(15&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="61" t="n">
+      <c r="Q34" s="38" t="n">
         <f aca="false">IF(16&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="R34" s="61" t="n">
+      <c r="R34" s="38" t="n">
         <f aca="false">IF(17&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="S34" s="61" t="n">
+      <c r="S34" s="38" t="n">
         <f aca="false">IF(18&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="T34" s="61" t="n">
+      <c r="T34" s="38" t="n">
         <f aca="false">IF(19&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="U34" s="61" t="n">
+      <c r="U34" s="38" t="n">
         <f aca="false">IF(20&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="V34" s="61" t="n">
+      <c r="V34" s="38" t="n">
         <f aca="false">IF(21&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="W34" s="61" t="n">
+      <c r="W34" s="38" t="n">
         <f aca="false">IF(22&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="X34" s="61" t="n">
+      <c r="X34" s="38" t="n">
         <f aca="false">IF(23&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="Y34" s="61" t="n">
+      <c r="Y34" s="38" t="n">
         <f aca="false">IF(24&lt;$B$5,8000,0)</f>
         <v>0</v>
       </c>
-      <c r="Z34" s="64" t="n">
+      <c r="Z34" s="18" t="n">
         <f aca="false">SUM(B34:M34)</f>
         <v>32000</v>
       </c>
-      <c r="AA34" s="64" t="n">
+      <c r="AA34" s="18" t="n">
         <f aca="false">SUM(N34:Y34)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B35" s="61" t="n">
+      <c r="B35" s="38" t="n">
         <f aca="false">IF(1=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="61" t="n">
+      <c r="C35" s="38" t="n">
         <f aca="false">IF(2=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="61" t="n">
+      <c r="D35" s="38" t="n">
         <f aca="false">IF(3=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="61" t="n">
+      <c r="E35" s="38" t="n">
         <f aca="false">IF(4=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="61" t="n">
+      <c r="F35" s="38" t="n">
         <f aca="false">IF(5=$B$5,$B$8,0)</f>
-        <v>106250</v>
-      </c>
-      <c r="G35" s="61" t="n">
+        <v>87500</v>
+      </c>
+      <c r="G35" s="38" t="n">
         <f aca="false">IF(6=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="61" t="n">
+      <c r="H35" s="38" t="n">
         <f aca="false">IF(7=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="61" t="n">
+      <c r="I35" s="38" t="n">
         <f aca="false">IF(8=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="61" t="n">
+      <c r="J35" s="38" t="n">
         <f aca="false">IF(9=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="K35" s="61" t="n">
+      <c r="K35" s="38" t="n">
         <f aca="false">IF(10=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="L35" s="61" t="n">
+      <c r="L35" s="38" t="n">
         <f aca="false">IF(11=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="61" t="n">
+      <c r="M35" s="38" t="n">
         <f aca="false">IF(12=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="61" t="n">
+      <c r="N35" s="38" t="n">
         <f aca="false">IF(13=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="O35" s="61" t="n">
+      <c r="O35" s="38" t="n">
         <f aca="false">IF(14=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="P35" s="61" t="n">
+      <c r="P35" s="38" t="n">
         <f aca="false">IF(15=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="61" t="n">
+      <c r="Q35" s="38" t="n">
         <f aca="false">IF(16=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="R35" s="61" t="n">
+      <c r="R35" s="38" t="n">
         <f aca="false">IF(17=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="S35" s="61" t="n">
+      <c r="S35" s="38" t="n">
         <f aca="false">IF(18=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="61" t="n">
+      <c r="T35" s="38" t="n">
         <f aca="false">IF(19=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="U35" s="61" t="n">
+      <c r="U35" s="38" t="n">
         <f aca="false">IF(20=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="V35" s="61" t="n">
+      <c r="V35" s="38" t="n">
         <f aca="false">IF(21=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="W35" s="61" t="n">
+      <c r="W35" s="38" t="n">
         <f aca="false">IF(22=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="X35" s="61" t="n">
+      <c r="X35" s="38" t="n">
         <f aca="false">IF(23=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Y35" s="61" t="n">
+      <c r="Y35" s="38" t="n">
         <f aca="false">IF(24=$B$5,$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="Z35" s="64" t="n">
+      <c r="Z35" s="18" t="n">
         <f aca="false">SUM(B35:M35)</f>
-        <v>106250</v>
-      </c>
-      <c r="AA35" s="64" t="n">
+        <v>87500</v>
+      </c>
+      <c r="AA35" s="18" t="n">
         <f aca="false">SUM(N35:Y35)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B36" s="61" t="n">
+      <c r="B36" s="38" t="n">
         <v>3500</v>
       </c>
-      <c r="C36" s="61" t="n">
+      <c r="C36" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="D36" s="61" t="n">
+      <c r="D36" s="38" t="n">
         <v>5000</v>
       </c>
-      <c r="E36" s="61" t="n">
+      <c r="E36" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="F36" s="61" t="n">
+      <c r="F36" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="G36" s="61" t="n">
+      <c r="G36" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="H36" s="61" t="n">
+      <c r="H36" s="38" t="n">
         <v>8000</v>
       </c>
-      <c r="I36" s="61" t="n">
+      <c r="I36" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="J36" s="61" t="n">
+      <c r="J36" s="38" t="n">
         <v>10500</v>
       </c>
-      <c r="K36" s="61" t="n">
+      <c r="K36" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="L36" s="61" t="n">
+      <c r="L36" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="M36" s="61" t="n">
+      <c r="M36" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="N36" s="61" t="n">
+      <c r="N36" s="38" t="n">
         <v>13500</v>
       </c>
-      <c r="O36" s="61" t="n">
+      <c r="O36" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="P36" s="61" t="n">
+      <c r="P36" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="Q36" s="61" t="n">
+      <c r="Q36" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="R36" s="61" t="n">
+      <c r="R36" s="38" t="n">
         <v>20000</v>
       </c>
-      <c r="S36" s="61" t="n">
+      <c r="S36" s="38" t="n">
         <v>20000</v>
       </c>
-      <c r="T36" s="61" t="n">
+      <c r="T36" s="38" t="n">
         <v>20000</v>
       </c>
-      <c r="U36" s="61" t="n">
+      <c r="U36" s="38" t="n">
         <v>23000</v>
       </c>
-      <c r="V36" s="61" t="n">
+      <c r="V36" s="38" t="n">
         <v>20000</v>
       </c>
-      <c r="W36" s="61" t="n">
+      <c r="W36" s="38" t="n">
         <v>20000</v>
       </c>
-      <c r="X36" s="61" t="n">
+      <c r="X36" s="38" t="n">
         <v>20500</v>
       </c>
-      <c r="Y36" s="61" t="n">
+      <c r="Y36" s="38" t="n">
         <v>20500</v>
       </c>
-      <c r="Z36" s="64" t="n">
+      <c r="Z36" s="18" t="n">
         <f aca="false">SUM(B36:M36)</f>
         <v>107000</v>
       </c>
-      <c r="AA36" s="64" t="n">
+      <c r="AA36" s="18" t="n">
         <f aca="false">SUM(N36:Y36)</f>
         <v>227000</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B37" s="64" t="n">
+      <c r="B37" s="18" t="n">
         <f aca="false">IF(1&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="C37" s="64" t="n">
+      <c r="C37" s="18" t="n">
         <f aca="false">IF(2&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="64" t="n">
+      <c r="D37" s="18" t="n">
         <f aca="false">IF(3&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="E37" s="64" t="n">
+      <c r="E37" s="18" t="n">
         <f aca="false">IF(4&gt;=$B$11,-$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="64" t="n">
+      <c r="F37" s="18" t="n">
         <f aca="false">IF(5&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="G37" s="64" t="n">
+      <c r="G37" s="18" t="n">
         <f aca="false">IF(6&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="H37" s="64" t="n">
+      <c r="H37" s="18" t="n">
         <f aca="false">IF(7&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="I37" s="64" t="n">
+      <c r="I37" s="18" t="n">
         <f aca="false">IF(8&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="J37" s="64" t="n">
+      <c r="J37" s="18" t="n">
         <f aca="false">IF(9&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="K37" s="64" t="n">
+      <c r="K37" s="18" t="n">
         <f aca="false">IF(10&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="L37" s="64" t="n">
+      <c r="L37" s="18" t="n">
         <f aca="false">IF(11&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="M37" s="64" t="n">
+      <c r="M37" s="18" t="n">
         <f aca="false">IF(12&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="N37" s="64" t="n">
+      <c r="N37" s="18" t="n">
         <f aca="false">IF(13&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="O37" s="64" t="n">
+      <c r="O37" s="18" t="n">
         <f aca="false">IF(14&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="P37" s="64" t="n">
+      <c r="P37" s="18" t="n">
         <f aca="false">IF(15&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="Q37" s="64" t="n">
+      <c r="Q37" s="18" t="n">
         <f aca="false">IF(16&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="R37" s="64" t="n">
+      <c r="R37" s="18" t="n">
         <f aca="false">IF(17&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="S37" s="64" t="n">
+      <c r="S37" s="18" t="n">
         <f aca="false">IF(18&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="T37" s="64" t="n">
+      <c r="T37" s="18" t="n">
         <f aca="false">IF(19&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="U37" s="64" t="n">
+      <c r="U37" s="18" t="n">
         <f aca="false">IF(20&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="V37" s="64" t="n">
+      <c r="V37" s="18" t="n">
         <f aca="false">IF(21&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="W37" s="64" t="n">
+      <c r="W37" s="18" t="n">
         <f aca="false">IF(22&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="X37" s="64" t="n">
+      <c r="X37" s="18" t="n">
         <f aca="false">IF(23&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="Y37" s="64" t="n">
+      <c r="Y37" s="18" t="n">
         <f aca="false">IF(24&gt;=$B$11,-$B$12,0)</f>
         <v>-2400</v>
       </c>
-      <c r="Z37" s="64" t="n">
+      <c r="Z37" s="18" t="n">
         <f aca="false">SUM(B37:M37)</f>
         <v>-19200</v>
       </c>
-      <c r="AA37" s="64" t="n">
+      <c r="AA37" s="18" t="n">
         <f aca="false">SUM(N37:Y37)</f>
         <v>-28800</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="62" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
         <v>559</v>
       </c>
-      <c r="B38" s="65" t="n">
+      <c r="B38" s="19" t="n">
         <f aca="false">B34+B35+B36+B37</f>
         <v>11500</v>
       </c>
-      <c r="C38" s="65" t="n">
+      <c r="C38" s="19" t="n">
         <f aca="false">C34+C35+C36+C37</f>
         <v>13000</v>
       </c>
-      <c r="D38" s="65" t="n">
+      <c r="D38" s="19" t="n">
         <f aca="false">D34+D35+D36+D37</f>
         <v>13000</v>
       </c>
-      <c r="E38" s="65" t="n">
+      <c r="E38" s="19" t="n">
         <f aca="false">E34+E35+E36+E37</f>
         <v>16000</v>
       </c>
-      <c r="F38" s="65" t="n">
+      <c r="F38" s="19" t="n">
         <f aca="false">F34+F35+F36+F37</f>
-        <v>111850</v>
-      </c>
-      <c r="G38" s="65" t="n">
+        <v>93100</v>
+      </c>
+      <c r="G38" s="19" t="n">
         <f aca="false">G34+G35+G36+G37</f>
         <v>5600</v>
       </c>
-      <c r="H38" s="65" t="n">
+      <c r="H38" s="19" t="n">
         <f aca="false">H34+H35+H36+H37</f>
         <v>5600</v>
       </c>
-      <c r="I38" s="65" t="n">
+      <c r="I38" s="19" t="n">
         <f aca="false">I34+I35+I36+I37</f>
         <v>8100</v>
       </c>
-      <c r="J38" s="65" t="n">
+      <c r="J38" s="19" t="n">
         <f aca="false">J34+J35+J36+J37</f>
         <v>8100</v>
       </c>
-      <c r="K38" s="65" t="n">
+      <c r="K38" s="19" t="n">
         <f aca="false">K34+K35+K36+K37</f>
         <v>11100</v>
       </c>
-      <c r="L38" s="65" t="n">
+      <c r="L38" s="19" t="n">
         <f aca="false">L34+L35+L36+L37</f>
         <v>11100</v>
       </c>
-      <c r="M38" s="65" t="n">
+      <c r="M38" s="19" t="n">
         <f aca="false">M34+M35+M36+M37</f>
         <v>11100</v>
       </c>
-      <c r="N38" s="65" t="n">
+      <c r="N38" s="19" t="n">
         <f aca="false">N34+N35+N36+N37</f>
         <v>11100</v>
       </c>
-      <c r="O38" s="65" t="n">
+      <c r="O38" s="19" t="n">
         <f aca="false">O34+O35+O36+O37</f>
         <v>14100</v>
       </c>
-      <c r="P38" s="65" t="n">
+      <c r="P38" s="19" t="n">
         <f aca="false">P34+P35+P36+P37</f>
         <v>14100</v>
       </c>
-      <c r="Q38" s="65" t="n">
+      <c r="Q38" s="19" t="n">
         <f aca="false">Q34+Q35+Q36+Q37</f>
         <v>14100</v>
       </c>
-      <c r="R38" s="65" t="n">
+      <c r="R38" s="19" t="n">
         <f aca="false">R34+R35+R36+R37</f>
         <v>17600</v>
       </c>
-      <c r="S38" s="65" t="n">
+      <c r="S38" s="19" t="n">
         <f aca="false">S34+S35+S36+S37</f>
         <v>17600</v>
       </c>
-      <c r="T38" s="65" t="n">
+      <c r="T38" s="19" t="n">
         <f aca="false">T34+T35+T36+T37</f>
         <v>17600</v>
       </c>
-      <c r="U38" s="65" t="n">
+      <c r="U38" s="19" t="n">
         <f aca="false">U34+U35+U36+U37</f>
         <v>20600</v>
       </c>
-      <c r="V38" s="65" t="n">
+      <c r="V38" s="19" t="n">
         <f aca="false">V34+V35+V36+V37</f>
         <v>17600</v>
       </c>
-      <c r="W38" s="65" t="n">
+      <c r="W38" s="19" t="n">
         <f aca="false">W34+W35+W36+W37</f>
         <v>17600</v>
       </c>
-      <c r="X38" s="65" t="n">
+      <c r="X38" s="19" t="n">
         <f aca="false">X34+X35+X36+X37</f>
         <v>18100</v>
       </c>
-      <c r="Y38" s="65" t="n">
+      <c r="Y38" s="19" t="n">
         <f aca="false">Y34+Y35+Y36+Y37</f>
         <v>18100</v>
       </c>
-      <c r="Z38" s="65" t="n">
+      <c r="Z38" s="19" t="n">
         <f aca="false">SUM(B38:M38)</f>
-        <v>226050</v>
-      </c>
-      <c r="AA38" s="65" t="n">
+        <v>207300</v>
+      </c>
+      <c r="AA38" s="19" t="n">
         <f aca="false">SUM(N38:Y38)</f>
         <v>198200</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="50" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="30" t="s">
         <v>132</v>
       </c>
@@ -6540,175 +6512,175 @@
         <v>401</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="B42" s="66" t="n">
+      <c r="B42" s="50" t="n">
         <f aca="false">Z23</f>
-        <v>300250</v>
-      </c>
-      <c r="C42" s="66" t="n">
+        <v>281500</v>
+      </c>
+      <c r="C42" s="50" t="n">
         <f aca="false">AA23</f>
         <v>255000</v>
       </c>
-      <c r="D42" s="66" t="n">
+      <c r="D42" s="50" t="n">
         <f aca="false">B42+C42</f>
-        <v>555250</v>
-      </c>
-      <c r="E42" s="0" t="s">
+        <v>536500</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="67" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="B43" s="68" t="n">
+      <c r="B43" s="52" t="n">
         <f aca="false">Z31</f>
-        <v>265050</v>
-      </c>
-      <c r="C43" s="68" t="n">
+        <v>246300</v>
+      </c>
+      <c r="C43" s="52" t="n">
         <f aca="false">AA31</f>
         <v>225700</v>
       </c>
-      <c r="D43" s="68" t="n">
+      <c r="D43" s="52" t="n">
         <f aca="false">B43+C43</f>
-        <v>490750</v>
-      </c>
-      <c r="E43" s="67" t="s">
+        <v>472000</v>
+      </c>
+      <c r="E43" s="51" t="s">
         <v>569</v>
       </c>
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="51" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B44" s="66" t="n">
+      <c r="B44" s="50" t="n">
         <f aca="false">Z38</f>
-        <v>226050</v>
-      </c>
-      <c r="C44" s="66" t="n">
+        <v>207300</v>
+      </c>
+      <c r="C44" s="50" t="n">
         <f aca="false">AA38</f>
         <v>198200</v>
       </c>
-      <c r="D44" s="66" t="n">
+      <c r="D44" s="50" t="n">
         <f aca="false">B44+C44</f>
-        <v>424250</v>
-      </c>
-      <c r="E44" s="0" t="s">
+        <v>405500</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="50" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="B46" s="50"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="50"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B47" s="69" t="n">
+      <c r="B47" s="41" t="n">
         <f aca="false">B15</f>
         <v>21</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="6" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B48" s="69" t="n">
+      <c r="B48" s="41" t="n">
         <f aca="false">3*18</f>
         <v>54</v>
       </c>
-      <c r="C48" s="52" t="s">
+      <c r="C48" s="6" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B49" s="69" t="n">
+      <c r="B49" s="41" t="n">
         <f aca="false">173/12</f>
         <v>14.4166666666667</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="6" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B50" s="69" t="n">
+      <c r="B50" s="41" t="n">
         <v>30</v>
       </c>
-      <c r="C50" s="52" t="s">
+      <c r="C50" s="6" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="62" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="24" t="s">
         <v>583</v>
       </c>
-      <c r="B51" s="70" t="n">
+      <c r="B51" s="53" t="n">
         <f aca="false">B47+B48+B49+B50</f>
         <v>119.416666666667</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="B52" s="69" t="n">
+      <c r="B52" s="41" t="n">
         <v>180</v>
       </c>
-      <c r="C52" s="52" t="s">
+      <c r="C52" s="6" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="62" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="24" t="s">
         <v>586</v>
       </c>
-      <c r="B53" s="71" t="n">
+      <c r="B53" s="54" t="n">
         <f aca="false">B52-B51</f>
         <v>60.5833333333333</v>
       </c>
-      <c r="C53" s="52" t="s">
+      <c r="C53" s="6" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="50" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="50"/>
-      <c r="E55" s="50"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="50"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
@@ -6881,8 +6853,89 @@
       <c r="N64" s="27"/>
       <c r="O64" s="27"/>
     </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="27" t="s">
+        <v>598</v>
+      </c>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
+      <c r="I65" s="27"/>
+      <c r="J65" s="27"/>
+      <c r="K65" s="27"/>
+      <c r="L65" s="27"/>
+      <c r="M65" s="27"/>
+      <c r="N65" s="27"/>
+      <c r="O65" s="27"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="55" t="s">
+        <v>599</v>
+      </c>
+      <c r="B76" s="55"/>
+      <c r="C76" s="55"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="55"/>
+      <c r="F76" s="55"/>
+      <c r="G76" s="55"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B77" s="56" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B78" s="56" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B79" s="56" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="57" t="s">
+        <v>603</v>
+      </c>
+      <c r="B80" s="58" t="n">
+        <f aca="false">B42*B77+B43*B78+B44*B79</f>
+        <v>241450</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="57" t="s">
+        <v>604</v>
+      </c>
+      <c r="B81" s="58" t="n">
+        <f aca="false">C42*B77+C43*B78+C44*B79</f>
+        <v>223400</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="57" t="s">
+        <v>605</v>
+      </c>
+      <c r="B82" s="58" t="n">
+        <f aca="false">B80+B81</f>
+        <v>464850</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="A2:AA2"/>
     <mergeCell ref="A4:F4"/>
@@ -6901,6 +6954,8 @@
     <mergeCell ref="A62:O62"/>
     <mergeCell ref="A63:O63"/>
     <mergeCell ref="A64:O64"/>
+    <mergeCell ref="A65:O65"/>
+    <mergeCell ref="A76:G76"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
